--- a/backend/edutrack/src/main/resources/templates/sf2-template.xlsx
+++ b/backend/edutrack/src/main/resources/templates/sf2-template.xlsx
@@ -3026,26 +3026,39 @@
     <col width="14.09765625" customWidth="1" style="204" min="3" max="3"/>
     <col width="17.296875" customWidth="1" style="204" min="4" max="4"/>
     <col width="0.09765625" customWidth="1" style="204" min="5" max="5"/>
-    <col width="0.8984375" customWidth="1" style="204" min="6" max="6"/>
-    <col width="2" customWidth="1" style="204" min="7" max="7"/>
-    <col width="2.8984375" customWidth="1" style="204" min="8" max="11"/>
-    <col width="2.59765625" customWidth="1" style="204" min="12" max="12"/>
-    <col width="0.296875" customWidth="1" style="204" min="13" max="13"/>
-    <col width="2.8984375" customWidth="1" style="204" min="14" max="17"/>
-    <col width="0.8984375" customWidth="1" style="204" min="18" max="18"/>
-    <col width="2" customWidth="1" style="204" min="19" max="19"/>
-    <col width="2.8984375" customWidth="1" style="204" min="20" max="21"/>
-    <col width="0.69921875" customWidth="1" style="204" min="22" max="22"/>
-    <col width="2.09765625" customWidth="1" style="204" min="23" max="23"/>
-    <col width="1.09765625" customWidth="1" style="204" min="24" max="24"/>
-    <col width="1.69921875" customWidth="1" style="204" min="25" max="26"/>
-    <col width="1.09765625" customWidth="1" style="204" min="27" max="27"/>
-    <col width="2.8984375" customWidth="1" style="204" min="28" max="32"/>
-    <col width="2.69921875" customWidth="1" style="204" min="33" max="33"/>
-    <col width="0.09765625" customWidth="1" style="204" min="34" max="34"/>
-    <col width="2.8984375" customWidth="1" style="204" min="35" max="36"/>
-    <col width="1.09765625" customWidth="1" style="204" min="37" max="37"/>
-    <col width="1.69921875" customWidth="1" style="204" min="38" max="39"/>
+    <col width="4.2" customWidth="1" style="204" min="6" max="6"/>
+    <col width="4.2" customWidth="1" style="204" min="7" max="7"/>
+    <col width="4.2" customWidth="1" style="204" min="8" max="11"/>
+    <col width="4.2" customWidth="1" style="204" min="9" max="9"/>
+    <col width="4.2" customWidth="1" style="204" min="10" max="10"/>
+    <col width="4.2" customWidth="1" style="204" min="11" max="11"/>
+    <col width="4.2" customWidth="1" style="204" min="12" max="12"/>
+    <col width="4.2" customWidth="1" style="204" min="13" max="13"/>
+    <col width="4.2" customWidth="1" style="204" min="14" max="17"/>
+    <col width="4.2" customWidth="1" style="204" min="15" max="15"/>
+    <col width="4.2" customWidth="1" style="204" min="16" max="16"/>
+    <col width="4.2" customWidth="1" style="204" min="17" max="17"/>
+    <col width="4.2" customWidth="1" style="204" min="18" max="18"/>
+    <col width="4.2" customWidth="1" style="204" min="19" max="19"/>
+    <col width="4.2" customWidth="1" style="204" min="20" max="21"/>
+    <col width="4.2" customWidth="1" style="204" min="21" max="21"/>
+    <col width="4.2" customWidth="1" style="204" min="22" max="22"/>
+    <col width="4.2" customWidth="1" style="204" min="23" max="23"/>
+    <col width="4.2" customWidth="1" style="204" min="24" max="24"/>
+    <col width="4.2" customWidth="1" style="204" min="25" max="26"/>
+    <col width="4.2" customWidth="1" style="204" min="26" max="26"/>
+    <col width="4.2" customWidth="1" style="204" min="27" max="27"/>
+    <col width="4.2" customWidth="1" style="204" min="28" max="32"/>
+    <col width="4.2" customWidth="1" style="204" min="29" max="29"/>
+    <col width="4.2" customWidth="1" style="204" min="30" max="30"/>
+    <col width="4.2" customWidth="1" style="204" min="31" max="31"/>
+    <col width="4.2" customWidth="1" style="204" min="32" max="32"/>
+    <col width="4.2" customWidth="1" style="204" min="33" max="33"/>
+    <col width="4.2" customWidth="1" style="204" min="34" max="34"/>
+    <col width="4.2" customWidth="1" style="204" min="35" max="36"/>
+    <col width="4.2" customWidth="1" style="204" min="36" max="36"/>
+    <col width="4.2" customWidth="1" style="204" min="37" max="37"/>
+    <col width="4.2" customWidth="1" style="204" min="38" max="39"/>
     <col width="5" customWidth="1" style="204" min="40" max="41"/>
     <col width="1.69921875" customWidth="1" style="204" min="42" max="42"/>
     <col width="10.09765625" customWidth="1" style="204" min="43" max="43"/>
@@ -3367,7 +3380,7 @@
       <c r="AJ8" s="9" t="n"/>
       <c r="AK8" s="253" t="n"/>
       <c r="AM8" s="254">
-        <f>COUNTIF(F8:AL8,"X")</f>
+        <f>COUNTIF(F8:AL8,"A")</f>
         <v/>
       </c>
       <c r="AN8" s="255" t="n"/>
@@ -3418,7 +3431,7 @@
       <c r="AJ9" s="9" t="n"/>
       <c r="AK9" s="21" t="n"/>
       <c r="AM9" s="254">
-        <f>COUNTIF(F9:AL9,"X")</f>
+        <f>COUNTIF(F9:AL9,"A")</f>
         <v/>
       </c>
       <c r="AN9" s="255" t="n"/>
@@ -3469,7 +3482,7 @@
       <c r="AJ10" s="9" t="n"/>
       <c r="AK10" s="21" t="n"/>
       <c r="AM10" s="254">
-        <f>COUNTIF(F10:AL10,"X")</f>
+        <f>COUNTIF(F10:AL10,"A")</f>
         <v/>
       </c>
       <c r="AN10" s="255" t="n"/>
@@ -3520,7 +3533,7 @@
       <c r="AJ11" s="9" t="n"/>
       <c r="AK11" s="21" t="n"/>
       <c r="AM11" s="254">
-        <f>COUNTIF(F11:AL11,"X")</f>
+        <f>COUNTIF(F11:AL11,"A")</f>
         <v/>
       </c>
       <c r="AN11" s="255" t="n"/>
@@ -3571,7 +3584,7 @@
       <c r="AJ12" s="9" t="n"/>
       <c r="AK12" s="21" t="n"/>
       <c r="AM12" s="254">
-        <f>COUNTIF(F12:AL12,"X")</f>
+        <f>COUNTIF(F12:AL12,"A")</f>
         <v/>
       </c>
       <c r="AN12" s="255" t="n"/>
@@ -3622,7 +3635,7 @@
       <c r="AJ13" s="9" t="n"/>
       <c r="AK13" s="21" t="n"/>
       <c r="AM13" s="254">
-        <f>COUNTIF(F13:AL13,"X")</f>
+        <f>COUNTIF(F13:AL13,"A")</f>
         <v/>
       </c>
       <c r="AN13" s="255" t="n"/>
@@ -3673,7 +3686,7 @@
       <c r="AJ14" s="9" t="n"/>
       <c r="AK14" s="21" t="n"/>
       <c r="AM14" s="254">
-        <f>COUNTIF(F14:AL14,"X")</f>
+        <f>COUNTIF(F14:AL14,"A")</f>
         <v/>
       </c>
       <c r="AN14" s="255" t="n"/>
@@ -3724,7 +3737,7 @@
       <c r="AJ15" s="9" t="n"/>
       <c r="AK15" s="21" t="n"/>
       <c r="AM15" s="254">
-        <f>COUNTIF(F15:AL15,"X")</f>
+        <f>COUNTIF(F15:AL15,"A")</f>
         <v/>
       </c>
       <c r="AN15" s="255" t="n"/>
@@ -3775,7 +3788,7 @@
       <c r="AJ16" s="9" t="n"/>
       <c r="AK16" s="21" t="n"/>
       <c r="AM16" s="254">
-        <f>COUNTIF(F16:AL16,"X")</f>
+        <f>COUNTIF(F16:AL16,"A")</f>
         <v/>
       </c>
       <c r="AN16" s="255" t="n"/>
@@ -3824,7 +3837,7 @@
       <c r="AJ17" s="9" t="n"/>
       <c r="AK17" s="21" t="n"/>
       <c r="AM17" s="254">
-        <f>COUNTIF(F17:AL17,"X")</f>
+        <f>COUNTIF(F17:AL17,"A")</f>
         <v/>
       </c>
       <c r="AN17" s="255" t="n"/>
@@ -3879,7 +3892,7 @@
       <c r="AJ18" s="9" t="n"/>
       <c r="AK18" s="21" t="n"/>
       <c r="AM18" s="254">
-        <f>COUNTIF(F18:AL18,"X")</f>
+        <f>COUNTIF(F18:AL18,"A")</f>
         <v/>
       </c>
       <c r="AN18" s="255" t="n"/>
@@ -3930,7 +3943,7 @@
       <c r="AJ19" s="9" t="n"/>
       <c r="AK19" s="21" t="n"/>
       <c r="AM19" s="254">
-        <f>COUNTIF(F19:AL19,"X")</f>
+        <f>COUNTIF(F19:AL19,"A")</f>
         <v/>
       </c>
       <c r="AN19" s="255" t="n"/>
@@ -3981,7 +3994,7 @@
       <c r="AJ20" s="9" t="n"/>
       <c r="AK20" s="21" t="n"/>
       <c r="AM20" s="254">
-        <f>COUNTIF(F20:AL20,"X")</f>
+        <f>COUNTIF(F20:AL20,"A")</f>
         <v/>
       </c>
       <c r="AN20" s="255" t="n"/>
@@ -4032,7 +4045,7 @@
       <c r="AJ21" s="9" t="n"/>
       <c r="AK21" s="21" t="n"/>
       <c r="AM21" s="254">
-        <f>COUNTIF(F21:AL21,"X")</f>
+        <f>COUNTIF(F21:AL21,"A")</f>
         <v/>
       </c>
       <c r="AN21" s="255" t="n"/>
@@ -4083,7 +4096,7 @@
       <c r="AJ22" s="9" t="n"/>
       <c r="AK22" s="21" t="n"/>
       <c r="AM22" s="254">
-        <f>COUNTIF(F22:AL22,"X")</f>
+        <f>COUNTIF(F22:AL22,"A")</f>
         <v/>
       </c>
       <c r="AN22" s="255" t="n"/>
@@ -4134,7 +4147,7 @@
       <c r="AJ23" s="9" t="n"/>
       <c r="AK23" s="21" t="n"/>
       <c r="AM23" s="254">
-        <f>COUNTIF(F23:AL23,"X")</f>
+        <f>COUNTIF(F23:AL23,"A")</f>
         <v/>
       </c>
       <c r="AN23" s="255" t="n"/>
@@ -4185,7 +4198,7 @@
       <c r="AJ24" s="9" t="n"/>
       <c r="AK24" s="21" t="n"/>
       <c r="AM24" s="254">
-        <f>COUNTIF(F24:AL24,"X")</f>
+        <f>COUNTIF(F24:AL24,"A")</f>
         <v/>
       </c>
       <c r="AN24" s="255" t="n"/>
@@ -4234,7 +4247,7 @@
       <c r="AJ25" s="36" t="n"/>
       <c r="AK25" s="21" t="n"/>
       <c r="AM25" s="254">
-        <f>COUNTIF(F25:AL25,"X")</f>
+        <f>COUNTIF(F25:AL25,"A")</f>
         <v/>
       </c>
       <c r="AN25" s="255" t="n"/>
@@ -4285,12 +4298,12 @@
       <c r="AJ26" s="9" t="n"/>
       <c r="AK26" s="179" t="n"/>
       <c r="AM26" s="254">
-        <f>COUNTIF(F26:AL26,"X")</f>
+        <f>COUNTIF(F26:AL26,"A")</f>
         <v/>
       </c>
       <c r="AN26" s="255" t="n"/>
       <c r="AO26" s="254">
-        <f>$AW$4-AM26</f>
+        <f>AW4-AM26</f>
         <v/>
       </c>
       <c r="AP26" s="255" t="n"/>
@@ -4336,12 +4349,12 @@
       <c r="AJ27" s="9" t="n"/>
       <c r="AK27" s="179" t="n"/>
       <c r="AM27" s="254">
-        <f>COUNTIF(F27:AL27,"X")</f>
+        <f>COUNTIF(F27:AL27,"A")</f>
         <v/>
       </c>
       <c r="AN27" s="255" t="n"/>
       <c r="AO27" s="254">
-        <f>$AW$4-AM27</f>
+        <f>AW4-AM27</f>
         <v/>
       </c>
       <c r="AP27" s="255" t="n"/>
@@ -4385,12 +4398,12 @@
       <c r="AJ28" s="9" t="n"/>
       <c r="AK28" s="21" t="n"/>
       <c r="AM28" s="254">
-        <f>COUNTIF(F28:AL28,"X")</f>
+        <f>COUNTIF(F28:AL28,"A")</f>
         <v/>
       </c>
       <c r="AN28" s="255" t="n"/>
       <c r="AO28" s="254">
-        <f>$AW$4-AM28</f>
+        <f>AW4-AM28</f>
         <v/>
       </c>
       <c r="AP28" s="255" t="n"/>
@@ -4434,12 +4447,12 @@
       <c r="AJ29" s="36" t="n"/>
       <c r="AK29" s="21" t="n"/>
       <c r="AM29" s="254">
-        <f>COUNTIF(F29:AL29,"X")</f>
+        <f>COUNTIF(F29:AL29,"A")</f>
         <v/>
       </c>
       <c r="AN29" s="255" t="n"/>
       <c r="AO29" s="254">
-        <f>$AW$4-AM29</f>
+        <f>AW4-AM29</f>
         <v/>
       </c>
       <c r="AP29" s="255" t="n"/>
@@ -4485,12 +4498,12 @@
       <c r="AJ30" s="9" t="n"/>
       <c r="AK30" s="179" t="n"/>
       <c r="AM30" s="254">
-        <f>COUNTIF(F30:AL30,"X")</f>
+        <f>COUNTIF(F30:AL30,"A")</f>
         <v/>
       </c>
       <c r="AN30" s="255" t="n"/>
       <c r="AO30" s="254">
-        <f>$AW$4-AM30</f>
+        <f>AW4-AM30</f>
         <v/>
       </c>
       <c r="AP30" s="255" t="n"/>
@@ -4535,9 +4548,15 @@
       <c r="AI31" s="55" t="n"/>
       <c r="AJ31" s="9" t="n"/>
       <c r="AK31" s="179" t="n"/>
-      <c r="AM31" s="254" t="n"/>
+      <c r="AM31" s="254">
+        <f>COUNTIF(F31:AL31,"A")</f>
+        <v/>
+      </c>
       <c r="AN31" s="255" t="n"/>
-      <c r="AO31" s="254" t="n"/>
+      <c r="AO31" s="254">
+        <f>AW4-AM31</f>
+        <v/>
+      </c>
       <c r="AP31" s="255" t="n"/>
       <c r="AQ31" s="48" t="n"/>
       <c r="AR31" s="220" t="n"/>
@@ -4578,9 +4597,15 @@
       <c r="AI32" s="55" t="n"/>
       <c r="AJ32" s="9" t="n"/>
       <c r="AK32" s="179" t="n"/>
-      <c r="AM32" s="254" t="n"/>
+      <c r="AM32" s="254">
+        <f>COUNTIF(F32:AL32,"A")</f>
+        <v/>
+      </c>
       <c r="AN32" s="255" t="n"/>
-      <c r="AO32" s="254" t="n"/>
+      <c r="AO32" s="254">
+        <f>AW4-AM32</f>
+        <v/>
+      </c>
       <c r="AP32" s="255" t="n"/>
       <c r="AQ32" s="48" t="n"/>
       <c r="AR32" s="220" t="n"/>
@@ -4673,7 +4698,7 @@
       <c r="AJ34" s="9" t="n"/>
       <c r="AK34" s="21" t="n"/>
       <c r="AM34" s="254">
-        <f>COUNTIF(F34:AL34,"X")</f>
+        <f>COUNTIF(F34:AL34,"A")</f>
         <v/>
       </c>
       <c r="AN34" s="255" t="n"/>
@@ -4722,7 +4747,7 @@
       <c r="AJ35" s="9" t="n"/>
       <c r="AK35" s="21" t="n"/>
       <c r="AM35" s="254">
-        <f>COUNTIF(F35:AL35,"X")</f>
+        <f>COUNTIF(F35:AL35,"A")</f>
         <v/>
       </c>
       <c r="AN35" s="255" t="n"/>
@@ -4771,7 +4796,7 @@
       <c r="AJ36" s="9" t="n"/>
       <c r="AK36" s="21" t="n"/>
       <c r="AM36" s="254">
-        <f>COUNTIF(F36:AL36,"X")</f>
+        <f>COUNTIF(F36:AL36,"A")</f>
         <v/>
       </c>
       <c r="AN36" s="255" t="n"/>
@@ -4820,7 +4845,7 @@
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="21" t="n"/>
       <c r="AM37" s="254">
-        <f>COUNTIF(F37:AL37,"X")</f>
+        <f>COUNTIF(F37:AL37,"A")</f>
         <v/>
       </c>
       <c r="AN37" s="255" t="n"/>
@@ -4869,7 +4894,7 @@
       <c r="AJ38" s="9" t="n"/>
       <c r="AK38" s="21" t="n"/>
       <c r="AM38" s="254">
-        <f>COUNTIF(F38:AL38,"X")</f>
+        <f>COUNTIF(F38:AL38,"A")</f>
         <v/>
       </c>
       <c r="AN38" s="255" t="n"/>
@@ -4918,7 +4943,7 @@
       <c r="AJ39" s="9" t="n"/>
       <c r="AK39" s="21" t="n"/>
       <c r="AM39" s="254">
-        <f>COUNTIF(F39:AL39,"X")</f>
+        <f>COUNTIF(F39:AL39,"A")</f>
         <v/>
       </c>
       <c r="AN39" s="255" t="n"/>
@@ -4967,7 +4992,7 @@
       <c r="AJ40" s="9" t="n"/>
       <c r="AK40" s="21" t="n"/>
       <c r="AM40" s="254">
-        <f>COUNTIF(F40:AL40,"X")</f>
+        <f>COUNTIF(F40:AL40,"A")</f>
         <v/>
       </c>
       <c r="AN40" s="255" t="n"/>
@@ -5016,7 +5041,7 @@
       <c r="AJ41" s="9" t="n"/>
       <c r="AK41" s="21" t="n"/>
       <c r="AM41" s="254">
-        <f>COUNTIF(F41:AL41,"X")</f>
+        <f>COUNTIF(F41:AL41,"A")</f>
         <v/>
       </c>
       <c r="AN41" s="255" t="n"/>
@@ -5065,7 +5090,7 @@
       <c r="AJ42" s="9" t="n"/>
       <c r="AK42" s="21" t="n"/>
       <c r="AM42" s="254">
-        <f>COUNTIF(F42:AL42,"X")</f>
+        <f>COUNTIF(F42:AL42,"A")</f>
         <v/>
       </c>
       <c r="AN42" s="255" t="n"/>
@@ -5114,7 +5139,7 @@
       <c r="AJ43" s="9" t="n"/>
       <c r="AK43" s="21" t="n"/>
       <c r="AM43" s="254">
-        <f>COUNTIF(F43:AL43,"X")</f>
+        <f>COUNTIF(F43:AL43,"A")</f>
         <v/>
       </c>
       <c r="AN43" s="255" t="n"/>
@@ -5163,7 +5188,7 @@
       <c r="AJ44" s="9" t="n"/>
       <c r="AK44" s="21" t="n"/>
       <c r="AM44" s="254">
-        <f>COUNTIF(F44:AL44,"X")</f>
+        <f>COUNTIF(F44:AL44,"A")</f>
         <v/>
       </c>
       <c r="AN44" s="255" t="n"/>
@@ -5212,7 +5237,7 @@
       <c r="AJ45" s="9" t="n"/>
       <c r="AK45" s="21" t="n"/>
       <c r="AM45" s="254">
-        <f>COUNTIF(F45:AL45,"X")</f>
+        <f>COUNTIF(F45:AL45,"A")</f>
         <v/>
       </c>
       <c r="AN45" s="255" t="n"/>
@@ -5263,7 +5288,7 @@
       <c r="AJ46" s="9" t="n"/>
       <c r="AK46" s="179" t="n"/>
       <c r="AM46" s="254">
-        <f>COUNTIF(F46:AL46,"X")</f>
+        <f>COUNTIF(F46:AL46,"A")</f>
         <v/>
       </c>
       <c r="AN46" s="255" t="n"/>
@@ -5314,7 +5339,7 @@
       <c r="AJ47" s="9" t="n"/>
       <c r="AK47" s="179" t="n"/>
       <c r="AM47" s="254">
-        <f>COUNTIF(F47:AL47,"X")</f>
+        <f>COUNTIF(F47:AL47,"A")</f>
         <v/>
       </c>
       <c r="AN47" s="255" t="n"/>
@@ -5365,7 +5390,7 @@
       <c r="AJ48" s="179" t="n"/>
       <c r="AK48" s="179" t="n"/>
       <c r="AM48" s="254">
-        <f>COUNTIF(F48:AL48,"X")</f>
+        <f>COUNTIF(F48:AL48,"A")</f>
         <v/>
       </c>
       <c r="AN48" s="255" t="n"/>
@@ -5416,7 +5441,7 @@
       <c r="AJ49" s="179" t="n"/>
       <c r="AK49" s="179" t="n"/>
       <c r="AM49" s="254">
-        <f>COUNTIF(F49:AL49,"X")</f>
+        <f>COUNTIF(F49:AL49,"A")</f>
         <v/>
       </c>
       <c r="AN49" s="255" t="n"/>
@@ -5467,7 +5492,7 @@
       <c r="AJ50" s="179" t="n"/>
       <c r="AK50" s="179" t="n"/>
       <c r="AM50" s="254">
-        <f>COUNTIF(F50:AL50,"X")</f>
+        <f>COUNTIF(F50:AL50,"A")</f>
         <v/>
       </c>
       <c r="AN50" s="255" t="n"/>
@@ -5516,7 +5541,7 @@
       <c r="AJ51" s="9" t="n"/>
       <c r="AK51" s="21" t="n"/>
       <c r="AM51" s="254">
-        <f>COUNTIF(F51:AL51,"X")</f>
+        <f>COUNTIF(F51:AL51,"A")</f>
         <v/>
       </c>
       <c r="AN51" s="255" t="n"/>
@@ -5565,7 +5590,7 @@
       <c r="AJ52" s="9" t="n"/>
       <c r="AK52" s="21" t="n"/>
       <c r="AM52" s="254">
-        <f>COUNTIF(F52:AL52,"X")</f>
+        <f>COUNTIF(F52:AL52,"A")</f>
         <v/>
       </c>
       <c r="AN52" s="255" t="n"/>
@@ -5614,7 +5639,7 @@
       <c r="AJ53" s="9" t="n"/>
       <c r="AK53" s="21" t="n"/>
       <c r="AM53" s="254">
-        <f>COUNTIF(F53:AL53,"X")</f>
+        <f>COUNTIF(F53:AL53,"A")</f>
         <v/>
       </c>
       <c r="AN53" s="255" t="n"/>
@@ -5663,7 +5688,7 @@
       <c r="AJ54" s="9" t="n"/>
       <c r="AK54" s="21" t="n"/>
       <c r="AM54" s="254">
-        <f>COUNTIF(F54:AL54,"X")</f>
+        <f>COUNTIF(F54:AL54,"A")</f>
         <v/>
       </c>
       <c r="AN54" s="255" t="n"/>
@@ -5714,7 +5739,7 @@
       <c r="AJ55" s="9" t="n"/>
       <c r="AK55" s="179" t="n"/>
       <c r="AM55" s="254">
-        <f>COUNTIF(F55:AL55,"X")</f>
+        <f>COUNTIF(F55:AL55,"A")</f>
         <v/>
       </c>
       <c r="AN55" s="255" t="n"/>
@@ -5765,7 +5790,7 @@
       <c r="AJ56" s="9" t="n"/>
       <c r="AK56" s="179" t="n"/>
       <c r="AM56" s="254">
-        <f>COUNTIF(F56:AL56,"X")</f>
+        <f>COUNTIF(F56:AL56,"A")</f>
         <v/>
       </c>
       <c r="AN56" s="255" t="n"/>
@@ -5816,7 +5841,7 @@
       <c r="AJ57" s="179" t="n"/>
       <c r="AK57" s="179" t="n"/>
       <c r="AM57" s="254">
-        <f>COUNTIF(F57:AL57,"X")</f>
+        <f>COUNTIF(F57:AL57,"A")</f>
         <v/>
       </c>
       <c r="AN57" s="255" t="n"/>
@@ -5866,9 +5891,15 @@
       <c r="AI58" s="22" t="n"/>
       <c r="AJ58" s="179" t="n"/>
       <c r="AK58" s="179" t="n"/>
-      <c r="AM58" s="254" t="n"/>
+      <c r="AM58" s="254">
+        <f>COUNTIF(F58:AL58,"A")</f>
+        <v/>
+      </c>
       <c r="AN58" s="255" t="n"/>
-      <c r="AO58" s="254" t="n"/>
+      <c r="AO58" s="254">
+        <f>AW4-AM58</f>
+        <v/>
+      </c>
       <c r="AP58" s="255" t="n"/>
       <c r="AQ58" s="48" t="n"/>
       <c r="AR58" s="220" t="n"/>
@@ -5911,9 +5942,15 @@
       <c r="AI59" s="22" t="n"/>
       <c r="AJ59" s="179" t="n"/>
       <c r="AK59" s="179" t="n"/>
-      <c r="AM59" s="254" t="n"/>
+      <c r="AM59" s="254">
+        <f>COUNTIF(F59:AL59,"A")</f>
+        <v/>
+      </c>
       <c r="AN59" s="255" t="n"/>
-      <c r="AO59" s="254" t="n"/>
+      <c r="AO59" s="254">
+        <f>AW4-AM59</f>
+        <v/>
+      </c>
       <c r="AP59" s="255" t="n"/>
       <c r="AQ59" s="48" t="n"/>
       <c r="AR59" s="220" t="n"/>
@@ -5954,9 +5991,15 @@
       <c r="AI60" s="38" t="n"/>
       <c r="AJ60" s="9" t="n"/>
       <c r="AK60" s="179" t="n"/>
-      <c r="AM60" s="254" t="n"/>
+      <c r="AM60" s="254">
+        <f>COUNTIF(F60:AL60,"A")</f>
+        <v/>
+      </c>
       <c r="AN60" s="255" t="n"/>
-      <c r="AO60" s="254" t="n"/>
+      <c r="AO60" s="254">
+        <f>AW4-AM60</f>
+        <v/>
+      </c>
       <c r="AP60" s="255" t="n"/>
       <c r="AQ60" s="48" t="n"/>
       <c r="AR60" s="220" t="n"/>
@@ -6093,18 +6136,10 @@
       <c r="AJ63" s="291" t="n"/>
       <c r="AK63" s="242" t="n"/>
       <c r="AL63" s="4" t="n"/>
-      <c r="AM63" s="292" t="inlineStr">
-        <is>
-          <t>Month :              JUNE</t>
-        </is>
-      </c>
+      <c r="AM63" s="292" t="n"/>
       <c r="AN63" s="223" t="n"/>
       <c r="AO63" s="231" t="n"/>
-      <c r="AP63" s="293" t="inlineStr">
-        <is>
-          <t>No. of Days of Classes: 16</t>
-        </is>
-      </c>
+      <c r="AP63" s="293" t="n"/>
       <c r="AQ63" s="231" t="n"/>
       <c r="AR63" s="294" t="inlineStr">
         <is>
@@ -6164,16 +6199,9 @@
         </is>
       </c>
       <c r="AQ65" s="248" t="n"/>
-      <c r="AR65" s="299" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS65" s="300" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT65" s="301">
-        <f>SUM(AR65:AS66)</f>
-        <v/>
-      </c>
+      <c r="AR65" s="299" t="n"/>
+      <c r="AS65" s="300" t="n"/>
+      <c r="AT65" s="301" t="n"/>
       <c r="AU65" s="302" t="n"/>
     </row>
     <row r="66" ht="7.5" customHeight="1" s="204">
@@ -6212,16 +6240,9 @@
         </is>
       </c>
       <c r="AQ67" s="248" t="n"/>
-      <c r="AR67" s="300" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS67" s="300" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT67" s="311">
-        <f>SUM(AR67:AS70)</f>
-        <v/>
-      </c>
+      <c r="AR67" s="300" t="n"/>
+      <c r="AS67" s="300" t="n"/>
+      <c r="AT67" s="311" t="n"/>
       <c r="AU67" s="302" t="n"/>
     </row>
     <row r="68" ht="6.75" customHeight="1" s="204">
@@ -6363,16 +6384,9 @@
       <c r="AO71" s="291" t="n"/>
       <c r="AP71" s="291" t="n"/>
       <c r="AQ71" s="242" t="n"/>
-      <c r="AR71" s="316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS71" s="316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT71" s="317">
-        <f>SUM(AR71:AS72)</f>
-        <v/>
-      </c>
+      <c r="AR71" s="316" t="n"/>
+      <c r="AS71" s="316" t="n"/>
+      <c r="AT71" s="317" t="n"/>
       <c r="AU71" s="302" t="n"/>
     </row>
     <row r="72" ht="9.75" customHeight="1" s="204">
@@ -6449,18 +6463,9 @@
       <c r="AO73" s="291" t="n"/>
       <c r="AP73" s="291" t="n"/>
       <c r="AQ73" s="242" t="n"/>
-      <c r="AR73" s="319">
-        <f>(AR71/AR65)*100%</f>
-        <v/>
-      </c>
-      <c r="AS73" s="319">
-        <f>(AS71/AS65)*100%</f>
-        <v/>
-      </c>
-      <c r="AT73" s="320">
-        <f>(AT71/AT65)*100%</f>
-        <v/>
-      </c>
+      <c r="AR73" s="319" t="n"/>
+      <c r="AS73" s="319" t="n"/>
+      <c r="AT73" s="320" t="n"/>
       <c r="AU73" s="302" t="n"/>
     </row>
     <row r="74" ht="12" customHeight="1" s="204">
@@ -6539,18 +6544,9 @@
         </is>
       </c>
       <c r="AQ75" s="248" t="n"/>
-      <c r="AR75" s="17">
-        <f>AO33/AW4*100%%</f>
-        <v/>
-      </c>
-      <c r="AS75" s="17">
-        <f>AO61/AW4*100%%</f>
-        <v/>
-      </c>
-      <c r="AT75" s="321">
-        <f>AO62/AW4*100%%</f>
-        <v/>
-      </c>
+      <c r="AR75" s="17" t="n"/>
+      <c r="AS75" s="17" t="n"/>
+      <c r="AT75" s="321" t="n"/>
       <c r="AU75" s="302" t="n"/>
     </row>
     <row r="76" ht="1.5" customHeight="1" s="204">
@@ -6589,18 +6585,9 @@
       <c r="AO77" s="305" t="n"/>
       <c r="AP77" s="305" t="n"/>
       <c r="AQ77" s="258" t="n"/>
-      <c r="AR77" s="17">
-        <f>AR75/AR71*100</f>
-        <v/>
-      </c>
-      <c r="AS77" s="17">
-        <f>AS75/AS71*100</f>
-        <v/>
-      </c>
-      <c r="AT77" s="321">
-        <f>AT75/AT71*100</f>
-        <v/>
-      </c>
+      <c r="AR77" s="17" t="n"/>
+      <c r="AS77" s="17" t="n"/>
+      <c r="AT77" s="321" t="n"/>
       <c r="AU77" s="255" t="n"/>
     </row>
     <row r="78" ht="17.25" customHeight="1" s="204">
@@ -6617,16 +6604,9 @@
       <c r="AO78" s="305" t="n"/>
       <c r="AP78" s="305" t="n"/>
       <c r="AQ78" s="258" t="n"/>
-      <c r="AR78" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS78" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT78" s="322">
-        <f>SUM(AR78:AS78)</f>
-        <v/>
-      </c>
+      <c r="AR78" s="18" t="n"/>
+      <c r="AS78" s="18" t="n"/>
+      <c r="AT78" s="322" t="n"/>
       <c r="AU78" s="255" t="n"/>
     </row>
     <row r="79" ht="9.75" customHeight="1" s="204">
@@ -6643,16 +6623,9 @@
       <c r="AO79" s="291" t="n"/>
       <c r="AP79" s="291" t="n"/>
       <c r="AQ79" s="242" t="n"/>
-      <c r="AR79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT79" s="322">
-        <f>SUM(AR79:AS80)</f>
-        <v/>
-      </c>
+      <c r="AR79" s="18" t="n"/>
+      <c r="AS79" s="18" t="n"/>
+      <c r="AT79" s="322" t="n"/>
       <c r="AU79" s="302" t="n"/>
     </row>
     <row r="80" ht="9.75" customHeight="1" s="204">
@@ -6716,16 +6689,9 @@
         </is>
       </c>
       <c r="AQ81" s="248" t="n"/>
-      <c r="AR81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT81" s="322">
-        <f>SUM(AR81:AS82)</f>
-        <v/>
-      </c>
+      <c r="AR81" s="18" t="n"/>
+      <c r="AS81" s="18" t="n"/>
+      <c r="AT81" s="322" t="n"/>
       <c r="AU81" s="302" t="n"/>
     </row>
     <row r="82" ht="9.75" customHeight="1" s="204">
@@ -6787,16 +6753,9 @@
         </is>
       </c>
       <c r="AQ83" s="248" t="n"/>
-      <c r="AR83" s="333" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS83" s="333" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT83" s="322">
-        <f>SUM(AR83:AS84)</f>
-        <v/>
-      </c>
+      <c r="AR83" s="333" t="n"/>
+      <c r="AS83" s="333" t="n"/>
+      <c r="AT83" s="322" t="n"/>
       <c r="AU83" s="302" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="204" thickBot="1">

--- a/backend/edutrack/src/main/resources/templates/sf2-template.xlsx
+++ b/backend/edutrack/src/main/resources/templates/sf2-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Edutrack\backend\edutrack\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56DA7D8-475B-4052-82C7-7E65C6376761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9959B98B-7B99-40AD-ABF8-CDC5A00C0FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,7 +266,7 @@
     <numFmt numFmtId="164" formatCode="#.###"/>
     <numFmt numFmtId="165" formatCode="#.####"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -353,11 +353,6 @@
       <name val="Sansserif"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="5"/>
       <name val="Arial Narrow"/>
@@ -397,13 +392,6 @@
       <name val="SansSerif"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
@@ -413,16 +401,16 @@
       <name val="Sansserif"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Sansserif"/>
-    </font>
-    <font>
       <sz val="7"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Sansserif"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1678,7 +1666,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1690,84 +1678,99 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="28" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="52" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
@@ -1775,42 +1778,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1822,10 +1798,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1840,12 +1813,35 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
@@ -1853,91 +1849,110 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1945,89 +1960,59 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="28" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2382,7 +2367,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="30" customHeight="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31"/>
@@ -2433,7 +2418,7 @@
       <c r="AU1" s="31"/>
     </row>
     <row r="2" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="130" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="31"/>
@@ -2484,31 +2469,31 @@
       <c r="AU2" s="31"/>
     </row>
     <row r="3" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="31"/>
       <c r="C3" s="31"/>
       <c r="D3" s="31"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="70">
+      <c r="F3" s="61">
         <v>107964</v>
       </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="53" t="s">
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="30" t="s">
         <v>3</v>
       </c>
       <c r="K3" s="31"/>
       <c r="L3" s="31"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="53" t="s">
+      <c r="M3" s="63"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="30" t="s">
         <v>4</v>
       </c>
       <c r="T3" s="31"/>
@@ -2518,13 +2503,13 @@
       <c r="X3" s="31"/>
       <c r="Y3" s="31"/>
       <c r="Z3" s="31"/>
-      <c r="AA3" s="23"/>
-      <c r="AB3" s="24"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="24"/>
-      <c r="AG3" s="25"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="22"/>
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="22"/>
+      <c r="AE3" s="22"/>
+      <c r="AF3" s="22"/>
+      <c r="AG3" s="62"/>
       <c r="AH3" s="4"/>
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
@@ -2539,33 +2524,33 @@
       <c r="AS3" s="4"/>
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
-      <c r="AW3" s="113"/>
+      <c r="AW3" s="122"/>
       <c r="AX3" s="31"/>
     </row>
     <row r="4" spans="1:50" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="30" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="53" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="30" t="s">
         <v>7</v>
       </c>
       <c r="T4" s="31"/>
@@ -2575,3365 +2560,3365 @@
       <c r="X4" s="31"/>
       <c r="Y4" s="31"/>
       <c r="Z4" s="31"/>
-      <c r="AA4" s="70"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="24"/>
-      <c r="AG4" s="25"/>
+      <c r="AA4" s="61"/>
+      <c r="AB4" s="22"/>
+      <c r="AC4" s="22"/>
+      <c r="AD4" s="22"/>
+      <c r="AE4" s="22"/>
+      <c r="AF4" s="22"/>
+      <c r="AG4" s="62"/>
       <c r="AH4" s="4"/>
-      <c r="AI4" s="53" t="s">
+      <c r="AI4" s="30" t="s">
         <v>8</v>
       </c>
       <c r="AJ4" s="31"/>
       <c r="AK4" s="31"/>
       <c r="AL4" s="31"/>
-      <c r="AM4" s="70"/>
-      <c r="AN4" s="24"/>
-      <c r="AO4" s="24"/>
-      <c r="AP4" s="24"/>
-      <c r="AQ4" s="24"/>
-      <c r="AR4" s="24"/>
-      <c r="AS4" s="24"/>
-      <c r="AT4" s="24"/>
-      <c r="AU4" s="25"/>
+      <c r="AM4" s="61"/>
+      <c r="AN4" s="22"/>
+      <c r="AO4" s="22"/>
+      <c r="AP4" s="22"/>
+      <c r="AQ4" s="22"/>
+      <c r="AR4" s="22"/>
+      <c r="AS4" s="22"/>
+      <c r="AT4" s="22"/>
+      <c r="AU4" s="62"/>
       <c r="AV4" s="1"/>
       <c r="AW4" s="2"/>
     </row>
     <row r="5" spans="1:50" ht="9.75" customHeight="1" thickBot="1">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="147" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="148"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="145" t="s">
+      <c r="D5" s="67"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="56"/>
-      <c r="Z5" s="56"/>
-      <c r="AA5" s="56"/>
-      <c r="AB5" s="56"/>
-      <c r="AC5" s="56"/>
-      <c r="AD5" s="56"/>
-      <c r="AE5" s="56"/>
-      <c r="AF5" s="56"/>
-      <c r="AG5" s="56"/>
-      <c r="AH5" s="56"/>
-      <c r="AI5" s="56"/>
-      <c r="AJ5" s="56"/>
-      <c r="AK5" s="56"/>
-      <c r="AL5" s="146"/>
-      <c r="AM5" s="150" t="s">
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="48"/>
+      <c r="Z5" s="48"/>
+      <c r="AA5" s="48"/>
+      <c r="AB5" s="48"/>
+      <c r="AC5" s="48"/>
+      <c r="AD5" s="48"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="48"/>
+      <c r="AJ5" s="48"/>
+      <c r="AK5" s="48"/>
+      <c r="AL5" s="65"/>
+      <c r="AM5" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="AN5" s="56"/>
-      <c r="AO5" s="56"/>
-      <c r="AP5" s="58"/>
+      <c r="AN5" s="48"/>
+      <c r="AO5" s="48"/>
+      <c r="AP5" s="50"/>
       <c r="AQ5" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="56"/>
-      <c r="AS5" s="56"/>
-      <c r="AT5" s="56"/>
-      <c r="AU5" s="58"/>
+      <c r="AR5" s="48"/>
+      <c r="AS5" s="48"/>
+      <c r="AT5" s="48"/>
+      <c r="AU5" s="50"/>
     </row>
     <row r="6" spans="1:50" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="101"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="101"/>
+      <c r="A6" s="69"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="69"/>
       <c r="D6" s="31"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="18"/>
-      <c r="AC6" s="18"/>
-      <c r="AD6" s="18"/>
-      <c r="AE6" s="18"/>
-      <c r="AF6" s="18"/>
-      <c r="AG6" s="18"/>
-      <c r="AH6" s="19"/>
-      <c r="AI6" s="18"/>
-      <c r="AJ6" s="18"/>
-      <c r="AK6" s="18"/>
-      <c r="AL6" s="19"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="13"/>
+      <c r="AG6" s="13"/>
+      <c r="AH6" s="13"/>
+      <c r="AI6" s="13"/>
+      <c r="AJ6" s="13"/>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="13"/>
       <c r="AM6" s="31"/>
       <c r="AN6" s="31"/>
-      <c r="AO6" s="79"/>
-      <c r="AP6" s="60"/>
-      <c r="AQ6" s="46"/>
+      <c r="AO6" s="85"/>
+      <c r="AP6" s="52"/>
+      <c r="AQ6" s="97"/>
       <c r="AR6" s="31"/>
       <c r="AS6" s="31"/>
       <c r="AT6" s="31"/>
       <c r="AU6" s="152"/>
-      <c r="AW6" s="131"/>
-      <c r="AX6" s="128"/>
+      <c r="AW6" s="136"/>
+      <c r="AX6" s="127"/>
     </row>
     <row r="7" spans="1:50" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="103"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="149"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
-      <c r="V7" s="18"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="18"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="18"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="18"/>
-      <c r="AC7" s="18"/>
-      <c r="AD7" s="18"/>
-      <c r="AE7" s="18"/>
-      <c r="AF7" s="18"/>
-      <c r="AG7" s="18"/>
-      <c r="AH7" s="19"/>
-      <c r="AI7" s="18"/>
-      <c r="AJ7" s="18"/>
-      <c r="AK7" s="18"/>
-      <c r="AL7" s="20"/>
-      <c r="AM7" s="111" t="s">
+      <c r="A7" s="71"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="15"/>
+      <c r="AI7" s="14"/>
+      <c r="AJ7" s="14"/>
+      <c r="AK7" s="14"/>
+      <c r="AL7" s="16"/>
+      <c r="AM7" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="AN7" s="112"/>
-      <c r="AO7" s="94" t="s">
+      <c r="AN7" s="91"/>
+      <c r="AO7" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="AP7" s="95"/>
-      <c r="AQ7" s="59"/>
-      <c r="AR7" s="79"/>
-      <c r="AS7" s="79"/>
-      <c r="AT7" s="79"/>
-      <c r="AU7" s="60"/>
-      <c r="AW7" s="86"/>
-      <c r="AX7" s="67"/>
+      <c r="AP7" s="110"/>
+      <c r="AQ7" s="51"/>
+      <c r="AR7" s="85"/>
+      <c r="AS7" s="85"/>
+      <c r="AT7" s="85"/>
+      <c r="AU7" s="52"/>
+      <c r="AW7" s="95"/>
+      <c r="AX7" s="58"/>
     </row>
     <row r="8" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A8" s="105">
+      <c r="A8" s="118">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="106"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="7"/>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="6"/>
-      <c r="AK8" s="6"/>
-      <c r="AL8" s="16"/>
-      <c r="AM8" s="115">
+      <c r="B8" s="40"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="154"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="154"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="154"/>
+      <c r="X8" s="18"/>
+      <c r="Y8" s="154"/>
+      <c r="Z8" s="18"/>
+      <c r="AA8" s="154"/>
+      <c r="AB8" s="18"/>
+      <c r="AC8" s="18"/>
+      <c r="AD8" s="18"/>
+      <c r="AE8" s="18"/>
+      <c r="AF8" s="18"/>
+      <c r="AG8" s="18"/>
+      <c r="AH8" s="154"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="18"/>
+      <c r="AK8" s="18"/>
+      <c r="AL8" s="155"/>
+      <c r="AM8" s="124">
         <f t="shared" ref="AM8:AM32" si="0">COUNTIF(F8:AL8,"A")</f>
         <v>0</v>
       </c>
-      <c r="AN8" s="116"/>
-      <c r="AO8" s="36">
+      <c r="AN8" s="125"/>
+      <c r="AO8" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP8" s="37"/>
-      <c r="AQ8" s="51"/>
-      <c r="AR8" s="24"/>
-      <c r="AS8" s="24"/>
-      <c r="AT8" s="24"/>
-      <c r="AU8" s="37"/>
-      <c r="AW8" s="68"/>
-      <c r="AX8" s="69"/>
+      <c r="AP8" s="28"/>
+      <c r="AQ8" s="27"/>
+      <c r="AR8" s="22"/>
+      <c r="AS8" s="22"/>
+      <c r="AT8" s="22"/>
+      <c r="AU8" s="28"/>
+      <c r="AW8" s="59"/>
+      <c r="AX8" s="60"/>
     </row>
     <row r="9" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A9" s="61">
+      <c r="A9" s="53">
         <v>2</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="7"/>
-      <c r="AI9" s="6"/>
-      <c r="AJ9" s="6"/>
-      <c r="AK9" s="6"/>
-      <c r="AL9" s="16"/>
-      <c r="AM9" s="49">
+      <c r="B9" s="22"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="154"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="154"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="154"/>
+      <c r="X9" s="18"/>
+      <c r="Y9" s="154"/>
+      <c r="Z9" s="18"/>
+      <c r="AA9" s="154"/>
+      <c r="AB9" s="18"/>
+      <c r="AC9" s="18"/>
+      <c r="AD9" s="18"/>
+      <c r="AE9" s="18"/>
+      <c r="AF9" s="18"/>
+      <c r="AG9" s="18"/>
+      <c r="AH9" s="154"/>
+      <c r="AI9" s="18"/>
+      <c r="AJ9" s="18"/>
+      <c r="AK9" s="18"/>
+      <c r="AL9" s="155"/>
+      <c r="AM9" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN9" s="50"/>
-      <c r="AO9" s="36">
+      <c r="AN9" s="24"/>
+      <c r="AO9" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP9" s="37"/>
-      <c r="AQ9" s="51"/>
-      <c r="AR9" s="24"/>
-      <c r="AS9" s="24"/>
-      <c r="AT9" s="24"/>
-      <c r="AU9" s="37"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="27"/>
+      <c r="AR9" s="22"/>
+      <c r="AS9" s="22"/>
+      <c r="AT9" s="22"/>
+      <c r="AU9" s="28"/>
       <c r="AW9" s="3"/>
       <c r="AX9" s="3"/>
     </row>
     <row r="10" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A10" s="48">
+      <c r="A10" s="21">
         <v>3</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
-      <c r="AE10" s="6"/>
-      <c r="AF10" s="6"/>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="7"/>
-      <c r="AI10" s="6"/>
-      <c r="AJ10" s="6"/>
-      <c r="AK10" s="6"/>
-      <c r="AL10" s="16"/>
-      <c r="AM10" s="49">
+      <c r="B10" s="22"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="154"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="154"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="154"/>
+      <c r="X10" s="18"/>
+      <c r="Y10" s="154"/>
+      <c r="Z10" s="18"/>
+      <c r="AA10" s="154"/>
+      <c r="AB10" s="18"/>
+      <c r="AC10" s="18"/>
+      <c r="AD10" s="18"/>
+      <c r="AE10" s="18"/>
+      <c r="AF10" s="18"/>
+      <c r="AG10" s="18"/>
+      <c r="AH10" s="154"/>
+      <c r="AI10" s="18"/>
+      <c r="AJ10" s="18"/>
+      <c r="AK10" s="18"/>
+      <c r="AL10" s="155"/>
+      <c r="AM10" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN10" s="50"/>
-      <c r="AO10" s="36">
+      <c r="AN10" s="24"/>
+      <c r="AO10" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="37"/>
-      <c r="AQ10" s="51"/>
-      <c r="AR10" s="24"/>
-      <c r="AS10" s="24"/>
-      <c r="AT10" s="24"/>
-      <c r="AU10" s="37"/>
-      <c r="AW10" s="127"/>
-      <c r="AX10" s="128"/>
+      <c r="AP10" s="28"/>
+      <c r="AQ10" s="27"/>
+      <c r="AR10" s="22"/>
+      <c r="AS10" s="22"/>
+      <c r="AT10" s="22"/>
+      <c r="AU10" s="28"/>
+      <c r="AW10" s="126"/>
+      <c r="AX10" s="127"/>
     </row>
     <row r="11" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A11" s="48">
+      <c r="A11" s="21">
         <v>4</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="7"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="6"/>
-      <c r="AL11" s="16"/>
-      <c r="AM11" s="49">
+      <c r="B11" s="22"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="154"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="154"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="154"/>
+      <c r="X11" s="18"/>
+      <c r="Y11" s="154"/>
+      <c r="Z11" s="18"/>
+      <c r="AA11" s="154"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="18"/>
+      <c r="AF11" s="18"/>
+      <c r="AG11" s="18"/>
+      <c r="AH11" s="154"/>
+      <c r="AI11" s="18"/>
+      <c r="AJ11" s="18"/>
+      <c r="AK11" s="18"/>
+      <c r="AL11" s="155"/>
+      <c r="AM11" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN11" s="50"/>
-      <c r="AO11" s="36">
+      <c r="AN11" s="24"/>
+      <c r="AO11" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP11" s="37"/>
-      <c r="AQ11" s="51"/>
-      <c r="AR11" s="24"/>
-      <c r="AS11" s="24"/>
-      <c r="AT11" s="24"/>
-      <c r="AU11" s="37"/>
-      <c r="AW11" s="86"/>
-      <c r="AX11" s="67"/>
+      <c r="AP11" s="28"/>
+      <c r="AQ11" s="27"/>
+      <c r="AR11" s="22"/>
+      <c r="AS11" s="22"/>
+      <c r="AT11" s="22"/>
+      <c r="AU11" s="28"/>
+      <c r="AW11" s="95"/>
+      <c r="AX11" s="58"/>
     </row>
     <row r="12" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A12" s="48">
+      <c r="A12" s="21">
         <v>5</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="6"/>
-      <c r="AC12" s="6"/>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="7"/>
-      <c r="AI12" s="6"/>
-      <c r="AJ12" s="6"/>
-      <c r="AK12" s="6"/>
-      <c r="AL12" s="16"/>
-      <c r="AM12" s="49">
+      <c r="B12" s="22"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="154"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="154"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="154"/>
+      <c r="X12" s="18"/>
+      <c r="Y12" s="154"/>
+      <c r="Z12" s="18"/>
+      <c r="AA12" s="154"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="18"/>
+      <c r="AE12" s="18"/>
+      <c r="AF12" s="18"/>
+      <c r="AG12" s="18"/>
+      <c r="AH12" s="154"/>
+      <c r="AI12" s="18"/>
+      <c r="AJ12" s="18"/>
+      <c r="AK12" s="18"/>
+      <c r="AL12" s="155"/>
+      <c r="AM12" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="50"/>
-      <c r="AO12" s="36">
+      <c r="AN12" s="24"/>
+      <c r="AO12" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP12" s="37"/>
-      <c r="AQ12" s="51"/>
-      <c r="AR12" s="24"/>
-      <c r="AS12" s="24"/>
-      <c r="AT12" s="24"/>
-      <c r="AU12" s="37"/>
-      <c r="AW12" s="86"/>
-      <c r="AX12" s="67"/>
+      <c r="AP12" s="28"/>
+      <c r="AQ12" s="27"/>
+      <c r="AR12" s="22"/>
+      <c r="AS12" s="22"/>
+      <c r="AT12" s="22"/>
+      <c r="AU12" s="28"/>
+      <c r="AW12" s="95"/>
+      <c r="AX12" s="58"/>
     </row>
     <row r="13" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A13" s="48">
+      <c r="A13" s="21">
         <v>6</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="6"/>
-      <c r="AC13" s="6"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="7"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="16"/>
-      <c r="AM13" s="49">
+      <c r="B13" s="22"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="154"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="154"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="154"/>
+      <c r="X13" s="18"/>
+      <c r="Y13" s="154"/>
+      <c r="Z13" s="18"/>
+      <c r="AA13" s="154"/>
+      <c r="AB13" s="18"/>
+      <c r="AC13" s="18"/>
+      <c r="AD13" s="18"/>
+      <c r="AE13" s="18"/>
+      <c r="AF13" s="18"/>
+      <c r="AG13" s="18"/>
+      <c r="AH13" s="154"/>
+      <c r="AI13" s="18"/>
+      <c r="AJ13" s="18"/>
+      <c r="AK13" s="18"/>
+      <c r="AL13" s="155"/>
+      <c r="AM13" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN13" s="50"/>
-      <c r="AO13" s="36">
+      <c r="AN13" s="24"/>
+      <c r="AO13" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP13" s="37"/>
-      <c r="AQ13" s="51"/>
-      <c r="AR13" s="24"/>
-      <c r="AS13" s="24"/>
-      <c r="AT13" s="24"/>
-      <c r="AU13" s="37"/>
-      <c r="AW13" s="86"/>
-      <c r="AX13" s="67"/>
+      <c r="AP13" s="28"/>
+      <c r="AQ13" s="27"/>
+      <c r="AR13" s="22"/>
+      <c r="AS13" s="22"/>
+      <c r="AT13" s="22"/>
+      <c r="AU13" s="28"/>
+      <c r="AW13" s="95"/>
+      <c r="AX13" s="58"/>
     </row>
     <row r="14" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A14" s="48">
+      <c r="A14" s="21">
         <v>7</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="6"/>
-      <c r="AC14" s="6"/>
-      <c r="AD14" s="6"/>
-      <c r="AE14" s="6"/>
-      <c r="AF14" s="6"/>
-      <c r="AG14" s="6"/>
-      <c r="AH14" s="7"/>
-      <c r="AI14" s="6"/>
-      <c r="AJ14" s="6"/>
-      <c r="AK14" s="6"/>
-      <c r="AL14" s="16"/>
-      <c r="AM14" s="49">
+      <c r="B14" s="22"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="154"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="154"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="18"/>
+      <c r="W14" s="154"/>
+      <c r="X14" s="18"/>
+      <c r="Y14" s="154"/>
+      <c r="Z14" s="18"/>
+      <c r="AA14" s="154"/>
+      <c r="AB14" s="18"/>
+      <c r="AC14" s="18"/>
+      <c r="AD14" s="18"/>
+      <c r="AE14" s="18"/>
+      <c r="AF14" s="18"/>
+      <c r="AG14" s="18"/>
+      <c r="AH14" s="154"/>
+      <c r="AI14" s="18"/>
+      <c r="AJ14" s="18"/>
+      <c r="AK14" s="18"/>
+      <c r="AL14" s="155"/>
+      <c r="AM14" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="50"/>
-      <c r="AO14" s="36">
+      <c r="AN14" s="24"/>
+      <c r="AO14" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP14" s="37"/>
-      <c r="AQ14" s="51"/>
-      <c r="AR14" s="24"/>
-      <c r="AS14" s="24"/>
-      <c r="AT14" s="24"/>
-      <c r="AU14" s="37"/>
-      <c r="AW14" s="86"/>
-      <c r="AX14" s="67"/>
+      <c r="AP14" s="28"/>
+      <c r="AQ14" s="27"/>
+      <c r="AR14" s="22"/>
+      <c r="AS14" s="22"/>
+      <c r="AT14" s="22"/>
+      <c r="AU14" s="28"/>
+      <c r="AW14" s="95"/>
+      <c r="AX14" s="58"/>
     </row>
     <row r="15" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A15" s="48">
+      <c r="A15" s="21">
         <v>8</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="6"/>
-      <c r="AC15" s="6"/>
-      <c r="AD15" s="6"/>
-      <c r="AE15" s="6"/>
-      <c r="AF15" s="6"/>
-      <c r="AG15" s="6"/>
-      <c r="AH15" s="7"/>
-      <c r="AI15" s="6"/>
-      <c r="AJ15" s="6"/>
-      <c r="AK15" s="6"/>
-      <c r="AL15" s="16"/>
-      <c r="AM15" s="49">
+      <c r="B15" s="22"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="154"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="154"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="154"/>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="154"/>
+      <c r="Z15" s="18"/>
+      <c r="AA15" s="154"/>
+      <c r="AB15" s="18"/>
+      <c r="AC15" s="18"/>
+      <c r="AD15" s="18"/>
+      <c r="AE15" s="18"/>
+      <c r="AF15" s="18"/>
+      <c r="AG15" s="18"/>
+      <c r="AH15" s="154"/>
+      <c r="AI15" s="18"/>
+      <c r="AJ15" s="18"/>
+      <c r="AK15" s="18"/>
+      <c r="AL15" s="155"/>
+      <c r="AM15" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN15" s="50"/>
-      <c r="AO15" s="36">
+      <c r="AN15" s="24"/>
+      <c r="AO15" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP15" s="37"/>
-      <c r="AQ15" s="51"/>
-      <c r="AR15" s="24"/>
-      <c r="AS15" s="24"/>
-      <c r="AT15" s="24"/>
-      <c r="AU15" s="37"/>
-      <c r="AW15" s="68"/>
-      <c r="AX15" s="69"/>
+      <c r="AP15" s="28"/>
+      <c r="AQ15" s="27"/>
+      <c r="AR15" s="22"/>
+      <c r="AS15" s="22"/>
+      <c r="AT15" s="22"/>
+      <c r="AU15" s="28"/>
+      <c r="AW15" s="59"/>
+      <c r="AX15" s="60"/>
     </row>
     <row r="16" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A16" s="48">
+      <c r="A16" s="21">
         <v>9</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="6"/>
-      <c r="AC16" s="6"/>
-      <c r="AD16" s="6"/>
-      <c r="AE16" s="6"/>
-      <c r="AF16" s="6"/>
-      <c r="AG16" s="6"/>
-      <c r="AH16" s="7"/>
-      <c r="AI16" s="6"/>
-      <c r="AJ16" s="6"/>
-      <c r="AK16" s="6"/>
-      <c r="AL16" s="16"/>
-      <c r="AM16" s="49">
+      <c r="B16" s="22"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="154"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="154"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="154"/>
+      <c r="X16" s="18"/>
+      <c r="Y16" s="154"/>
+      <c r="Z16" s="18"/>
+      <c r="AA16" s="154"/>
+      <c r="AB16" s="18"/>
+      <c r="AC16" s="18"/>
+      <c r="AD16" s="18"/>
+      <c r="AE16" s="18"/>
+      <c r="AF16" s="18"/>
+      <c r="AG16" s="18"/>
+      <c r="AH16" s="154"/>
+      <c r="AI16" s="18"/>
+      <c r="AJ16" s="18"/>
+      <c r="AK16" s="18"/>
+      <c r="AL16" s="155"/>
+      <c r="AM16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN16" s="50"/>
-      <c r="AO16" s="36">
+      <c r="AN16" s="24"/>
+      <c r="AO16" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP16" s="37"/>
-      <c r="AQ16" s="51"/>
-      <c r="AR16" s="24"/>
-      <c r="AS16" s="24"/>
-      <c r="AT16" s="24"/>
-      <c r="AU16" s="37"/>
+      <c r="AP16" s="28"/>
+      <c r="AQ16" s="27"/>
+      <c r="AR16" s="22"/>
+      <c r="AS16" s="22"/>
+      <c r="AT16" s="22"/>
+      <c r="AU16" s="28"/>
     </row>
     <row r="17" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A17" s="48">
+      <c r="A17" s="21">
         <v>10</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
-      <c r="V17" s="6"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="6"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="6"/>
-      <c r="AC17" s="6"/>
-      <c r="AD17" s="6"/>
-      <c r="AE17" s="6"/>
-      <c r="AF17" s="6"/>
-      <c r="AG17" s="6"/>
-      <c r="AH17" s="7"/>
-      <c r="AI17" s="6"/>
-      <c r="AJ17" s="6"/>
-      <c r="AK17" s="6"/>
-      <c r="AL17" s="16"/>
-      <c r="AM17" s="49">
+      <c r="B17" s="22"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="154"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="154"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="154"/>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="154"/>
+      <c r="Z17" s="18"/>
+      <c r="AA17" s="154"/>
+      <c r="AB17" s="18"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="18"/>
+      <c r="AE17" s="18"/>
+      <c r="AF17" s="18"/>
+      <c r="AG17" s="18"/>
+      <c r="AH17" s="154"/>
+      <c r="AI17" s="18"/>
+      <c r="AJ17" s="18"/>
+      <c r="AK17" s="18"/>
+      <c r="AL17" s="155"/>
+      <c r="AM17" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN17" s="50"/>
-      <c r="AO17" s="36">
+      <c r="AN17" s="24"/>
+      <c r="AO17" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP17" s="37"/>
-      <c r="AQ17" s="51"/>
-      <c r="AR17" s="24"/>
-      <c r="AS17" s="24"/>
-      <c r="AT17" s="24"/>
-      <c r="AU17" s="37"/>
-      <c r="AW17" s="127" t="s">
+      <c r="AP17" s="28"/>
+      <c r="AQ17" s="27"/>
+      <c r="AR17" s="22"/>
+      <c r="AS17" s="22"/>
+      <c r="AT17" s="22"/>
+      <c r="AU17" s="28"/>
+      <c r="AW17" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="AX17" s="128"/>
+      <c r="AX17" s="127"/>
     </row>
     <row r="18" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A18" s="48">
+      <c r="A18" s="21">
         <v>11</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="6"/>
-      <c r="AC18" s="6"/>
-      <c r="AD18" s="6"/>
-      <c r="AE18" s="6"/>
-      <c r="AF18" s="6"/>
-      <c r="AG18" s="6"/>
-      <c r="AH18" s="7"/>
-      <c r="AI18" s="6"/>
-      <c r="AJ18" s="6"/>
-      <c r="AK18" s="6"/>
-      <c r="AL18" s="16"/>
-      <c r="AM18" s="49">
+      <c r="B18" s="22"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="154"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="154"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="18"/>
+      <c r="V18" s="18"/>
+      <c r="W18" s="154"/>
+      <c r="X18" s="18"/>
+      <c r="Y18" s="154"/>
+      <c r="Z18" s="18"/>
+      <c r="AA18" s="154"/>
+      <c r="AB18" s="18"/>
+      <c r="AC18" s="18"/>
+      <c r="AD18" s="18"/>
+      <c r="AE18" s="18"/>
+      <c r="AF18" s="18"/>
+      <c r="AG18" s="18"/>
+      <c r="AH18" s="154"/>
+      <c r="AI18" s="18"/>
+      <c r="AJ18" s="18"/>
+      <c r="AK18" s="18"/>
+      <c r="AL18" s="155"/>
+      <c r="AM18" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN18" s="50"/>
-      <c r="AO18" s="36">
+      <c r="AN18" s="24"/>
+      <c r="AO18" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP18" s="37"/>
-      <c r="AQ18" s="51"/>
-      <c r="AR18" s="24"/>
-      <c r="AS18" s="24"/>
-      <c r="AT18" s="24"/>
-      <c r="AU18" s="37"/>
-      <c r="AW18" s="86"/>
-      <c r="AX18" s="67"/>
+      <c r="AP18" s="28"/>
+      <c r="AQ18" s="27"/>
+      <c r="AR18" s="22"/>
+      <c r="AS18" s="22"/>
+      <c r="AT18" s="22"/>
+      <c r="AU18" s="28"/>
+      <c r="AW18" s="95"/>
+      <c r="AX18" s="58"/>
     </row>
     <row r="19" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A19" s="48">
+      <c r="A19" s="21">
         <v>12</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="6"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="6"/>
-      <c r="AD19" s="6"/>
-      <c r="AE19" s="6"/>
-      <c r="AF19" s="6"/>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="7"/>
-      <c r="AI19" s="6"/>
-      <c r="AJ19" s="6"/>
-      <c r="AK19" s="6"/>
-      <c r="AL19" s="16"/>
-      <c r="AM19" s="49">
+      <c r="B19" s="22"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="154"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="154"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="154"/>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="154"/>
+      <c r="Z19" s="18"/>
+      <c r="AA19" s="154"/>
+      <c r="AB19" s="18"/>
+      <c r="AC19" s="18"/>
+      <c r="AD19" s="18"/>
+      <c r="AE19" s="18"/>
+      <c r="AF19" s="18"/>
+      <c r="AG19" s="18"/>
+      <c r="AH19" s="154"/>
+      <c r="AI19" s="18"/>
+      <c r="AJ19" s="18"/>
+      <c r="AK19" s="18"/>
+      <c r="AL19" s="155"/>
+      <c r="AM19" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="50"/>
-      <c r="AO19" s="36">
+      <c r="AN19" s="24"/>
+      <c r="AO19" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP19" s="37"/>
-      <c r="AQ19" s="51"/>
-      <c r="AR19" s="24"/>
-      <c r="AS19" s="24"/>
-      <c r="AT19" s="24"/>
-      <c r="AU19" s="37"/>
-      <c r="AW19" s="86"/>
-      <c r="AX19" s="67"/>
+      <c r="AP19" s="28"/>
+      <c r="AQ19" s="27"/>
+      <c r="AR19" s="22"/>
+      <c r="AS19" s="22"/>
+      <c r="AT19" s="22"/>
+      <c r="AU19" s="28"/>
+      <c r="AW19" s="95"/>
+      <c r="AX19" s="58"/>
     </row>
     <row r="20" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A20" s="48">
+      <c r="A20" s="21">
         <v>13</v>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="6"/>
-      <c r="AC20" s="6"/>
-      <c r="AD20" s="6"/>
-      <c r="AE20" s="6"/>
-      <c r="AF20" s="6"/>
-      <c r="AG20" s="6"/>
-      <c r="AH20" s="7"/>
-      <c r="AI20" s="6"/>
-      <c r="AJ20" s="6"/>
-      <c r="AK20" s="6"/>
-      <c r="AL20" s="16"/>
-      <c r="AM20" s="49">
+      <c r="B20" s="22"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="154"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="154"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="154"/>
+      <c r="X20" s="18"/>
+      <c r="Y20" s="154"/>
+      <c r="Z20" s="18"/>
+      <c r="AA20" s="154"/>
+      <c r="AB20" s="18"/>
+      <c r="AC20" s="18"/>
+      <c r="AD20" s="18"/>
+      <c r="AE20" s="18"/>
+      <c r="AF20" s="18"/>
+      <c r="AG20" s="18"/>
+      <c r="AH20" s="154"/>
+      <c r="AI20" s="18"/>
+      <c r="AJ20" s="18"/>
+      <c r="AK20" s="18"/>
+      <c r="AL20" s="155"/>
+      <c r="AM20" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN20" s="50"/>
-      <c r="AO20" s="36">
+      <c r="AN20" s="24"/>
+      <c r="AO20" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP20" s="37"/>
-      <c r="AQ20" s="51"/>
-      <c r="AR20" s="24"/>
-      <c r="AS20" s="24"/>
-      <c r="AT20" s="24"/>
-      <c r="AU20" s="37"/>
-      <c r="AW20" s="86"/>
-      <c r="AX20" s="67"/>
+      <c r="AP20" s="28"/>
+      <c r="AQ20" s="27"/>
+      <c r="AR20" s="22"/>
+      <c r="AS20" s="22"/>
+      <c r="AT20" s="22"/>
+      <c r="AU20" s="28"/>
+      <c r="AW20" s="95"/>
+      <c r="AX20" s="58"/>
     </row>
     <row r="21" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A21" s="48">
+      <c r="A21" s="21">
         <v>14</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="6"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="6"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="6"/>
-      <c r="AD21" s="6"/>
-      <c r="AE21" s="6"/>
-      <c r="AF21" s="6"/>
-      <c r="AG21" s="6"/>
-      <c r="AH21" s="7"/>
-      <c r="AI21" s="6"/>
-      <c r="AJ21" s="6"/>
-      <c r="AK21" s="6"/>
-      <c r="AL21" s="16"/>
-      <c r="AM21" s="49">
+      <c r="B21" s="22"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="154"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="154"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="154"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="154"/>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="154"/>
+      <c r="AB21" s="18"/>
+      <c r="AC21" s="18"/>
+      <c r="AD21" s="18"/>
+      <c r="AE21" s="18"/>
+      <c r="AF21" s="18"/>
+      <c r="AG21" s="18"/>
+      <c r="AH21" s="154"/>
+      <c r="AI21" s="18"/>
+      <c r="AJ21" s="18"/>
+      <c r="AK21" s="18"/>
+      <c r="AL21" s="155"/>
+      <c r="AM21" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="50"/>
-      <c r="AO21" s="36">
+      <c r="AN21" s="24"/>
+      <c r="AO21" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP21" s="37"/>
-      <c r="AQ21" s="51"/>
-      <c r="AR21" s="24"/>
-      <c r="AS21" s="24"/>
-      <c r="AT21" s="24"/>
-      <c r="AU21" s="37"/>
-      <c r="AW21" s="86"/>
-      <c r="AX21" s="67"/>
+      <c r="AP21" s="28"/>
+      <c r="AQ21" s="27"/>
+      <c r="AR21" s="22"/>
+      <c r="AS21" s="22"/>
+      <c r="AT21" s="22"/>
+      <c r="AU21" s="28"/>
+      <c r="AW21" s="95"/>
+      <c r="AX21" s="58"/>
     </row>
     <row r="22" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A22" s="48">
+      <c r="A22" s="21">
         <v>15</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="6"/>
-      <c r="AC22" s="6"/>
-      <c r="AD22" s="6"/>
-      <c r="AE22" s="6"/>
-      <c r="AF22" s="6"/>
-      <c r="AG22" s="6"/>
-      <c r="AH22" s="7"/>
-      <c r="AI22" s="6"/>
-      <c r="AJ22" s="6"/>
-      <c r="AK22" s="6"/>
-      <c r="AL22" s="16"/>
-      <c r="AM22" s="49">
+      <c r="B22" s="22"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="154"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="154"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="154"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="154"/>
+      <c r="Z22" s="18"/>
+      <c r="AA22" s="154"/>
+      <c r="AB22" s="18"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="18"/>
+      <c r="AE22" s="18"/>
+      <c r="AF22" s="18"/>
+      <c r="AG22" s="18"/>
+      <c r="AH22" s="154"/>
+      <c r="AI22" s="18"/>
+      <c r="AJ22" s="18"/>
+      <c r="AK22" s="18"/>
+      <c r="AL22" s="155"/>
+      <c r="AM22" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN22" s="50"/>
-      <c r="AO22" s="36">
+      <c r="AN22" s="24"/>
+      <c r="AO22" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP22" s="37"/>
-      <c r="AQ22" s="51"/>
-      <c r="AR22" s="24"/>
-      <c r="AS22" s="24"/>
-      <c r="AT22" s="24"/>
-      <c r="AU22" s="37"/>
-      <c r="AW22" s="86"/>
-      <c r="AX22" s="67"/>
+      <c r="AP22" s="28"/>
+      <c r="AQ22" s="27"/>
+      <c r="AR22" s="22"/>
+      <c r="AS22" s="22"/>
+      <c r="AT22" s="22"/>
+      <c r="AU22" s="28"/>
+      <c r="AW22" s="95"/>
+      <c r="AX22" s="58"/>
     </row>
     <row r="23" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A23" s="28">
+      <c r="A23" s="74">
         <v>16</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="6"/>
-      <c r="AC23" s="6"/>
-      <c r="AD23" s="6"/>
-      <c r="AE23" s="6"/>
-      <c r="AF23" s="6"/>
-      <c r="AG23" s="6"/>
-      <c r="AH23" s="7"/>
-      <c r="AI23" s="6"/>
-      <c r="AJ23" s="6"/>
-      <c r="AK23" s="6"/>
-      <c r="AL23" s="16"/>
-      <c r="AM23" s="49">
+      <c r="B23" s="75"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="154"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="154"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="154"/>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="154"/>
+      <c r="Z23" s="18"/>
+      <c r="AA23" s="154"/>
+      <c r="AB23" s="18"/>
+      <c r="AC23" s="18"/>
+      <c r="AD23" s="18"/>
+      <c r="AE23" s="18"/>
+      <c r="AF23" s="18"/>
+      <c r="AG23" s="18"/>
+      <c r="AH23" s="154"/>
+      <c r="AI23" s="18"/>
+      <c r="AJ23" s="18"/>
+      <c r="AK23" s="18"/>
+      <c r="AL23" s="155"/>
+      <c r="AM23" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="50"/>
-      <c r="AO23" s="36">
+      <c r="AN23" s="24"/>
+      <c r="AO23" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP23" s="37"/>
-      <c r="AQ23" s="85"/>
-      <c r="AR23" s="24"/>
-      <c r="AS23" s="24"/>
-      <c r="AT23" s="24"/>
-      <c r="AU23" s="37"/>
-      <c r="AW23" s="68"/>
-      <c r="AX23" s="69"/>
+      <c r="AP23" s="28"/>
+      <c r="AQ23" s="105"/>
+      <c r="AR23" s="22"/>
+      <c r="AS23" s="22"/>
+      <c r="AT23" s="22"/>
+      <c r="AU23" s="28"/>
+      <c r="AW23" s="59"/>
+      <c r="AX23" s="60"/>
     </row>
     <row r="24" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A24" s="125">
+      <c r="A24" s="128">
         <v>17</v>
       </c>
-      <c r="B24" s="126"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="7"/>
-      <c r="AB24" s="6"/>
-      <c r="AC24" s="6"/>
-      <c r="AD24" s="6"/>
-      <c r="AE24" s="6"/>
-      <c r="AF24" s="6"/>
-      <c r="AG24" s="6"/>
-      <c r="AH24" s="7"/>
-      <c r="AI24" s="6"/>
-      <c r="AJ24" s="6"/>
-      <c r="AK24" s="6"/>
-      <c r="AL24" s="16"/>
-      <c r="AM24" s="49">
+      <c r="B24" s="129"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="154"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="154"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="154"/>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="154"/>
+      <c r="Z24" s="18"/>
+      <c r="AA24" s="154"/>
+      <c r="AB24" s="18"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="18"/>
+      <c r="AE24" s="18"/>
+      <c r="AF24" s="18"/>
+      <c r="AG24" s="18"/>
+      <c r="AH24" s="154"/>
+      <c r="AI24" s="18"/>
+      <c r="AJ24" s="18"/>
+      <c r="AK24" s="18"/>
+      <c r="AL24" s="155"/>
+      <c r="AM24" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN24" s="50"/>
-      <c r="AO24" s="36">
+      <c r="AN24" s="24"/>
+      <c r="AO24" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP24" s="37"/>
-      <c r="AQ24" s="51"/>
-      <c r="AR24" s="24"/>
-      <c r="AS24" s="24"/>
-      <c r="AT24" s="24"/>
-      <c r="AU24" s="37"/>
+      <c r="AP24" s="28"/>
+      <c r="AQ24" s="27"/>
+      <c r="AR24" s="22"/>
+      <c r="AS24" s="22"/>
+      <c r="AT24" s="22"/>
+      <c r="AU24" s="28"/>
     </row>
     <row r="25" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A25" s="28">
+      <c r="A25" s="74">
         <v>18</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="6"/>
-      <c r="AC25" s="6"/>
-      <c r="AD25" s="6"/>
-      <c r="AE25" s="6"/>
-      <c r="AF25" s="6"/>
-      <c r="AG25" s="6"/>
-      <c r="AH25" s="7"/>
-      <c r="AI25" s="6"/>
-      <c r="AJ25" s="6"/>
-      <c r="AK25" s="6"/>
-      <c r="AL25" s="16"/>
-      <c r="AM25" s="49">
+      <c r="B25" s="75"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="154"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="154"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="154"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="154"/>
+      <c r="Z25" s="18"/>
+      <c r="AA25" s="154"/>
+      <c r="AB25" s="18"/>
+      <c r="AC25" s="18"/>
+      <c r="AD25" s="18"/>
+      <c r="AE25" s="18"/>
+      <c r="AF25" s="18"/>
+      <c r="AG25" s="18"/>
+      <c r="AH25" s="154"/>
+      <c r="AI25" s="18"/>
+      <c r="AJ25" s="18"/>
+      <c r="AK25" s="18"/>
+      <c r="AL25" s="155"/>
+      <c r="AM25" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="50"/>
-      <c r="AO25" s="36">
+      <c r="AN25" s="24"/>
+      <c r="AO25" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP25" s="37"/>
-      <c r="AQ25" s="51"/>
-      <c r="AR25" s="24"/>
-      <c r="AS25" s="24"/>
-      <c r="AT25" s="24"/>
-      <c r="AU25" s="37"/>
+      <c r="AP25" s="28"/>
+      <c r="AQ25" s="27"/>
+      <c r="AR25" s="22"/>
+      <c r="AS25" s="22"/>
+      <c r="AT25" s="22"/>
+      <c r="AU25" s="28"/>
     </row>
     <row r="26" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A26" s="125">
+      <c r="A26" s="128">
         <v>19</v>
       </c>
-      <c r="B26" s="126"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="7"/>
-      <c r="AB26" s="6"/>
-      <c r="AC26" s="6"/>
-      <c r="AD26" s="6"/>
-      <c r="AE26" s="6"/>
-      <c r="AF26" s="6"/>
-      <c r="AG26" s="6"/>
-      <c r="AH26" s="6"/>
-      <c r="AI26" s="6"/>
-      <c r="AJ26" s="6"/>
-      <c r="AK26" s="6"/>
-      <c r="AL26" s="16"/>
-      <c r="AM26" s="49">
+      <c r="B26" s="129"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="154"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="154"/>
+      <c r="X26" s="18"/>
+      <c r="Y26" s="154"/>
+      <c r="Z26" s="18"/>
+      <c r="AA26" s="154"/>
+      <c r="AB26" s="18"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="18"/>
+      <c r="AE26" s="18"/>
+      <c r="AF26" s="18"/>
+      <c r="AG26" s="18"/>
+      <c r="AH26" s="18"/>
+      <c r="AI26" s="18"/>
+      <c r="AJ26" s="18"/>
+      <c r="AK26" s="18"/>
+      <c r="AL26" s="155"/>
+      <c r="AM26" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN26" s="50"/>
-      <c r="AO26" s="36">
+      <c r="AN26" s="24"/>
+      <c r="AO26" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP26" s="37"/>
-      <c r="AQ26" s="64"/>
-      <c r="AR26" s="24"/>
-      <c r="AS26" s="24"/>
-      <c r="AT26" s="24"/>
+      <c r="AP26" s="28"/>
+      <c r="AQ26" s="34"/>
+      <c r="AR26" s="22"/>
+      <c r="AS26" s="22"/>
+      <c r="AT26" s="22"/>
       <c r="AU26" s="5"/>
     </row>
     <row r="27" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A27" s="48">
+      <c r="A27" s="21">
         <v>20</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="7"/>
-      <c r="X27" s="6"/>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="7"/>
-      <c r="AB27" s="6"/>
-      <c r="AC27" s="6"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="6"/>
-      <c r="AL27" s="16"/>
-      <c r="AM27" s="49">
+      <c r="B27" s="22"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="154"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="154"/>
+      <c r="X27" s="18"/>
+      <c r="Y27" s="154"/>
+      <c r="Z27" s="18"/>
+      <c r="AA27" s="154"/>
+      <c r="AB27" s="18"/>
+      <c r="AC27" s="18"/>
+      <c r="AD27" s="18"/>
+      <c r="AE27" s="18"/>
+      <c r="AF27" s="18"/>
+      <c r="AG27" s="18"/>
+      <c r="AH27" s="18"/>
+      <c r="AI27" s="18"/>
+      <c r="AJ27" s="18"/>
+      <c r="AK27" s="18"/>
+      <c r="AL27" s="155"/>
+      <c r="AM27" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN27" s="50"/>
-      <c r="AO27" s="36">
+      <c r="AN27" s="24"/>
+      <c r="AO27" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP27" s="37"/>
-      <c r="AQ27" s="64"/>
-      <c r="AR27" s="24"/>
-      <c r="AS27" s="24"/>
-      <c r="AT27" s="24"/>
+      <c r="AP27" s="28"/>
+      <c r="AQ27" s="34"/>
+      <c r="AR27" s="22"/>
+      <c r="AS27" s="22"/>
+      <c r="AT27" s="22"/>
       <c r="AU27" s="5"/>
     </row>
     <row r="28" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A28" s="48">
+      <c r="A28" s="21">
         <v>21</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="7"/>
-      <c r="X28" s="6"/>
-      <c r="Y28" s="7"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="7"/>
-      <c r="AB28" s="6"/>
-      <c r="AC28" s="6"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="7"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="16"/>
-      <c r="AM28" s="49">
+      <c r="B28" s="22"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="154"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="154"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="154"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="154"/>
+      <c r="Z28" s="18"/>
+      <c r="AA28" s="154"/>
+      <c r="AB28" s="18"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="18"/>
+      <c r="AE28" s="18"/>
+      <c r="AF28" s="18"/>
+      <c r="AG28" s="18"/>
+      <c r="AH28" s="154"/>
+      <c r="AI28" s="18"/>
+      <c r="AJ28" s="18"/>
+      <c r="AK28" s="18"/>
+      <c r="AL28" s="155"/>
+      <c r="AM28" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN28" s="50"/>
-      <c r="AO28" s="36">
+      <c r="AN28" s="24"/>
+      <c r="AO28" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP28" s="37"/>
-      <c r="AQ28" s="51"/>
-      <c r="AR28" s="24"/>
-      <c r="AS28" s="24"/>
-      <c r="AT28" s="24"/>
-      <c r="AU28" s="37"/>
+      <c r="AP28" s="28"/>
+      <c r="AQ28" s="27"/>
+      <c r="AR28" s="22"/>
+      <c r="AS28" s="22"/>
+      <c r="AT28" s="22"/>
+      <c r="AU28" s="28"/>
     </row>
     <row r="29" spans="1:50" ht="19.5" customHeight="1">
-      <c r="A29" s="48">
+      <c r="A29" s="21">
         <v>22</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="7"/>
-      <c r="Z29" s="6"/>
-      <c r="AA29" s="7"/>
-      <c r="AB29" s="6"/>
-      <c r="AC29" s="6"/>
-      <c r="AD29" s="6"/>
-      <c r="AE29" s="6"/>
-      <c r="AF29" s="6"/>
-      <c r="AG29" s="6"/>
-      <c r="AH29" s="7"/>
-      <c r="AI29" s="6"/>
-      <c r="AJ29" s="6"/>
-      <c r="AK29" s="6"/>
-      <c r="AL29" s="16"/>
-      <c r="AM29" s="49">
+      <c r="B29" s="22"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="154"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="154"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="154"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="154"/>
+      <c r="Z29" s="18"/>
+      <c r="AA29" s="154"/>
+      <c r="AB29" s="18"/>
+      <c r="AC29" s="18"/>
+      <c r="AD29" s="18"/>
+      <c r="AE29" s="18"/>
+      <c r="AF29" s="18"/>
+      <c r="AG29" s="18"/>
+      <c r="AH29" s="154"/>
+      <c r="AI29" s="18"/>
+      <c r="AJ29" s="18"/>
+      <c r="AK29" s="18"/>
+      <c r="AL29" s="155"/>
+      <c r="AM29" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN29" s="50"/>
-      <c r="AO29" s="36">
+      <c r="AN29" s="24"/>
+      <c r="AO29" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP29" s="37"/>
-      <c r="AQ29" s="51"/>
-      <c r="AR29" s="24"/>
-      <c r="AS29" s="24"/>
-      <c r="AT29" s="24"/>
-      <c r="AU29" s="37"/>
+      <c r="AP29" s="28"/>
+      <c r="AQ29" s="27"/>
+      <c r="AR29" s="22"/>
+      <c r="AS29" s="22"/>
+      <c r="AT29" s="22"/>
+      <c r="AU29" s="28"/>
     </row>
     <row r="30" spans="1:50" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="48">
+      <c r="A30" s="21">
         <v>23</v>
       </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="6"/>
-      <c r="Y30" s="7"/>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="7"/>
-      <c r="AB30" s="6"/>
-      <c r="AC30" s="6"/>
-      <c r="AD30" s="6"/>
-      <c r="AE30" s="6"/>
-      <c r="AF30" s="6"/>
-      <c r="AG30" s="6"/>
-      <c r="AH30" s="6"/>
-      <c r="AI30" s="6"/>
-      <c r="AJ30" s="6"/>
-      <c r="AK30" s="6"/>
-      <c r="AL30" s="16"/>
-      <c r="AM30" s="49">
+      <c r="B30" s="22"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="154"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="18"/>
+      <c r="W30" s="154"/>
+      <c r="X30" s="18"/>
+      <c r="Y30" s="154"/>
+      <c r="Z30" s="18"/>
+      <c r="AA30" s="154"/>
+      <c r="AB30" s="18"/>
+      <c r="AC30" s="18"/>
+      <c r="AD30" s="18"/>
+      <c r="AE30" s="18"/>
+      <c r="AF30" s="18"/>
+      <c r="AG30" s="18"/>
+      <c r="AH30" s="18"/>
+      <c r="AI30" s="18"/>
+      <c r="AJ30" s="18"/>
+      <c r="AK30" s="18"/>
+      <c r="AL30" s="155"/>
+      <c r="AM30" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN30" s="50"/>
-      <c r="AO30" s="36">
+      <c r="AN30" s="24"/>
+      <c r="AO30" s="33">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP30" s="37"/>
-      <c r="AQ30" s="64"/>
-      <c r="AR30" s="24"/>
-      <c r="AS30" s="24"/>
-      <c r="AT30" s="24"/>
+      <c r="AP30" s="28"/>
+      <c r="AQ30" s="34"/>
+      <c r="AR30" s="22"/>
+      <c r="AS30" s="22"/>
+      <c r="AT30" s="22"/>
       <c r="AU30" s="5"/>
     </row>
     <row r="31" spans="1:50" ht="19.5" hidden="1" customHeight="1" thickBot="1">
-      <c r="A31" s="48">
+      <c r="A31" s="21">
         <v>24</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="6"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="6"/>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="7"/>
-      <c r="Z31" s="6"/>
-      <c r="AA31" s="7"/>
-      <c r="AB31" s="6"/>
-      <c r="AC31" s="6"/>
-      <c r="AD31" s="6"/>
-      <c r="AE31" s="6"/>
-      <c r="AF31" s="6"/>
-      <c r="AG31" s="6"/>
-      <c r="AH31" s="6"/>
-      <c r="AI31" s="6"/>
-      <c r="AJ31" s="6"/>
-      <c r="AK31" s="6"/>
-      <c r="AL31" s="16"/>
-      <c r="AM31" s="49">
+      <c r="B31" s="22"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="154"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
+      <c r="W31" s="154"/>
+      <c r="X31" s="18"/>
+      <c r="Y31" s="154"/>
+      <c r="Z31" s="18"/>
+      <c r="AA31" s="154"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="18"/>
+      <c r="AD31" s="18"/>
+      <c r="AE31" s="18"/>
+      <c r="AF31" s="18"/>
+      <c r="AG31" s="18"/>
+      <c r="AH31" s="18"/>
+      <c r="AI31" s="18"/>
+      <c r="AJ31" s="18"/>
+      <c r="AK31" s="18"/>
+      <c r="AL31" s="155"/>
+      <c r="AM31" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN31" s="50"/>
-      <c r="AO31" s="36">
+      <c r="AN31" s="24"/>
+      <c r="AO31" s="33">
         <f>AW4-AM31</f>
         <v>0</v>
       </c>
-      <c r="AP31" s="37"/>
-      <c r="AQ31" s="64"/>
-      <c r="AR31" s="24"/>
-      <c r="AS31" s="24"/>
-      <c r="AT31" s="24"/>
+      <c r="AP31" s="28"/>
+      <c r="AQ31" s="34"/>
+      <c r="AR31" s="22"/>
+      <c r="AS31" s="22"/>
+      <c r="AT31" s="22"/>
       <c r="AU31" s="5"/>
     </row>
     <row r="32" spans="1:50" ht="19.5" hidden="1" customHeight="1" thickBot="1">
-      <c r="A32" s="114"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="6"/>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="6"/>
-      <c r="AA32" s="7"/>
-      <c r="AB32" s="6"/>
-      <c r="AC32" s="6"/>
-      <c r="AD32" s="6"/>
-      <c r="AE32" s="6"/>
-      <c r="AF32" s="6"/>
-      <c r="AG32" s="6"/>
-      <c r="AH32" s="6"/>
-      <c r="AI32" s="6"/>
-      <c r="AJ32" s="6"/>
-      <c r="AK32" s="6"/>
-      <c r="AL32" s="16"/>
-      <c r="AM32" s="49">
+      <c r="A32" s="123"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="18"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="154"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="154"/>
+      <c r="X32" s="18"/>
+      <c r="Y32" s="154"/>
+      <c r="Z32" s="18"/>
+      <c r="AA32" s="154"/>
+      <c r="AB32" s="18"/>
+      <c r="AC32" s="18"/>
+      <c r="AD32" s="18"/>
+      <c r="AE32" s="18"/>
+      <c r="AF32" s="18"/>
+      <c r="AG32" s="18"/>
+      <c r="AH32" s="18"/>
+      <c r="AI32" s="18"/>
+      <c r="AJ32" s="18"/>
+      <c r="AK32" s="18"/>
+      <c r="AL32" s="155"/>
+      <c r="AM32" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN32" s="50"/>
-      <c r="AO32" s="36">
+      <c r="AN32" s="24"/>
+      <c r="AO32" s="33">
         <f>AW4-AM32</f>
         <v>0</v>
       </c>
-      <c r="AP32" s="37"/>
-      <c r="AQ32" s="64"/>
-      <c r="AR32" s="24"/>
-      <c r="AS32" s="24"/>
-      <c r="AT32" s="24"/>
+      <c r="AP32" s="28"/>
+      <c r="AQ32" s="34"/>
+      <c r="AR32" s="22"/>
+      <c r="AS32" s="22"/>
+      <c r="AT32" s="22"/>
       <c r="AU32" s="5"/>
     </row>
     <row r="33" spans="1:47" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A33" s="130"/>
-      <c r="B33" s="112"/>
-      <c r="C33" s="87" t="s">
+      <c r="A33" s="93"/>
+      <c r="B33" s="91"/>
+      <c r="C33" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="88"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="6"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="10"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="6"/>
-      <c r="Y33" s="7"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="7"/>
-      <c r="AB33" s="6"/>
-      <c r="AC33" s="6"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="7"/>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
-      <c r="AK33" s="6"/>
-      <c r="AL33" s="16"/>
-      <c r="AM33" s="42">
+      <c r="D33" s="100"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="154"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="154"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="154"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="154"/>
+      <c r="X33" s="18"/>
+      <c r="Y33" s="154"/>
+      <c r="Z33" s="18"/>
+      <c r="AA33" s="154"/>
+      <c r="AB33" s="18"/>
+      <c r="AC33" s="18"/>
+      <c r="AD33" s="18"/>
+      <c r="AE33" s="18"/>
+      <c r="AF33" s="18"/>
+      <c r="AG33" s="18"/>
+      <c r="AH33" s="154"/>
+      <c r="AI33" s="18"/>
+      <c r="AJ33" s="18"/>
+      <c r="AK33" s="18"/>
+      <c r="AL33" s="155"/>
+      <c r="AM33" s="45">
         <f>SUM(AM8:AN32)</f>
         <v>0</v>
       </c>
-      <c r="AN33" s="43"/>
-      <c r="AO33" s="83">
+      <c r="AN33" s="46"/>
+      <c r="AO33" s="103">
         <f>COUNTIF(F8:AL8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP33" s="40"/>
-      <c r="AQ33" s="38"/>
-      <c r="AR33" s="39"/>
-      <c r="AS33" s="39"/>
-      <c r="AT33" s="39"/>
-      <c r="AU33" s="40"/>
+      <c r="AP33" s="43"/>
+      <c r="AQ33" s="41"/>
+      <c r="AR33" s="42"/>
+      <c r="AS33" s="42"/>
+      <c r="AT33" s="42"/>
+      <c r="AU33" s="43"/>
     </row>
     <row r="34" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A34" s="144">
+      <c r="A34" s="147">
         <v>1</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="6"/>
-      <c r="Y34" s="7"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="7"/>
-      <c r="AB34" s="6"/>
-      <c r="AC34" s="6"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="7"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="16"/>
-      <c r="AM34" s="49">
+      <c r="B34" s="40"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="154"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="154"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="154"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="154"/>
+      <c r="X34" s="18"/>
+      <c r="Y34" s="154"/>
+      <c r="Z34" s="18"/>
+      <c r="AA34" s="154"/>
+      <c r="AB34" s="18"/>
+      <c r="AC34" s="18"/>
+      <c r="AD34" s="18"/>
+      <c r="AE34" s="18"/>
+      <c r="AF34" s="18"/>
+      <c r="AG34" s="18"/>
+      <c r="AH34" s="154"/>
+      <c r="AI34" s="18"/>
+      <c r="AJ34" s="18"/>
+      <c r="AK34" s="18"/>
+      <c r="AL34" s="155"/>
+      <c r="AM34" s="23">
         <f t="shared" ref="AM34:AM60" si="1">COUNTIF(F34:AL34,"A")</f>
         <v>0</v>
       </c>
-      <c r="AN34" s="50"/>
-      <c r="AO34" s="36">
+      <c r="AN34" s="24"/>
+      <c r="AO34" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP34" s="37"/>
-      <c r="AQ34" s="51"/>
-      <c r="AR34" s="24"/>
-      <c r="AS34" s="24"/>
-      <c r="AT34" s="24"/>
-      <c r="AU34" s="37"/>
+      <c r="AP34" s="28"/>
+      <c r="AQ34" s="27"/>
+      <c r="AR34" s="22"/>
+      <c r="AS34" s="22"/>
+      <c r="AT34" s="22"/>
+      <c r="AU34" s="28"/>
     </row>
     <row r="35" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A35" s="153">
+      <c r="A35" s="143">
         <v>2</v>
       </c>
-      <c r="B35" s="24"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="6"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="6"/>
-      <c r="U35" s="6"/>
-      <c r="V35" s="6"/>
-      <c r="W35" s="7"/>
-      <c r="X35" s="6"/>
-      <c r="Y35" s="7"/>
-      <c r="Z35" s="6"/>
-      <c r="AA35" s="7"/>
-      <c r="AB35" s="6"/>
-      <c r="AC35" s="6"/>
-      <c r="AD35" s="6"/>
-      <c r="AE35" s="6"/>
-      <c r="AF35" s="6"/>
-      <c r="AG35" s="6"/>
-      <c r="AH35" s="7"/>
-      <c r="AI35" s="6"/>
-      <c r="AJ35" s="6"/>
-      <c r="AK35" s="6"/>
-      <c r="AL35" s="16"/>
-      <c r="AM35" s="49">
+      <c r="B35" s="22"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="154"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="154"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="154"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="154"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="154"/>
+      <c r="Z35" s="18"/>
+      <c r="AA35" s="154"/>
+      <c r="AB35" s="18"/>
+      <c r="AC35" s="18"/>
+      <c r="AD35" s="18"/>
+      <c r="AE35" s="18"/>
+      <c r="AF35" s="18"/>
+      <c r="AG35" s="18"/>
+      <c r="AH35" s="154"/>
+      <c r="AI35" s="18"/>
+      <c r="AJ35" s="18"/>
+      <c r="AK35" s="18"/>
+      <c r="AL35" s="155"/>
+      <c r="AM35" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN35" s="50"/>
-      <c r="AO35" s="36">
+      <c r="AN35" s="24"/>
+      <c r="AO35" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP35" s="37"/>
-      <c r="AQ35" s="51"/>
-      <c r="AR35" s="24"/>
-      <c r="AS35" s="24"/>
-      <c r="AT35" s="24"/>
-      <c r="AU35" s="37"/>
+      <c r="AP35" s="28"/>
+      <c r="AQ35" s="27"/>
+      <c r="AR35" s="22"/>
+      <c r="AS35" s="22"/>
+      <c r="AT35" s="22"/>
+      <c r="AU35" s="28"/>
     </row>
     <row r="36" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A36" s="52">
+      <c r="A36" s="29">
         <v>3</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="7"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="6"/>
-      <c r="Y36" s="7"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="7"/>
-      <c r="AB36" s="6"/>
-      <c r="AC36" s="6"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="7"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="16"/>
-      <c r="AM36" s="49">
+      <c r="B36" s="22"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="154"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="154"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="154"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="18"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="154"/>
+      <c r="X36" s="18"/>
+      <c r="Y36" s="154"/>
+      <c r="Z36" s="18"/>
+      <c r="AA36" s="154"/>
+      <c r="AB36" s="18"/>
+      <c r="AC36" s="18"/>
+      <c r="AD36" s="18"/>
+      <c r="AE36" s="18"/>
+      <c r="AF36" s="18"/>
+      <c r="AG36" s="18"/>
+      <c r="AH36" s="154"/>
+      <c r="AI36" s="18"/>
+      <c r="AJ36" s="18"/>
+      <c r="AK36" s="18"/>
+      <c r="AL36" s="155"/>
+      <c r="AM36" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="50"/>
-      <c r="AO36" s="36">
+      <c r="AN36" s="24"/>
+      <c r="AO36" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP36" s="37"/>
-      <c r="AQ36" s="51"/>
-      <c r="AR36" s="24"/>
-      <c r="AS36" s="24"/>
-      <c r="AT36" s="24"/>
-      <c r="AU36" s="37"/>
+      <c r="AP36" s="28"/>
+      <c r="AQ36" s="27"/>
+      <c r="AR36" s="22"/>
+      <c r="AS36" s="22"/>
+      <c r="AT36" s="22"/>
+      <c r="AU36" s="28"/>
     </row>
     <row r="37" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A37" s="52">
+      <c r="A37" s="29">
         <v>4</v>
       </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-      <c r="S37" s="7"/>
-      <c r="T37" s="6"/>
-      <c r="U37" s="6"/>
-      <c r="V37" s="6"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="6"/>
-      <c r="Y37" s="7"/>
-      <c r="Z37" s="6"/>
-      <c r="AA37" s="7"/>
-      <c r="AB37" s="6"/>
-      <c r="AC37" s="6"/>
-      <c r="AD37" s="6"/>
-      <c r="AE37" s="6"/>
-      <c r="AF37" s="6"/>
-      <c r="AG37" s="6"/>
-      <c r="AH37" s="7"/>
-      <c r="AI37" s="6"/>
-      <c r="AJ37" s="6"/>
-      <c r="AK37" s="6"/>
-      <c r="AL37" s="16"/>
-      <c r="AM37" s="49">
+      <c r="B37" s="22"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="154"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="154"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="154"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="154"/>
+      <c r="X37" s="18"/>
+      <c r="Y37" s="154"/>
+      <c r="Z37" s="18"/>
+      <c r="AA37" s="154"/>
+      <c r="AB37" s="18"/>
+      <c r="AC37" s="18"/>
+      <c r="AD37" s="18"/>
+      <c r="AE37" s="18"/>
+      <c r="AF37" s="18"/>
+      <c r="AG37" s="18"/>
+      <c r="AH37" s="154"/>
+      <c r="AI37" s="18"/>
+      <c r="AJ37" s="18"/>
+      <c r="AK37" s="18"/>
+      <c r="AL37" s="155"/>
+      <c r="AM37" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN37" s="50"/>
-      <c r="AO37" s="36">
+      <c r="AN37" s="24"/>
+      <c r="AO37" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP37" s="37"/>
-      <c r="AQ37" s="51"/>
-      <c r="AR37" s="24"/>
-      <c r="AS37" s="24"/>
-      <c r="AT37" s="24"/>
-      <c r="AU37" s="37"/>
+      <c r="AP37" s="28"/>
+      <c r="AQ37" s="27"/>
+      <c r="AR37" s="22"/>
+      <c r="AS37" s="22"/>
+      <c r="AT37" s="22"/>
+      <c r="AU37" s="28"/>
     </row>
     <row r="38" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A38" s="52">
+      <c r="A38" s="29">
         <v>5</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="7"/>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
-      <c r="V38" s="6"/>
-      <c r="W38" s="7"/>
-      <c r="X38" s="6"/>
-      <c r="Y38" s="7"/>
-      <c r="Z38" s="6"/>
-      <c r="AA38" s="7"/>
-      <c r="AB38" s="6"/>
-      <c r="AC38" s="6"/>
-      <c r="AD38" s="6"/>
-      <c r="AE38" s="6"/>
-      <c r="AF38" s="6"/>
-      <c r="AG38" s="6"/>
-      <c r="AH38" s="7"/>
-      <c r="AI38" s="6"/>
-      <c r="AJ38" s="6"/>
-      <c r="AK38" s="6"/>
-      <c r="AL38" s="16"/>
-      <c r="AM38" s="49">
+      <c r="B38" s="22"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="154"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="154"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="154"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="154"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="154"/>
+      <c r="Z38" s="18"/>
+      <c r="AA38" s="154"/>
+      <c r="AB38" s="18"/>
+      <c r="AC38" s="18"/>
+      <c r="AD38" s="18"/>
+      <c r="AE38" s="18"/>
+      <c r="AF38" s="18"/>
+      <c r="AG38" s="18"/>
+      <c r="AH38" s="154"/>
+      <c r="AI38" s="18"/>
+      <c r="AJ38" s="18"/>
+      <c r="AK38" s="18"/>
+      <c r="AL38" s="155"/>
+      <c r="AM38" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN38" s="50"/>
-      <c r="AO38" s="36">
+      <c r="AN38" s="24"/>
+      <c r="AO38" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP38" s="37"/>
-      <c r="AQ38" s="51"/>
-      <c r="AR38" s="24"/>
-      <c r="AS38" s="24"/>
-      <c r="AT38" s="24"/>
-      <c r="AU38" s="37"/>
+      <c r="AP38" s="28"/>
+      <c r="AQ38" s="27"/>
+      <c r="AR38" s="22"/>
+      <c r="AS38" s="22"/>
+      <c r="AT38" s="22"/>
+      <c r="AU38" s="28"/>
     </row>
     <row r="39" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A39" s="52">
+      <c r="A39" s="29">
         <v>6</v>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="7"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="7"/>
-      <c r="X39" s="6"/>
-      <c r="Y39" s="7"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="7"/>
-      <c r="AB39" s="6"/>
-      <c r="AC39" s="6"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="7"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="16"/>
-      <c r="AM39" s="49">
+      <c r="B39" s="22"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="154"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="154"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="154"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="154"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="154"/>
+      <c r="Z39" s="18"/>
+      <c r="AA39" s="154"/>
+      <c r="AB39" s="18"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="18"/>
+      <c r="AE39" s="18"/>
+      <c r="AF39" s="18"/>
+      <c r="AG39" s="18"/>
+      <c r="AH39" s="154"/>
+      <c r="AI39" s="18"/>
+      <c r="AJ39" s="18"/>
+      <c r="AK39" s="18"/>
+      <c r="AL39" s="155"/>
+      <c r="AM39" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN39" s="50"/>
-      <c r="AO39" s="36">
+      <c r="AN39" s="24"/>
+      <c r="AO39" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP39" s="37"/>
-      <c r="AQ39" s="51"/>
-      <c r="AR39" s="24"/>
-      <c r="AS39" s="24"/>
-      <c r="AT39" s="24"/>
-      <c r="AU39" s="37"/>
+      <c r="AP39" s="28"/>
+      <c r="AQ39" s="27"/>
+      <c r="AR39" s="22"/>
+      <c r="AS39" s="22"/>
+      <c r="AT39" s="22"/>
+      <c r="AU39" s="28"/>
     </row>
     <row r="40" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A40" s="52">
+      <c r="A40" s="29">
         <v>7</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="7"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
-      <c r="V40" s="6"/>
-      <c r="W40" s="7"/>
-      <c r="X40" s="6"/>
-      <c r="Y40" s="7"/>
-      <c r="Z40" s="6"/>
-      <c r="AA40" s="7"/>
-      <c r="AB40" s="6"/>
-      <c r="AC40" s="6"/>
-      <c r="AD40" s="6"/>
-      <c r="AE40" s="6"/>
-      <c r="AF40" s="6"/>
-      <c r="AG40" s="6"/>
-      <c r="AH40" s="7"/>
-      <c r="AI40" s="6"/>
-      <c r="AJ40" s="6"/>
-      <c r="AK40" s="6"/>
-      <c r="AL40" s="16"/>
-      <c r="AM40" s="49">
+      <c r="B40" s="22"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="154"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="154"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="154"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="154"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="154"/>
+      <c r="Z40" s="18"/>
+      <c r="AA40" s="154"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="18"/>
+      <c r="AE40" s="18"/>
+      <c r="AF40" s="18"/>
+      <c r="AG40" s="18"/>
+      <c r="AH40" s="154"/>
+      <c r="AI40" s="18"/>
+      <c r="AJ40" s="18"/>
+      <c r="AK40" s="18"/>
+      <c r="AL40" s="155"/>
+      <c r="AM40" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN40" s="50"/>
-      <c r="AO40" s="36">
+      <c r="AN40" s="24"/>
+      <c r="AO40" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP40" s="37"/>
-      <c r="AQ40" s="51"/>
-      <c r="AR40" s="24"/>
-      <c r="AS40" s="24"/>
-      <c r="AT40" s="24"/>
-      <c r="AU40" s="37"/>
+      <c r="AP40" s="28"/>
+      <c r="AQ40" s="27"/>
+      <c r="AR40" s="22"/>
+      <c r="AS40" s="22"/>
+      <c r="AT40" s="22"/>
+      <c r="AU40" s="28"/>
     </row>
     <row r="41" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A41" s="52">
+      <c r="A41" s="29">
         <v>8</v>
       </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="6"/>
-      <c r="S41" s="7"/>
-      <c r="T41" s="6"/>
-      <c r="U41" s="6"/>
-      <c r="V41" s="6"/>
-      <c r="W41" s="7"/>
-      <c r="X41" s="6"/>
-      <c r="Y41" s="7"/>
-      <c r="Z41" s="6"/>
-      <c r="AA41" s="7"/>
-      <c r="AB41" s="6"/>
-      <c r="AC41" s="6"/>
-      <c r="AD41" s="6"/>
-      <c r="AE41" s="6"/>
-      <c r="AF41" s="6"/>
-      <c r="AG41" s="6"/>
-      <c r="AH41" s="7"/>
-      <c r="AI41" s="6"/>
-      <c r="AJ41" s="6"/>
-      <c r="AK41" s="6"/>
-      <c r="AL41" s="16"/>
-      <c r="AM41" s="49">
+      <c r="B41" s="22"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="154"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="154"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="154"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="154"/>
+      <c r="Z41" s="18"/>
+      <c r="AA41" s="154"/>
+      <c r="AB41" s="18"/>
+      <c r="AC41" s="18"/>
+      <c r="AD41" s="18"/>
+      <c r="AE41" s="18"/>
+      <c r="AF41" s="18"/>
+      <c r="AG41" s="18"/>
+      <c r="AH41" s="154"/>
+      <c r="AI41" s="18"/>
+      <c r="AJ41" s="18"/>
+      <c r="AK41" s="18"/>
+      <c r="AL41" s="155"/>
+      <c r="AM41" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN41" s="50"/>
-      <c r="AO41" s="36">
+      <c r="AN41" s="24"/>
+      <c r="AO41" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP41" s="37"/>
-      <c r="AQ41" s="51"/>
-      <c r="AR41" s="24"/>
-      <c r="AS41" s="24"/>
-      <c r="AT41" s="24"/>
-      <c r="AU41" s="37"/>
+      <c r="AP41" s="28"/>
+      <c r="AQ41" s="27"/>
+      <c r="AR41" s="22"/>
+      <c r="AS41" s="22"/>
+      <c r="AT41" s="22"/>
+      <c r="AU41" s="28"/>
     </row>
     <row r="42" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A42" s="52">
+      <c r="A42" s="29">
         <v>9</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="7"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="7"/>
-      <c r="X42" s="6"/>
-      <c r="Y42" s="7"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="7"/>
-      <c r="AB42" s="6"/>
-      <c r="AC42" s="6"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="7"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="16"/>
-      <c r="AM42" s="49">
+      <c r="B42" s="22"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="154"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="154"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
+      <c r="Q42" s="18"/>
+      <c r="R42" s="18"/>
+      <c r="S42" s="154"/>
+      <c r="T42" s="18"/>
+      <c r="U42" s="18"/>
+      <c r="V42" s="18"/>
+      <c r="W42" s="154"/>
+      <c r="X42" s="18"/>
+      <c r="Y42" s="154"/>
+      <c r="Z42" s="18"/>
+      <c r="AA42" s="154"/>
+      <c r="AB42" s="18"/>
+      <c r="AC42" s="18"/>
+      <c r="AD42" s="18"/>
+      <c r="AE42" s="18"/>
+      <c r="AF42" s="18"/>
+      <c r="AG42" s="18"/>
+      <c r="AH42" s="154"/>
+      <c r="AI42" s="18"/>
+      <c r="AJ42" s="18"/>
+      <c r="AK42" s="18"/>
+      <c r="AL42" s="155"/>
+      <c r="AM42" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN42" s="50"/>
-      <c r="AO42" s="36">
+      <c r="AN42" s="24"/>
+      <c r="AO42" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP42" s="37"/>
-      <c r="AQ42" s="51"/>
-      <c r="AR42" s="24"/>
-      <c r="AS42" s="24"/>
-      <c r="AT42" s="24"/>
-      <c r="AU42" s="37"/>
+      <c r="AP42" s="28"/>
+      <c r="AQ42" s="27"/>
+      <c r="AR42" s="22"/>
+      <c r="AS42" s="22"/>
+      <c r="AT42" s="22"/>
+      <c r="AU42" s="28"/>
     </row>
     <row r="43" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A43" s="52">
+      <c r="A43" s="29">
         <v>10</v>
       </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="6"/>
-      <c r="S43" s="7"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="7"/>
-      <c r="X43" s="6"/>
-      <c r="Y43" s="7"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="7"/>
-      <c r="AB43" s="6"/>
-      <c r="AC43" s="6"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="7"/>
-      <c r="AI43" s="6"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="6"/>
-      <c r="AL43" s="16"/>
-      <c r="AM43" s="49">
+      <c r="B43" s="22"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="154"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="154"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="154"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="154"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="154"/>
+      <c r="Z43" s="18"/>
+      <c r="AA43" s="154"/>
+      <c r="AB43" s="18"/>
+      <c r="AC43" s="18"/>
+      <c r="AD43" s="18"/>
+      <c r="AE43" s="18"/>
+      <c r="AF43" s="18"/>
+      <c r="AG43" s="18"/>
+      <c r="AH43" s="154"/>
+      <c r="AI43" s="18"/>
+      <c r="AJ43" s="18"/>
+      <c r="AK43" s="18"/>
+      <c r="AL43" s="155"/>
+      <c r="AM43" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN43" s="50"/>
-      <c r="AO43" s="36">
+      <c r="AN43" s="24"/>
+      <c r="AO43" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP43" s="37"/>
-      <c r="AQ43" s="51"/>
-      <c r="AR43" s="24"/>
-      <c r="AS43" s="24"/>
-      <c r="AT43" s="24"/>
-      <c r="AU43" s="37"/>
+      <c r="AP43" s="28"/>
+      <c r="AQ43" s="27"/>
+      <c r="AR43" s="22"/>
+      <c r="AS43" s="22"/>
+      <c r="AT43" s="22"/>
+      <c r="AU43" s="28"/>
     </row>
     <row r="44" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A44" s="52">
+      <c r="A44" s="29">
         <v>11</v>
       </c>
-      <c r="B44" s="24"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="6"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="7"/>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
-      <c r="V44" s="6"/>
-      <c r="W44" s="7"/>
-      <c r="X44" s="6"/>
-      <c r="Y44" s="7"/>
-      <c r="Z44" s="6"/>
-      <c r="AA44" s="7"/>
-      <c r="AB44" s="6"/>
-      <c r="AC44" s="6"/>
-      <c r="AD44" s="6"/>
-      <c r="AE44" s="6"/>
-      <c r="AF44" s="6"/>
-      <c r="AG44" s="6"/>
-      <c r="AH44" s="7"/>
-      <c r="AI44" s="6"/>
-      <c r="AJ44" s="6"/>
-      <c r="AK44" s="6"/>
-      <c r="AL44" s="16"/>
-      <c r="AM44" s="49">
+      <c r="B44" s="22"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="154"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="154"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="154"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="154"/>
+      <c r="X44" s="18"/>
+      <c r="Y44" s="154"/>
+      <c r="Z44" s="18"/>
+      <c r="AA44" s="154"/>
+      <c r="AB44" s="18"/>
+      <c r="AC44" s="18"/>
+      <c r="AD44" s="18"/>
+      <c r="AE44" s="18"/>
+      <c r="AF44" s="18"/>
+      <c r="AG44" s="18"/>
+      <c r="AH44" s="154"/>
+      <c r="AI44" s="18"/>
+      <c r="AJ44" s="18"/>
+      <c r="AK44" s="18"/>
+      <c r="AL44" s="155"/>
+      <c r="AM44" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN44" s="50"/>
-      <c r="AO44" s="36">
+      <c r="AN44" s="24"/>
+      <c r="AO44" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP44" s="37"/>
-      <c r="AQ44" s="51"/>
-      <c r="AR44" s="24"/>
-      <c r="AS44" s="24"/>
-      <c r="AT44" s="24"/>
-      <c r="AU44" s="37"/>
+      <c r="AP44" s="28"/>
+      <c r="AQ44" s="27"/>
+      <c r="AR44" s="22"/>
+      <c r="AS44" s="22"/>
+      <c r="AT44" s="22"/>
+      <c r="AU44" s="28"/>
     </row>
     <row r="45" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A45" s="52">
+      <c r="A45" s="29">
         <v>12</v>
       </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="7"/>
-      <c r="T45" s="6"/>
-      <c r="U45" s="6"/>
-      <c r="V45" s="6"/>
-      <c r="W45" s="7"/>
-      <c r="X45" s="6"/>
-      <c r="Y45" s="7"/>
-      <c r="Z45" s="6"/>
-      <c r="AA45" s="7"/>
-      <c r="AB45" s="6"/>
-      <c r="AC45" s="6"/>
-      <c r="AD45" s="6"/>
-      <c r="AE45" s="6"/>
-      <c r="AF45" s="6"/>
-      <c r="AG45" s="6"/>
-      <c r="AH45" s="7"/>
-      <c r="AI45" s="6"/>
-      <c r="AJ45" s="6"/>
-      <c r="AK45" s="6"/>
-      <c r="AL45" s="16"/>
-      <c r="AM45" s="49">
+      <c r="B45" s="22"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="154"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="154"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="154"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="154"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="154"/>
+      <c r="Z45" s="18"/>
+      <c r="AA45" s="154"/>
+      <c r="AB45" s="18"/>
+      <c r="AC45" s="18"/>
+      <c r="AD45" s="18"/>
+      <c r="AE45" s="18"/>
+      <c r="AF45" s="18"/>
+      <c r="AG45" s="18"/>
+      <c r="AH45" s="154"/>
+      <c r="AI45" s="18"/>
+      <c r="AJ45" s="18"/>
+      <c r="AK45" s="18"/>
+      <c r="AL45" s="155"/>
+      <c r="AM45" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN45" s="50"/>
-      <c r="AO45" s="36">
+      <c r="AN45" s="24"/>
+      <c r="AO45" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP45" s="37"/>
-      <c r="AQ45" s="51"/>
-      <c r="AR45" s="24"/>
-      <c r="AS45" s="24"/>
-      <c r="AT45" s="24"/>
-      <c r="AU45" s="37"/>
+      <c r="AP45" s="28"/>
+      <c r="AQ45" s="27"/>
+      <c r="AR45" s="22"/>
+      <c r="AS45" s="22"/>
+      <c r="AT45" s="22"/>
+      <c r="AU45" s="28"/>
     </row>
     <row r="46" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A46" s="52">
+      <c r="A46" s="29">
         <v>13</v>
       </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="7"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="7"/>
-      <c r="X46" s="6"/>
-      <c r="Y46" s="7"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="7"/>
-      <c r="AB46" s="6"/>
-      <c r="AC46" s="6"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="16"/>
-      <c r="AM46" s="49">
+      <c r="B46" s="22"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="154"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="154"/>
+      <c r="T46" s="18"/>
+      <c r="U46" s="18"/>
+      <c r="V46" s="18"/>
+      <c r="W46" s="154"/>
+      <c r="X46" s="18"/>
+      <c r="Y46" s="154"/>
+      <c r="Z46" s="18"/>
+      <c r="AA46" s="154"/>
+      <c r="AB46" s="18"/>
+      <c r="AC46" s="18"/>
+      <c r="AD46" s="18"/>
+      <c r="AE46" s="18"/>
+      <c r="AF46" s="18"/>
+      <c r="AG46" s="18"/>
+      <c r="AH46" s="18"/>
+      <c r="AI46" s="18"/>
+      <c r="AJ46" s="18"/>
+      <c r="AK46" s="18"/>
+      <c r="AL46" s="155"/>
+      <c r="AM46" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN46" s="50"/>
-      <c r="AO46" s="36">
+      <c r="AN46" s="24"/>
+      <c r="AO46" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP46" s="37"/>
-      <c r="AQ46" s="64"/>
-      <c r="AR46" s="24"/>
-      <c r="AS46" s="24"/>
-      <c r="AT46" s="24"/>
+      <c r="AP46" s="28"/>
+      <c r="AQ46" s="34"/>
+      <c r="AR46" s="22"/>
+      <c r="AS46" s="22"/>
+      <c r="AT46" s="22"/>
       <c r="AU46" s="5"/>
     </row>
     <row r="47" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A47" s="52">
+      <c r="A47" s="29">
         <v>14</v>
       </c>
-      <c r="B47" s="24"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="7"/>
-      <c r="T47" s="6"/>
-      <c r="U47" s="6"/>
-      <c r="V47" s="6"/>
-      <c r="W47" s="7"/>
-      <c r="X47" s="6"/>
-      <c r="Y47" s="7"/>
-      <c r="Z47" s="6"/>
-      <c r="AA47" s="7"/>
-      <c r="AB47" s="6"/>
-      <c r="AC47" s="6"/>
-      <c r="AD47" s="6"/>
-      <c r="AE47" s="6"/>
-      <c r="AF47" s="6"/>
-      <c r="AG47" s="6"/>
-      <c r="AH47" s="6"/>
-      <c r="AI47" s="6"/>
-      <c r="AJ47" s="6"/>
-      <c r="AK47" s="6"/>
-      <c r="AL47" s="16"/>
-      <c r="AM47" s="49">
+      <c r="B47" s="22"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="154"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="154"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="154"/>
+      <c r="X47" s="18"/>
+      <c r="Y47" s="154"/>
+      <c r="Z47" s="18"/>
+      <c r="AA47" s="154"/>
+      <c r="AB47" s="18"/>
+      <c r="AC47" s="18"/>
+      <c r="AD47" s="18"/>
+      <c r="AE47" s="18"/>
+      <c r="AF47" s="18"/>
+      <c r="AG47" s="18"/>
+      <c r="AH47" s="18"/>
+      <c r="AI47" s="18"/>
+      <c r="AJ47" s="18"/>
+      <c r="AK47" s="18"/>
+      <c r="AL47" s="155"/>
+      <c r="AM47" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN47" s="50"/>
-      <c r="AO47" s="36">
+      <c r="AN47" s="24"/>
+      <c r="AO47" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP47" s="37"/>
-      <c r="AQ47" s="64"/>
-      <c r="AR47" s="24"/>
-      <c r="AS47" s="24"/>
-      <c r="AT47" s="24"/>
+      <c r="AP47" s="28"/>
+      <c r="AQ47" s="34"/>
+      <c r="AR47" s="22"/>
+      <c r="AS47" s="22"/>
+      <c r="AT47" s="22"/>
       <c r="AU47" s="5"/>
     </row>
     <row r="48" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A48" s="52">
+      <c r="A48" s="29">
         <v>15</v>
       </c>
-      <c r="B48" s="24"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="35"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
-      <c r="S48" s="7"/>
-      <c r="T48" s="6"/>
-      <c r="U48" s="6"/>
-      <c r="V48" s="6"/>
-      <c r="W48" s="7"/>
-      <c r="X48" s="6"/>
-      <c r="Y48" s="7"/>
-      <c r="Z48" s="6"/>
-      <c r="AA48" s="7"/>
-      <c r="AB48" s="6"/>
-      <c r="AC48" s="6"/>
-      <c r="AD48" s="6"/>
-      <c r="AE48" s="6"/>
-      <c r="AF48" s="6"/>
-      <c r="AG48" s="6"/>
-      <c r="AH48" s="6"/>
-      <c r="AI48" s="6"/>
-      <c r="AJ48" s="6"/>
-      <c r="AK48" s="6"/>
-      <c r="AL48" s="16"/>
-      <c r="AM48" s="49">
+      <c r="B48" s="22"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="154"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18"/>
+      <c r="R48" s="18"/>
+      <c r="S48" s="154"/>
+      <c r="T48" s="18"/>
+      <c r="U48" s="18"/>
+      <c r="V48" s="18"/>
+      <c r="W48" s="154"/>
+      <c r="X48" s="18"/>
+      <c r="Y48" s="154"/>
+      <c r="Z48" s="18"/>
+      <c r="AA48" s="154"/>
+      <c r="AB48" s="18"/>
+      <c r="AC48" s="18"/>
+      <c r="AD48" s="18"/>
+      <c r="AE48" s="18"/>
+      <c r="AF48" s="18"/>
+      <c r="AG48" s="18"/>
+      <c r="AH48" s="18"/>
+      <c r="AI48" s="18"/>
+      <c r="AJ48" s="18"/>
+      <c r="AK48" s="18"/>
+      <c r="AL48" s="155"/>
+      <c r="AM48" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN48" s="50"/>
-      <c r="AO48" s="36">
+      <c r="AN48" s="24"/>
+      <c r="AO48" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP48" s="37"/>
-      <c r="AQ48" s="64"/>
-      <c r="AR48" s="24"/>
-      <c r="AS48" s="24"/>
-      <c r="AT48" s="24"/>
+      <c r="AP48" s="28"/>
+      <c r="AQ48" s="34"/>
+      <c r="AR48" s="22"/>
+      <c r="AS48" s="22"/>
+      <c r="AT48" s="22"/>
       <c r="AU48" s="5"/>
     </row>
     <row r="49" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A49" s="52">
+      <c r="A49" s="29">
         <v>16</v>
       </c>
-      <c r="B49" s="24"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="35"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="6"/>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="6"/>
-      <c r="S49" s="7"/>
-      <c r="T49" s="6"/>
-      <c r="U49" s="6"/>
-      <c r="V49" s="6"/>
-      <c r="W49" s="7"/>
-      <c r="X49" s="6"/>
-      <c r="Y49" s="7"/>
-      <c r="Z49" s="6"/>
-      <c r="AA49" s="7"/>
-      <c r="AB49" s="6"/>
-      <c r="AC49" s="6"/>
-      <c r="AD49" s="6"/>
-      <c r="AE49" s="6"/>
-      <c r="AF49" s="6"/>
-      <c r="AG49" s="6"/>
-      <c r="AH49" s="6"/>
-      <c r="AI49" s="6"/>
-      <c r="AJ49" s="6"/>
-      <c r="AK49" s="6"/>
-      <c r="AL49" s="16"/>
-      <c r="AM49" s="49">
+      <c r="B49" s="22"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="154"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="154"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="18"/>
+      <c r="V49" s="18"/>
+      <c r="W49" s="154"/>
+      <c r="X49" s="18"/>
+      <c r="Y49" s="154"/>
+      <c r="Z49" s="18"/>
+      <c r="AA49" s="154"/>
+      <c r="AB49" s="18"/>
+      <c r="AC49" s="18"/>
+      <c r="AD49" s="18"/>
+      <c r="AE49" s="18"/>
+      <c r="AF49" s="18"/>
+      <c r="AG49" s="18"/>
+      <c r="AH49" s="18"/>
+      <c r="AI49" s="18"/>
+      <c r="AJ49" s="18"/>
+      <c r="AK49" s="18"/>
+      <c r="AL49" s="155"/>
+      <c r="AM49" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN49" s="50"/>
-      <c r="AO49" s="36">
+      <c r="AN49" s="24"/>
+      <c r="AO49" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP49" s="37"/>
-      <c r="AQ49" s="64"/>
-      <c r="AR49" s="24"/>
-      <c r="AS49" s="24"/>
-      <c r="AT49" s="24"/>
+      <c r="AP49" s="28"/>
+      <c r="AQ49" s="34"/>
+      <c r="AR49" s="22"/>
+      <c r="AS49" s="22"/>
+      <c r="AT49" s="22"/>
       <c r="AU49" s="5"/>
     </row>
     <row r="50" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A50" s="52">
+      <c r="A50" s="29">
         <v>17</v>
       </c>
-      <c r="B50" s="24"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="7"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="7"/>
-      <c r="X50" s="6"/>
-      <c r="Y50" s="7"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="7"/>
-      <c r="AB50" s="6"/>
-      <c r="AC50" s="6"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="16"/>
-      <c r="AM50" s="49">
+      <c r="B50" s="22"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="154"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18"/>
+      <c r="R50" s="18"/>
+      <c r="S50" s="154"/>
+      <c r="T50" s="18"/>
+      <c r="U50" s="18"/>
+      <c r="V50" s="18"/>
+      <c r="W50" s="154"/>
+      <c r="X50" s="18"/>
+      <c r="Y50" s="154"/>
+      <c r="Z50" s="18"/>
+      <c r="AA50" s="154"/>
+      <c r="AB50" s="18"/>
+      <c r="AC50" s="18"/>
+      <c r="AD50" s="18"/>
+      <c r="AE50" s="18"/>
+      <c r="AF50" s="18"/>
+      <c r="AG50" s="18"/>
+      <c r="AH50" s="18"/>
+      <c r="AI50" s="18"/>
+      <c r="AJ50" s="18"/>
+      <c r="AK50" s="18"/>
+      <c r="AL50" s="155"/>
+      <c r="AM50" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN50" s="50"/>
-      <c r="AO50" s="36">
+      <c r="AN50" s="24"/>
+      <c r="AO50" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP50" s="37"/>
-      <c r="AQ50" s="64"/>
-      <c r="AR50" s="24"/>
-      <c r="AS50" s="24"/>
-      <c r="AT50" s="24"/>
+      <c r="AP50" s="28"/>
+      <c r="AQ50" s="34"/>
+      <c r="AR50" s="22"/>
+      <c r="AS50" s="22"/>
+      <c r="AT50" s="22"/>
       <c r="AU50" s="5"/>
     </row>
     <row r="51" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A51" s="52">
+      <c r="A51" s="29">
         <v>18</v>
       </c>
-      <c r="B51" s="24"/>
-      <c r="C51" s="34"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="6"/>
-      <c r="S51" s="7"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="7"/>
-      <c r="X51" s="6"/>
-      <c r="Y51" s="7"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="7"/>
-      <c r="AB51" s="6"/>
-      <c r="AC51" s="6"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="7"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="16"/>
-      <c r="AM51" s="49">
+      <c r="B51" s="22"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="154"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="154"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="18"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="154"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="18"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="154"/>
+      <c r="X51" s="18"/>
+      <c r="Y51" s="154"/>
+      <c r="Z51" s="18"/>
+      <c r="AA51" s="154"/>
+      <c r="AB51" s="18"/>
+      <c r="AC51" s="18"/>
+      <c r="AD51" s="18"/>
+      <c r="AE51" s="18"/>
+      <c r="AF51" s="18"/>
+      <c r="AG51" s="18"/>
+      <c r="AH51" s="154"/>
+      <c r="AI51" s="18"/>
+      <c r="AJ51" s="18"/>
+      <c r="AK51" s="18"/>
+      <c r="AL51" s="155"/>
+      <c r="AM51" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN51" s="50"/>
-      <c r="AO51" s="36">
+      <c r="AN51" s="24"/>
+      <c r="AO51" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP51" s="37"/>
-      <c r="AQ51" s="51"/>
-      <c r="AR51" s="24"/>
-      <c r="AS51" s="24"/>
-      <c r="AT51" s="24"/>
-      <c r="AU51" s="37"/>
+      <c r="AP51" s="28"/>
+      <c r="AQ51" s="27"/>
+      <c r="AR51" s="22"/>
+      <c r="AS51" s="22"/>
+      <c r="AT51" s="22"/>
+      <c r="AU51" s="28"/>
     </row>
     <row r="52" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A52" s="52">
+      <c r="A52" s="29">
         <v>19</v>
       </c>
-      <c r="B52" s="24"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="7"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6"/>
-      <c r="W52" s="7"/>
-      <c r="X52" s="6"/>
-      <c r="Y52" s="7"/>
-      <c r="Z52" s="6"/>
-      <c r="AA52" s="7"/>
-      <c r="AB52" s="6"/>
-      <c r="AC52" s="6"/>
-      <c r="AD52" s="6"/>
-      <c r="AE52" s="6"/>
-      <c r="AF52" s="6"/>
-      <c r="AG52" s="6"/>
-      <c r="AH52" s="7"/>
-      <c r="AI52" s="6"/>
-      <c r="AJ52" s="6"/>
-      <c r="AK52" s="6"/>
-      <c r="AL52" s="16"/>
-      <c r="AM52" s="49">
+      <c r="B52" s="22"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="154"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="154"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="18"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="154"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="18"/>
+      <c r="V52" s="18"/>
+      <c r="W52" s="154"/>
+      <c r="X52" s="18"/>
+      <c r="Y52" s="154"/>
+      <c r="Z52" s="18"/>
+      <c r="AA52" s="154"/>
+      <c r="AB52" s="18"/>
+      <c r="AC52" s="18"/>
+      <c r="AD52" s="18"/>
+      <c r="AE52" s="18"/>
+      <c r="AF52" s="18"/>
+      <c r="AG52" s="18"/>
+      <c r="AH52" s="154"/>
+      <c r="AI52" s="18"/>
+      <c r="AJ52" s="18"/>
+      <c r="AK52" s="18"/>
+      <c r="AL52" s="155"/>
+      <c r="AM52" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN52" s="50"/>
-      <c r="AO52" s="36">
+      <c r="AN52" s="24"/>
+      <c r="AO52" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP52" s="37"/>
-      <c r="AQ52" s="51"/>
-      <c r="AR52" s="24"/>
-      <c r="AS52" s="24"/>
-      <c r="AT52" s="24"/>
-      <c r="AU52" s="37"/>
+      <c r="AP52" s="28"/>
+      <c r="AQ52" s="27"/>
+      <c r="AR52" s="22"/>
+      <c r="AS52" s="22"/>
+      <c r="AT52" s="22"/>
+      <c r="AU52" s="28"/>
     </row>
     <row r="53" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A53" s="52">
+      <c r="A53" s="29">
         <v>20</v>
       </c>
-      <c r="B53" s="24"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="7"/>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="7"/>
-      <c r="X53" s="6"/>
-      <c r="Y53" s="7"/>
-      <c r="Z53" s="6"/>
-      <c r="AA53" s="7"/>
-      <c r="AB53" s="6"/>
-      <c r="AC53" s="6"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="7"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="16"/>
-      <c r="AM53" s="49">
+      <c r="B53" s="22"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="154"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="154"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
+      <c r="P53" s="18"/>
+      <c r="Q53" s="18"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="154"/>
+      <c r="T53" s="18"/>
+      <c r="U53" s="18"/>
+      <c r="V53" s="18"/>
+      <c r="W53" s="154"/>
+      <c r="X53" s="18"/>
+      <c r="Y53" s="154"/>
+      <c r="Z53" s="18"/>
+      <c r="AA53" s="154"/>
+      <c r="AB53" s="18"/>
+      <c r="AC53" s="18"/>
+      <c r="AD53" s="18"/>
+      <c r="AE53" s="18"/>
+      <c r="AF53" s="18"/>
+      <c r="AG53" s="18"/>
+      <c r="AH53" s="154"/>
+      <c r="AI53" s="18"/>
+      <c r="AJ53" s="18"/>
+      <c r="AK53" s="18"/>
+      <c r="AL53" s="155"/>
+      <c r="AM53" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN53" s="50"/>
-      <c r="AO53" s="36">
+      <c r="AN53" s="24"/>
+      <c r="AO53" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP53" s="37"/>
-      <c r="AQ53" s="51"/>
-      <c r="AR53" s="24"/>
-      <c r="AS53" s="24"/>
-      <c r="AT53" s="24"/>
-      <c r="AU53" s="37"/>
+      <c r="AP53" s="28"/>
+      <c r="AQ53" s="27"/>
+      <c r="AR53" s="22"/>
+      <c r="AS53" s="22"/>
+      <c r="AT53" s="22"/>
+      <c r="AU53" s="28"/>
     </row>
     <row r="54" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A54" s="52">
+      <c r="A54" s="29">
         <v>21</v>
       </c>
-      <c r="B54" s="24"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="7"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="7"/>
-      <c r="X54" s="6"/>
-      <c r="Y54" s="7"/>
-      <c r="Z54" s="6"/>
-      <c r="AA54" s="7"/>
-      <c r="AB54" s="6"/>
-      <c r="AC54" s="6"/>
-      <c r="AD54" s="6"/>
-      <c r="AE54" s="6"/>
-      <c r="AF54" s="6"/>
-      <c r="AG54" s="6"/>
-      <c r="AH54" s="7"/>
-      <c r="AI54" s="6"/>
-      <c r="AJ54" s="6"/>
-      <c r="AK54" s="6"/>
-      <c r="AL54" s="16"/>
-      <c r="AM54" s="49">
+      <c r="B54" s="22"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="154"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="154"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="18"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="154"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="154"/>
+      <c r="X54" s="18"/>
+      <c r="Y54" s="154"/>
+      <c r="Z54" s="18"/>
+      <c r="AA54" s="154"/>
+      <c r="AB54" s="18"/>
+      <c r="AC54" s="18"/>
+      <c r="AD54" s="18"/>
+      <c r="AE54" s="18"/>
+      <c r="AF54" s="18"/>
+      <c r="AG54" s="18"/>
+      <c r="AH54" s="154"/>
+      <c r="AI54" s="18"/>
+      <c r="AJ54" s="18"/>
+      <c r="AK54" s="18"/>
+      <c r="AL54" s="155"/>
+      <c r="AM54" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN54" s="50"/>
-      <c r="AO54" s="36">
+      <c r="AN54" s="24"/>
+      <c r="AO54" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP54" s="37"/>
-      <c r="AQ54" s="51"/>
-      <c r="AR54" s="24"/>
-      <c r="AS54" s="24"/>
-      <c r="AT54" s="24"/>
-      <c r="AU54" s="37"/>
+      <c r="AP54" s="28"/>
+      <c r="AQ54" s="27"/>
+      <c r="AR54" s="22"/>
+      <c r="AS54" s="22"/>
+      <c r="AT54" s="22"/>
+      <c r="AU54" s="28"/>
     </row>
     <row r="55" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A55" s="52">
+      <c r="A55" s="29">
         <v>22</v>
       </c>
-      <c r="B55" s="24"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="7"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="7"/>
-      <c r="X55" s="6"/>
-      <c r="Y55" s="7"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="7"/>
-      <c r="AB55" s="6"/>
-      <c r="AC55" s="6"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="16"/>
-      <c r="AM55" s="49">
+      <c r="B55" s="22"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="154"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="18"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="154"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="18"/>
+      <c r="V55" s="18"/>
+      <c r="W55" s="154"/>
+      <c r="X55" s="18"/>
+      <c r="Y55" s="154"/>
+      <c r="Z55" s="18"/>
+      <c r="AA55" s="154"/>
+      <c r="AB55" s="18"/>
+      <c r="AC55" s="18"/>
+      <c r="AD55" s="18"/>
+      <c r="AE55" s="18"/>
+      <c r="AF55" s="18"/>
+      <c r="AG55" s="18"/>
+      <c r="AH55" s="18"/>
+      <c r="AI55" s="18"/>
+      <c r="AJ55" s="18"/>
+      <c r="AK55" s="18"/>
+      <c r="AL55" s="155"/>
+      <c r="AM55" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN55" s="50"/>
-      <c r="AO55" s="36">
+      <c r="AN55" s="24"/>
+      <c r="AO55" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP55" s="37"/>
-      <c r="AQ55" s="64"/>
-      <c r="AR55" s="24"/>
-      <c r="AS55" s="24"/>
-      <c r="AT55" s="24"/>
+      <c r="AP55" s="28"/>
+      <c r="AQ55" s="34"/>
+      <c r="AR55" s="22"/>
+      <c r="AS55" s="22"/>
+      <c r="AT55" s="22"/>
       <c r="AU55" s="5"/>
     </row>
     <row r="56" spans="1:47" ht="19.5" customHeight="1">
-      <c r="A56" s="52">
+      <c r="A56" s="29">
         <v>23</v>
       </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
-      <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="7"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
-      <c r="V56" s="6"/>
-      <c r="W56" s="7"/>
-      <c r="X56" s="6"/>
-      <c r="Y56" s="7"/>
-      <c r="Z56" s="6"/>
-      <c r="AA56" s="7"/>
-      <c r="AB56" s="6"/>
-      <c r="AC56" s="6"/>
-      <c r="AD56" s="6"/>
-      <c r="AE56" s="6"/>
-      <c r="AF56" s="6"/>
-      <c r="AG56" s="6"/>
-      <c r="AH56" s="6"/>
-      <c r="AI56" s="6"/>
-      <c r="AJ56" s="6"/>
-      <c r="AK56" s="6"/>
-      <c r="AL56" s="16"/>
-      <c r="AM56" s="49">
+      <c r="B56" s="22"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="154"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="18"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="154"/>
+      <c r="T56" s="18"/>
+      <c r="U56" s="18"/>
+      <c r="V56" s="18"/>
+      <c r="W56" s="154"/>
+      <c r="X56" s="18"/>
+      <c r="Y56" s="154"/>
+      <c r="Z56" s="18"/>
+      <c r="AA56" s="154"/>
+      <c r="AB56" s="18"/>
+      <c r="AC56" s="18"/>
+      <c r="AD56" s="18"/>
+      <c r="AE56" s="18"/>
+      <c r="AF56" s="18"/>
+      <c r="AG56" s="18"/>
+      <c r="AH56" s="18"/>
+      <c r="AI56" s="18"/>
+      <c r="AJ56" s="18"/>
+      <c r="AK56" s="18"/>
+      <c r="AL56" s="155"/>
+      <c r="AM56" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN56" s="50"/>
-      <c r="AO56" s="36">
+      <c r="AN56" s="24"/>
+      <c r="AO56" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP56" s="37"/>
-      <c r="AQ56" s="64"/>
-      <c r="AR56" s="24"/>
-      <c r="AS56" s="24"/>
-      <c r="AT56" s="24"/>
+      <c r="AP56" s="28"/>
+      <c r="AQ56" s="34"/>
+      <c r="AR56" s="22"/>
+      <c r="AS56" s="22"/>
+      <c r="AT56" s="22"/>
       <c r="AU56" s="5"/>
     </row>
     <row r="57" spans="1:47" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A57" s="52">
+      <c r="A57" s="29">
         <v>24</v>
       </c>
-      <c r="B57" s="24"/>
-      <c r="C57" s="34"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6"/>
-      <c r="O57" s="6"/>
-      <c r="P57" s="6"/>
-      <c r="Q57" s="6"/>
-      <c r="R57" s="6"/>
-      <c r="S57" s="7"/>
-      <c r="T57" s="6"/>
-      <c r="U57" s="6"/>
-      <c r="V57" s="6"/>
-      <c r="W57" s="7"/>
-      <c r="X57" s="6"/>
-      <c r="Y57" s="7"/>
-      <c r="Z57" s="6"/>
-      <c r="AA57" s="7"/>
-      <c r="AB57" s="6"/>
-      <c r="AC57" s="6"/>
-      <c r="AD57" s="6"/>
-      <c r="AE57" s="6"/>
-      <c r="AF57" s="6"/>
-      <c r="AG57" s="6"/>
-      <c r="AH57" s="6"/>
-      <c r="AI57" s="6"/>
-      <c r="AJ57" s="6"/>
-      <c r="AK57" s="6"/>
-      <c r="AL57" s="16"/>
-      <c r="AM57" s="49">
+      <c r="B57" s="22"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="154"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="18"/>
+      <c r="P57" s="18"/>
+      <c r="Q57" s="18"/>
+      <c r="R57" s="18"/>
+      <c r="S57" s="154"/>
+      <c r="T57" s="18"/>
+      <c r="U57" s="18"/>
+      <c r="V57" s="18"/>
+      <c r="W57" s="154"/>
+      <c r="X57" s="18"/>
+      <c r="Y57" s="154"/>
+      <c r="Z57" s="18"/>
+      <c r="AA57" s="154"/>
+      <c r="AB57" s="18"/>
+      <c r="AC57" s="18"/>
+      <c r="AD57" s="18"/>
+      <c r="AE57" s="18"/>
+      <c r="AF57" s="18"/>
+      <c r="AG57" s="18"/>
+      <c r="AH57" s="18"/>
+      <c r="AI57" s="18"/>
+      <c r="AJ57" s="18"/>
+      <c r="AK57" s="18"/>
+      <c r="AL57" s="155"/>
+      <c r="AM57" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN57" s="50"/>
-      <c r="AO57" s="36">
+      <c r="AN57" s="24"/>
+      <c r="AO57" s="33">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP57" s="37"/>
-      <c r="AQ57" s="64"/>
-      <c r="AR57" s="24"/>
-      <c r="AS57" s="24"/>
-      <c r="AT57" s="24"/>
+      <c r="AP57" s="28"/>
+      <c r="AQ57" s="34"/>
+      <c r="AR57" s="22"/>
+      <c r="AS57" s="22"/>
+      <c r="AT57" s="22"/>
       <c r="AU57" s="5"/>
     </row>
     <row r="58" spans="1:47" ht="19.5" hidden="1" customHeight="1">
-      <c r="A58" s="52">
+      <c r="A58" s="29">
         <v>25</v>
       </c>
-      <c r="B58" s="24"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="6"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="7"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="7"/>
-      <c r="X58" s="6"/>
-      <c r="Y58" s="7"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="7"/>
-      <c r="AB58" s="6"/>
-      <c r="AC58" s="6"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="16"/>
-      <c r="AM58" s="49">
+      <c r="B58" s="22"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="154"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+      <c r="P58" s="18"/>
+      <c r="Q58" s="18"/>
+      <c r="R58" s="18"/>
+      <c r="S58" s="154"/>
+      <c r="T58" s="18"/>
+      <c r="U58" s="18"/>
+      <c r="V58" s="18"/>
+      <c r="W58" s="154"/>
+      <c r="X58" s="18"/>
+      <c r="Y58" s="154"/>
+      <c r="Z58" s="18"/>
+      <c r="AA58" s="154"/>
+      <c r="AB58" s="18"/>
+      <c r="AC58" s="18"/>
+      <c r="AD58" s="18"/>
+      <c r="AE58" s="18"/>
+      <c r="AF58" s="18"/>
+      <c r="AG58" s="18"/>
+      <c r="AH58" s="18"/>
+      <c r="AI58" s="18"/>
+      <c r="AJ58" s="18"/>
+      <c r="AK58" s="18"/>
+      <c r="AL58" s="155"/>
+      <c r="AM58" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN58" s="50"/>
-      <c r="AO58" s="36">
+      <c r="AN58" s="24"/>
+      <c r="AO58" s="33">
         <f>AW4-AM58</f>
         <v>0</v>
       </c>
-      <c r="AP58" s="37"/>
-      <c r="AQ58" s="64"/>
-      <c r="AR58" s="24"/>
-      <c r="AS58" s="24"/>
-      <c r="AT58" s="24"/>
+      <c r="AP58" s="28"/>
+      <c r="AQ58" s="34"/>
+      <c r="AR58" s="22"/>
+      <c r="AS58" s="22"/>
+      <c r="AT58" s="22"/>
       <c r="AU58" s="5"/>
     </row>
     <row r="59" spans="1:47" ht="19.5" hidden="1" customHeight="1">
-      <c r="A59" s="52">
+      <c r="A59" s="29">
         <v>26</v>
       </c>
-      <c r="B59" s="24"/>
-      <c r="C59" s="34"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="6"/>
-      <c r="P59" s="6"/>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="6"/>
-      <c r="S59" s="7"/>
-      <c r="T59" s="6"/>
-      <c r="U59" s="6"/>
-      <c r="V59" s="6"/>
-      <c r="W59" s="7"/>
-      <c r="X59" s="6"/>
-      <c r="Y59" s="7"/>
-      <c r="Z59" s="6"/>
-      <c r="AA59" s="7"/>
-      <c r="AB59" s="6"/>
-      <c r="AC59" s="6"/>
-      <c r="AD59" s="6"/>
-      <c r="AE59" s="6"/>
-      <c r="AF59" s="6"/>
-      <c r="AG59" s="6"/>
-      <c r="AH59" s="6"/>
-      <c r="AI59" s="6"/>
-      <c r="AJ59" s="6"/>
-      <c r="AK59" s="6"/>
-      <c r="AL59" s="16"/>
-      <c r="AM59" s="49">
+      <c r="B59" s="22"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="154"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
+      <c r="P59" s="18"/>
+      <c r="Q59" s="18"/>
+      <c r="R59" s="18"/>
+      <c r="S59" s="154"/>
+      <c r="T59" s="18"/>
+      <c r="U59" s="18"/>
+      <c r="V59" s="18"/>
+      <c r="W59" s="154"/>
+      <c r="X59" s="18"/>
+      <c r="Y59" s="154"/>
+      <c r="Z59" s="18"/>
+      <c r="AA59" s="154"/>
+      <c r="AB59" s="18"/>
+      <c r="AC59" s="18"/>
+      <c r="AD59" s="18"/>
+      <c r="AE59" s="18"/>
+      <c r="AF59" s="18"/>
+      <c r="AG59" s="18"/>
+      <c r="AH59" s="18"/>
+      <c r="AI59" s="18"/>
+      <c r="AJ59" s="18"/>
+      <c r="AK59" s="18"/>
+      <c r="AL59" s="155"/>
+      <c r="AM59" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN59" s="50"/>
-      <c r="AO59" s="36">
+      <c r="AN59" s="24"/>
+      <c r="AO59" s="33">
         <f>AW4-AM59</f>
         <v>0</v>
       </c>
-      <c r="AP59" s="37"/>
-      <c r="AQ59" s="64"/>
-      <c r="AR59" s="24"/>
-      <c r="AS59" s="24"/>
-      <c r="AT59" s="24"/>
+      <c r="AP59" s="28"/>
+      <c r="AQ59" s="34"/>
+      <c r="AR59" s="22"/>
+      <c r="AS59" s="22"/>
+      <c r="AT59" s="22"/>
       <c r="AU59" s="5"/>
     </row>
     <row r="60" spans="1:47" ht="19.5" hidden="1" customHeight="1">
-      <c r="A60" s="129"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="138"/>
-      <c r="D60" s="139"/>
-      <c r="E60" s="140"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="6"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="7"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
-      <c r="W60" s="7"/>
-      <c r="X60" s="6"/>
-      <c r="Y60" s="7"/>
-      <c r="Z60" s="6"/>
-      <c r="AA60" s="7"/>
-      <c r="AB60" s="6"/>
-      <c r="AC60" s="6"/>
-      <c r="AD60" s="6"/>
-      <c r="AE60" s="6"/>
-      <c r="AF60" s="6"/>
-      <c r="AG60" s="6"/>
-      <c r="AH60" s="6"/>
-      <c r="AI60" s="6"/>
-      <c r="AJ60" s="6"/>
-      <c r="AK60" s="6"/>
-      <c r="AL60" s="16"/>
-      <c r="AM60" s="49">
+      <c r="A60" s="92"/>
+      <c r="B60" s="37"/>
+      <c r="C60" s="148"/>
+      <c r="D60" s="149"/>
+      <c r="E60" s="150"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="154"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+      <c r="P60" s="18"/>
+      <c r="Q60" s="18"/>
+      <c r="R60" s="18"/>
+      <c r="S60" s="154"/>
+      <c r="T60" s="18"/>
+      <c r="U60" s="18"/>
+      <c r="V60" s="18"/>
+      <c r="W60" s="154"/>
+      <c r="X60" s="18"/>
+      <c r="Y60" s="154"/>
+      <c r="Z60" s="18"/>
+      <c r="AA60" s="154"/>
+      <c r="AB60" s="18"/>
+      <c r="AC60" s="18"/>
+      <c r="AD60" s="18"/>
+      <c r="AE60" s="18"/>
+      <c r="AF60" s="18"/>
+      <c r="AG60" s="18"/>
+      <c r="AH60" s="18"/>
+      <c r="AI60" s="18"/>
+      <c r="AJ60" s="18"/>
+      <c r="AK60" s="18"/>
+      <c r="AL60" s="155"/>
+      <c r="AM60" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN60" s="50"/>
-      <c r="AO60" s="36">
+      <c r="AN60" s="24"/>
+      <c r="AO60" s="33">
         <f>AW4-AM60</f>
         <v>0</v>
       </c>
-      <c r="AP60" s="37"/>
-      <c r="AQ60" s="64"/>
-      <c r="AR60" s="24"/>
-      <c r="AS60" s="24"/>
-      <c r="AT60" s="24"/>
+      <c r="AP60" s="28"/>
+      <c r="AQ60" s="34"/>
+      <c r="AR60" s="22"/>
+      <c r="AS60" s="22"/>
+      <c r="AT60" s="22"/>
       <c r="AU60" s="5"/>
     </row>
     <row r="61" spans="1:47" ht="19.5" customHeight="1" thickBot="1">
       <c r="A61" s="141"/>
-      <c r="B61" s="112"/>
-      <c r="C61" s="122" t="s">
+      <c r="B61" s="91"/>
+      <c r="C61" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="D61" s="123"/>
-      <c r="E61" s="124"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="7"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="6"/>
-      <c r="S61" s="7"/>
-      <c r="T61" s="6"/>
-      <c r="U61" s="6"/>
-      <c r="V61" s="6"/>
-      <c r="W61" s="7"/>
-      <c r="X61" s="6"/>
-      <c r="Y61" s="7"/>
-      <c r="Z61" s="6"/>
-      <c r="AA61" s="7"/>
-      <c r="AB61" s="6"/>
-      <c r="AC61" s="6"/>
-      <c r="AD61" s="6"/>
-      <c r="AE61" s="6"/>
-      <c r="AF61" s="6"/>
-      <c r="AG61" s="6"/>
-      <c r="AH61" s="7"/>
-      <c r="AI61" s="6"/>
-      <c r="AJ61" s="6"/>
-      <c r="AK61" s="6"/>
-      <c r="AL61" s="16"/>
-      <c r="AM61" s="42">
+      <c r="D61" s="134"/>
+      <c r="E61" s="135"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="154"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="154"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+      <c r="P61" s="18"/>
+      <c r="Q61" s="18"/>
+      <c r="R61" s="18"/>
+      <c r="S61" s="154"/>
+      <c r="T61" s="18"/>
+      <c r="U61" s="18"/>
+      <c r="V61" s="18"/>
+      <c r="W61" s="154"/>
+      <c r="X61" s="18"/>
+      <c r="Y61" s="154"/>
+      <c r="Z61" s="18"/>
+      <c r="AA61" s="154"/>
+      <c r="AB61" s="18"/>
+      <c r="AC61" s="18"/>
+      <c r="AD61" s="18"/>
+      <c r="AE61" s="18"/>
+      <c r="AF61" s="18"/>
+      <c r="AG61" s="18"/>
+      <c r="AH61" s="154"/>
+      <c r="AI61" s="18"/>
+      <c r="AJ61" s="18"/>
+      <c r="AK61" s="18"/>
+      <c r="AL61" s="155"/>
+      <c r="AM61" s="45">
         <f>SUM(AM34:AN58)</f>
         <v>0</v>
       </c>
-      <c r="AN61" s="43"/>
-      <c r="AO61" s="136">
+      <c r="AN61" s="46"/>
+      <c r="AO61" s="139">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP61" s="137"/>
-      <c r="AQ61" s="38"/>
-      <c r="AR61" s="39"/>
-      <c r="AS61" s="39"/>
-      <c r="AT61" s="39"/>
-      <c r="AU61" s="40"/>
+      <c r="AP61" s="140"/>
+      <c r="AQ61" s="41"/>
+      <c r="AR61" s="42"/>
+      <c r="AS61" s="42"/>
+      <c r="AT61" s="42"/>
+      <c r="AU61" s="43"/>
     </row>
     <row r="62" spans="1:47" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A62" s="154">
+      <c r="A62" s="144">
         <f>A33+A61</f>
         <v>0</v>
       </c>
-      <c r="B62" s="79"/>
-      <c r="C62" s="117" t="s">
+      <c r="B62" s="85"/>
+      <c r="C62" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="D62" s="118"/>
-      <c r="E62" s="112"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="6"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="7"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="7"/>
-      <c r="X62" s="6"/>
-      <c r="Y62" s="7"/>
-      <c r="Z62" s="6"/>
-      <c r="AA62" s="7"/>
-      <c r="AB62" s="6"/>
-      <c r="AC62" s="6"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="6"/>
-      <c r="AF62" s="6"/>
-      <c r="AG62" s="6"/>
-      <c r="AH62" s="7"/>
-      <c r="AI62" s="6"/>
-      <c r="AJ62" s="6"/>
-      <c r="AK62" s="6"/>
-      <c r="AL62" s="16"/>
-      <c r="AM62" s="80">
+      <c r="D62" s="90"/>
+      <c r="E62" s="91"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="154"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="154"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="18"/>
+      <c r="R62" s="18"/>
+      <c r="S62" s="154"/>
+      <c r="T62" s="18"/>
+      <c r="U62" s="18"/>
+      <c r="V62" s="18"/>
+      <c r="W62" s="154"/>
+      <c r="X62" s="18"/>
+      <c r="Y62" s="154"/>
+      <c r="Z62" s="18"/>
+      <c r="AA62" s="154"/>
+      <c r="AB62" s="18"/>
+      <c r="AC62" s="18"/>
+      <c r="AD62" s="18"/>
+      <c r="AE62" s="18"/>
+      <c r="AF62" s="18"/>
+      <c r="AG62" s="18"/>
+      <c r="AH62" s="154"/>
+      <c r="AI62" s="18"/>
+      <c r="AJ62" s="18"/>
+      <c r="AK62" s="18"/>
+      <c r="AL62" s="155"/>
+      <c r="AM62" s="86">
         <f>SUM(AM61,AM33)</f>
         <v>0</v>
       </c>
-      <c r="AN62" s="81"/>
-      <c r="AO62" s="63">
+      <c r="AN62" s="87"/>
+      <c r="AO62" s="55">
         <f>COUNTIF(F34:AL34,"P")</f>
         <v>0</v>
       </c>
-      <c r="AP62" s="60"/>
-      <c r="AQ62" s="38"/>
-      <c r="AR62" s="39"/>
-      <c r="AS62" s="39"/>
-      <c r="AT62" s="39"/>
-      <c r="AU62" s="40"/>
+      <c r="AP62" s="52"/>
+      <c r="AQ62" s="41"/>
+      <c r="AR62" s="42"/>
+      <c r="AS62" s="42"/>
+      <c r="AT62" s="42"/>
+      <c r="AU62" s="43"/>
     </row>
     <row r="63" spans="1:47" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A63" s="47" t="s">
+      <c r="A63" s="98" t="s">
         <v>20</v>
       </c>
       <c r="B63" s="31"/>
@@ -5960,7 +5945,7 @@
       <c r="W63" s="31"/>
       <c r="X63" s="31"/>
       <c r="Y63" s="4"/>
-      <c r="Z63" s="82" t="s">
+      <c r="Z63" s="88" t="s">
         <v>21</v>
       </c>
       <c r="AA63" s="31"/>
@@ -5973,22 +5958,22 @@
       <c r="AH63" s="31"/>
       <c r="AI63" s="31"/>
       <c r="AJ63" s="31"/>
-      <c r="AK63" s="67"/>
+      <c r="AK63" s="58"/>
       <c r="AL63" s="4"/>
-      <c r="AM63" s="97"/>
+      <c r="AM63" s="112"/>
       <c r="AN63" s="31"/>
-      <c r="AO63" s="58"/>
-      <c r="AP63" s="57"/>
-      <c r="AQ63" s="58"/>
-      <c r="AR63" s="108" t="s">
+      <c r="AO63" s="50"/>
+      <c r="AP63" s="49"/>
+      <c r="AQ63" s="50"/>
+      <c r="AR63" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="AS63" s="109"/>
-      <c r="AT63" s="109"/>
-      <c r="AU63" s="110"/>
+      <c r="AS63" s="114"/>
+      <c r="AT63" s="114"/>
+      <c r="AU63" s="115"/>
     </row>
     <row r="64" spans="1:47" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A64" s="54" t="s">
+      <c r="A64" s="32" t="s">
         <v>23</v>
       </c>
       <c r="B64" s="31"/>
@@ -6015,7 +6000,7 @@
       <c r="W64" s="31"/>
       <c r="X64" s="31"/>
       <c r="Y64" s="4"/>
-      <c r="Z64" s="133" t="s">
+      <c r="Z64" s="137" t="s">
         <v>24</v>
       </c>
       <c r="AA64" s="31"/>
@@ -6028,23 +6013,23 @@
       <c r="AH64" s="31"/>
       <c r="AI64" s="31"/>
       <c r="AJ64" s="31"/>
-      <c r="AK64" s="67"/>
+      <c r="AK64" s="58"/>
       <c r="AL64" s="4"/>
-      <c r="AM64" s="59"/>
-      <c r="AN64" s="79"/>
-      <c r="AO64" s="60"/>
-      <c r="AP64" s="59"/>
-      <c r="AQ64" s="60"/>
-      <c r="AR64" s="21" t="s">
+      <c r="AM64" s="51"/>
+      <c r="AN64" s="85"/>
+      <c r="AO64" s="52"/>
+      <c r="AP64" s="51"/>
+      <c r="AQ64" s="52"/>
+      <c r="AR64" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AS64" s="21" t="s">
+      <c r="AS64" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AT64" s="120" t="s">
+      <c r="AT64" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="AU64" s="121"/>
+      <c r="AU64" s="132"/>
     </row>
     <row r="65" spans="1:47" ht="12.95" customHeight="1">
       <c r="A65" s="31"/>
@@ -6072,7 +6057,7 @@
       <c r="W65" s="31"/>
       <c r="X65" s="31"/>
       <c r="Y65" s="4"/>
-      <c r="Z65" s="86"/>
+      <c r="Z65" s="95"/>
       <c r="AA65" s="31"/>
       <c r="AB65" s="31"/>
       <c r="AC65" s="31"/>
@@ -6083,19 +6068,19 @@
       <c r="AH65" s="31"/>
       <c r="AI65" s="31"/>
       <c r="AJ65" s="31"/>
-      <c r="AK65" s="67"/>
+      <c r="AK65" s="58"/>
       <c r="AL65" s="4"/>
-      <c r="AM65" s="30" t="s">
+      <c r="AM65" s="38" t="s">
         <v>28</v>
       </c>
       <c r="AN65" s="31"/>
       <c r="AO65" s="31"/>
       <c r="AP65" s="31"/>
       <c r="AQ65" s="31"/>
-      <c r="AR65" s="155"/>
-      <c r="AS65" s="155"/>
-      <c r="AT65" s="155"/>
-      <c r="AU65" s="155"/>
+      <c r="AR65" s="35"/>
+      <c r="AS65" s="35"/>
+      <c r="AT65" s="35"/>
+      <c r="AU65" s="35"/>
     </row>
     <row r="66" spans="1:47" ht="7.5" customHeight="1">
       <c r="A66" s="31"/>
@@ -6123,7 +6108,7 @@
       <c r="W66" s="31"/>
       <c r="X66" s="31"/>
       <c r="Y66" s="4"/>
-      <c r="Z66" s="82" t="s">
+      <c r="Z66" s="88" t="s">
         <v>29</v>
       </c>
       <c r="AA66" s="31"/>
@@ -6136,17 +6121,17 @@
       <c r="AH66" s="31"/>
       <c r="AI66" s="31"/>
       <c r="AJ66" s="31"/>
-      <c r="AK66" s="67"/>
+      <c r="AK66" s="58"/>
       <c r="AL66" s="4"/>
-      <c r="AM66" s="32"/>
-      <c r="AN66" s="33"/>
-      <c r="AO66" s="33"/>
-      <c r="AP66" s="33"/>
-      <c r="AQ66" s="33"/>
-      <c r="AR66" s="155"/>
-      <c r="AS66" s="155"/>
-      <c r="AT66" s="155"/>
-      <c r="AU66" s="155"/>
+      <c r="AM66" s="39"/>
+      <c r="AN66" s="40"/>
+      <c r="AO66" s="40"/>
+      <c r="AP66" s="40"/>
+      <c r="AQ66" s="40"/>
+      <c r="AR66" s="35"/>
+      <c r="AS66" s="35"/>
+      <c r="AT66" s="35"/>
+      <c r="AU66" s="35"/>
     </row>
     <row r="67" spans="1:47" ht="6" customHeight="1">
       <c r="A67" s="31"/>
@@ -6174,7 +6159,7 @@
       <c r="W67" s="31"/>
       <c r="X67" s="31"/>
       <c r="Y67" s="4"/>
-      <c r="Z67" s="86"/>
+      <c r="Z67" s="95"/>
       <c r="AA67" s="31"/>
       <c r="AB67" s="31"/>
       <c r="AC67" s="31"/>
@@ -6185,32 +6170,32 @@
       <c r="AH67" s="31"/>
       <c r="AI67" s="31"/>
       <c r="AJ67" s="31"/>
-      <c r="AK67" s="67"/>
+      <c r="AK67" s="58"/>
       <c r="AL67" s="4"/>
-      <c r="AM67" s="44" t="s">
+      <c r="AM67" s="96" t="s">
         <v>30</v>
       </c>
       <c r="AN67" s="31"/>
-      <c r="AO67" s="45"/>
-      <c r="AP67" s="96" t="s">
+      <c r="AO67" s="80"/>
+      <c r="AP67" s="111" t="s">
         <v>31</v>
       </c>
       <c r="AQ67" s="31"/>
-      <c r="AR67" s="155"/>
-      <c r="AS67" s="155"/>
-      <c r="AT67" s="155"/>
-      <c r="AU67" s="155"/>
+      <c r="AR67" s="35"/>
+      <c r="AS67" s="35"/>
+      <c r="AT67" s="35"/>
+      <c r="AU67" s="35"/>
     </row>
     <row r="68" spans="1:47" ht="6.75" customHeight="1">
       <c r="A68" s="4"/>
-      <c r="B68" s="84" t="s">
+      <c r="B68" s="104" t="s">
         <v>32</v>
       </c>
       <c r="C68" s="31"/>
       <c r="D68" s="31"/>
       <c r="E68" s="31"/>
       <c r="F68" s="31"/>
-      <c r="G68" s="41" t="s">
+      <c r="G68" s="44" t="s">
         <v>33</v>
       </c>
       <c r="H68" s="31"/>
@@ -6225,7 +6210,7 @@
       <c r="Q68" s="31"/>
       <c r="R68" s="31"/>
       <c r="S68" s="31"/>
-      <c r="T68" s="91" t="s">
+      <c r="T68" s="102" t="s">
         <v>34</v>
       </c>
       <c r="U68" s="31"/>
@@ -6233,7 +6218,7 @@
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
       <c r="Y68" s="4"/>
-      <c r="Z68" s="82" t="s">
+      <c r="Z68" s="88" t="s">
         <v>35</v>
       </c>
       <c r="AA68" s="31"/>
@@ -6246,17 +6231,17 @@
       <c r="AH68" s="31"/>
       <c r="AI68" s="31"/>
       <c r="AJ68" s="31"/>
-      <c r="AK68" s="67"/>
+      <c r="AK68" s="58"/>
       <c r="AL68" s="4"/>
-      <c r="AM68" s="46"/>
+      <c r="AM68" s="97"/>
       <c r="AN68" s="31"/>
-      <c r="AO68" s="45"/>
+      <c r="AO68" s="80"/>
       <c r="AP68" s="31"/>
       <c r="AQ68" s="31"/>
-      <c r="AR68" s="155"/>
-      <c r="AS68" s="155"/>
-      <c r="AT68" s="155"/>
-      <c r="AU68" s="155"/>
+      <c r="AR68" s="35"/>
+      <c r="AS68" s="35"/>
+      <c r="AT68" s="35"/>
+      <c r="AU68" s="35"/>
     </row>
     <row r="69" spans="1:47" ht="3.75" customHeight="1">
       <c r="A69" s="4"/>
@@ -6265,26 +6250,26 @@
       <c r="D69" s="31"/>
       <c r="E69" s="31"/>
       <c r="F69" s="31"/>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="33"/>
-      <c r="J69" s="33"/>
-      <c r="K69" s="33"/>
-      <c r="L69" s="33"/>
-      <c r="M69" s="33"/>
-      <c r="N69" s="33"/>
-      <c r="O69" s="33"/>
-      <c r="P69" s="33"/>
-      <c r="Q69" s="33"/>
-      <c r="R69" s="33"/>
-      <c r="S69" s="33"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="40"/>
+      <c r="I69" s="40"/>
+      <c r="J69" s="40"/>
+      <c r="K69" s="40"/>
+      <c r="L69" s="40"/>
+      <c r="M69" s="40"/>
+      <c r="N69" s="40"/>
+      <c r="O69" s="40"/>
+      <c r="P69" s="40"/>
+      <c r="Q69" s="40"/>
+      <c r="R69" s="40"/>
+      <c r="S69" s="40"/>
       <c r="T69" s="31"/>
       <c r="U69" s="31"/>
       <c r="V69" s="31"/>
       <c r="W69" s="4"/>
       <c r="X69" s="4"/>
       <c r="Y69" s="4"/>
-      <c r="Z69" s="86"/>
+      <c r="Z69" s="95"/>
       <c r="AA69" s="31"/>
       <c r="AB69" s="31"/>
       <c r="AC69" s="31"/>
@@ -6295,19 +6280,19 @@
       <c r="AH69" s="31"/>
       <c r="AI69" s="31"/>
       <c r="AJ69" s="31"/>
-      <c r="AK69" s="67"/>
+      <c r="AK69" s="58"/>
       <c r="AL69" s="4"/>
-      <c r="AM69" s="62" t="s">
+      <c r="AM69" s="54" t="s">
         <v>36</v>
       </c>
       <c r="AN69" s="31"/>
       <c r="AO69" s="31"/>
       <c r="AP69" s="31"/>
       <c r="AQ69" s="31"/>
-      <c r="AR69" s="155"/>
-      <c r="AS69" s="155"/>
-      <c r="AT69" s="155"/>
-      <c r="AU69" s="155"/>
+      <c r="AR69" s="35"/>
+      <c r="AS69" s="35"/>
+      <c r="AT69" s="35"/>
+      <c r="AU69" s="35"/>
     </row>
     <row r="70" spans="1:47" ht="6.95" customHeight="1">
       <c r="A70" s="4"/>
@@ -6316,7 +6301,7 @@
       <c r="D70" s="31"/>
       <c r="E70" s="31"/>
       <c r="F70" s="31"/>
-      <c r="G70" s="91" t="s">
+      <c r="G70" s="102" t="s">
         <v>37</v>
       </c>
       <c r="H70" s="31"/>
@@ -6337,7 +6322,7 @@
       <c r="W70" s="4"/>
       <c r="X70" s="4"/>
       <c r="Y70" s="4"/>
-      <c r="Z70" s="90" t="s">
+      <c r="Z70" s="94" t="s">
         <v>38</v>
       </c>
       <c r="AA70" s="31"/>
@@ -6350,49 +6335,49 @@
       <c r="AH70" s="31"/>
       <c r="AI70" s="31"/>
       <c r="AJ70" s="31"/>
-      <c r="AK70" s="67"/>
+      <c r="AK70" s="58"/>
       <c r="AL70" s="4"/>
-      <c r="AM70" s="32"/>
-      <c r="AN70" s="33"/>
-      <c r="AO70" s="33"/>
-      <c r="AP70" s="33"/>
-      <c r="AQ70" s="33"/>
-      <c r="AR70" s="155"/>
-      <c r="AS70" s="155"/>
-      <c r="AT70" s="155"/>
-      <c r="AU70" s="155"/>
+      <c r="AM70" s="39"/>
+      <c r="AN70" s="40"/>
+      <c r="AO70" s="40"/>
+      <c r="AP70" s="40"/>
+      <c r="AQ70" s="40"/>
+      <c r="AR70" s="35"/>
+      <c r="AS70" s="35"/>
+      <c r="AT70" s="35"/>
+      <c r="AU70" s="35"/>
     </row>
     <row r="71" spans="1:47" ht="9.75" customHeight="1">
       <c r="A71" s="4"/>
-      <c r="B71" s="84" t="s">
+      <c r="B71" s="104" t="s">
         <v>39</v>
       </c>
       <c r="C71" s="31"/>
       <c r="D71" s="31"/>
       <c r="E71" s="31"/>
       <c r="F71" s="31"/>
-      <c r="G71" s="41" t="s">
+      <c r="G71" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="H71" s="33"/>
-      <c r="I71" s="33"/>
-      <c r="J71" s="33"/>
-      <c r="K71" s="33"/>
-      <c r="L71" s="33"/>
-      <c r="M71" s="33"/>
-      <c r="N71" s="33"/>
-      <c r="O71" s="33"/>
-      <c r="P71" s="33"/>
-      <c r="Q71" s="33"/>
-      <c r="R71" s="33"/>
-      <c r="S71" s="33"/>
+      <c r="H71" s="40"/>
+      <c r="I71" s="40"/>
+      <c r="J71" s="40"/>
+      <c r="K71" s="40"/>
+      <c r="L71" s="40"/>
+      <c r="M71" s="40"/>
+      <c r="N71" s="40"/>
+      <c r="O71" s="40"/>
+      <c r="P71" s="40"/>
+      <c r="Q71" s="40"/>
+      <c r="R71" s="40"/>
+      <c r="S71" s="40"/>
       <c r="T71" s="4"/>
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
       <c r="W71" s="4"/>
       <c r="X71" s="4"/>
       <c r="Y71" s="4"/>
-      <c r="Z71" s="86"/>
+      <c r="Z71" s="95"/>
       <c r="AA71" s="31"/>
       <c r="AB71" s="31"/>
       <c r="AC71" s="31"/>
@@ -6403,19 +6388,19 @@
       <c r="AH71" s="31"/>
       <c r="AI71" s="31"/>
       <c r="AJ71" s="31"/>
-      <c r="AK71" s="67"/>
+      <c r="AK71" s="58"/>
       <c r="AL71" s="4"/>
-      <c r="AM71" s="26" t="s">
+      <c r="AM71" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="AN71" s="27"/>
-      <c r="AO71" s="27"/>
-      <c r="AP71" s="27"/>
-      <c r="AQ71" s="27"/>
-      <c r="AR71" s="155"/>
-      <c r="AS71" s="155"/>
-      <c r="AT71" s="155"/>
-      <c r="AU71" s="155"/>
+      <c r="AN71" s="37"/>
+      <c r="AO71" s="37"/>
+      <c r="AP71" s="37"/>
+      <c r="AQ71" s="37"/>
+      <c r="AR71" s="35"/>
+      <c r="AS71" s="35"/>
+      <c r="AT71" s="35"/>
+      <c r="AU71" s="35"/>
     </row>
     <row r="72" spans="1:47" ht="9.75" customHeight="1">
       <c r="A72" s="4"/>
@@ -6424,7 +6409,7 @@
       <c r="D72" s="31"/>
       <c r="E72" s="31"/>
       <c r="F72" s="31"/>
-      <c r="G72" s="91" t="s">
+      <c r="G72" s="102" t="s">
         <v>42</v>
       </c>
       <c r="H72" s="31"/>
@@ -6445,7 +6430,7 @@
       <c r="W72" s="4"/>
       <c r="X72" s="4"/>
       <c r="Y72" s="4"/>
-      <c r="Z72" s="86"/>
+      <c r="Z72" s="95"/>
       <c r="AA72" s="31"/>
       <c r="AB72" s="31"/>
       <c r="AC72" s="31"/>
@@ -6456,45 +6441,45 @@
       <c r="AH72" s="31"/>
       <c r="AI72" s="31"/>
       <c r="AJ72" s="31"/>
-      <c r="AK72" s="67"/>
+      <c r="AK72" s="58"/>
       <c r="AL72" s="4"/>
-      <c r="AM72" s="135" t="s">
+      <c r="AM72" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="AN72" s="33"/>
-      <c r="AO72" s="33"/>
-      <c r="AP72" s="33"/>
-      <c r="AQ72" s="33"/>
-      <c r="AR72" s="155"/>
-      <c r="AS72" s="155"/>
-      <c r="AT72" s="155"/>
-      <c r="AU72" s="155"/>
+      <c r="AN72" s="40"/>
+      <c r="AO72" s="40"/>
+      <c r="AP72" s="40"/>
+      <c r="AQ72" s="40"/>
+      <c r="AR72" s="35"/>
+      <c r="AS72" s="35"/>
+      <c r="AT72" s="35"/>
+      <c r="AU72" s="35"/>
     </row>
     <row r="73" spans="1:47" ht="10.5" customHeight="1">
       <c r="A73" s="4"/>
-      <c r="B73" s="84" t="s">
+      <c r="B73" s="104" t="s">
         <v>44</v>
       </c>
       <c r="C73" s="31"/>
       <c r="D73" s="31"/>
       <c r="E73" s="31"/>
       <c r="F73" s="31"/>
-      <c r="G73" s="41" t="s">
+      <c r="G73" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="H73" s="33"/>
-      <c r="I73" s="33"/>
-      <c r="J73" s="33"/>
-      <c r="K73" s="33"/>
-      <c r="L73" s="33"/>
-      <c r="M73" s="33"/>
-      <c r="N73" s="33"/>
-      <c r="O73" s="33"/>
-      <c r="P73" s="33"/>
-      <c r="Q73" s="33"/>
-      <c r="R73" s="33"/>
-      <c r="S73" s="33"/>
-      <c r="T73" s="91" t="s">
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="40"/>
+      <c r="K73" s="40"/>
+      <c r="L73" s="40"/>
+      <c r="M73" s="40"/>
+      <c r="N73" s="40"/>
+      <c r="O73" s="40"/>
+      <c r="P73" s="40"/>
+      <c r="Q73" s="40"/>
+      <c r="R73" s="40"/>
+      <c r="S73" s="40"/>
+      <c r="T73" s="102" t="s">
         <v>34</v>
       </c>
       <c r="U73" s="31"/>
@@ -6502,7 +6487,7 @@
       <c r="W73" s="4"/>
       <c r="X73" s="4"/>
       <c r="Y73" s="4"/>
-      <c r="Z73" s="86"/>
+      <c r="Z73" s="95"/>
       <c r="AA73" s="31"/>
       <c r="AB73" s="31"/>
       <c r="AC73" s="31"/>
@@ -6513,19 +6498,19 @@
       <c r="AH73" s="31"/>
       <c r="AI73" s="31"/>
       <c r="AJ73" s="31"/>
-      <c r="AK73" s="67"/>
+      <c r="AK73" s="58"/>
       <c r="AL73" s="4"/>
-      <c r="AM73" s="26" t="s">
+      <c r="AM73" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="AN73" s="27"/>
-      <c r="AO73" s="27"/>
-      <c r="AP73" s="27"/>
-      <c r="AQ73" s="27"/>
-      <c r="AR73" s="132"/>
-      <c r="AS73" s="132"/>
-      <c r="AT73" s="132"/>
-      <c r="AU73" s="132"/>
+      <c r="AN73" s="37"/>
+      <c r="AO73" s="37"/>
+      <c r="AP73" s="37"/>
+      <c r="AQ73" s="37"/>
+      <c r="AR73" s="108"/>
+      <c r="AS73" s="108"/>
+      <c r="AT73" s="108"/>
+      <c r="AU73" s="108"/>
     </row>
     <row r="74" spans="1:47" ht="12" customHeight="1">
       <c r="A74" s="4"/>
@@ -6534,7 +6519,7 @@
       <c r="D74" s="31"/>
       <c r="E74" s="31"/>
       <c r="F74" s="31"/>
-      <c r="G74" s="91" t="s">
+      <c r="G74" s="102" t="s">
         <v>33</v>
       </c>
       <c r="H74" s="31"/>
@@ -6555,7 +6540,7 @@
       <c r="W74" s="4"/>
       <c r="X74" s="4"/>
       <c r="Y74" s="4"/>
-      <c r="Z74" s="82" t="s">
+      <c r="Z74" s="88" t="s">
         <v>47</v>
       </c>
       <c r="AA74" s="31"/>
@@ -6568,19 +6553,19 @@
       <c r="AH74" s="31"/>
       <c r="AI74" s="31"/>
       <c r="AJ74" s="31"/>
-      <c r="AK74" s="67"/>
+      <c r="AK74" s="58"/>
       <c r="AL74" s="4"/>
-      <c r="AM74" s="135" t="s">
+      <c r="AM74" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="AN74" s="33"/>
-      <c r="AO74" s="33"/>
-      <c r="AP74" s="33"/>
-      <c r="AQ74" s="33"/>
-      <c r="AR74" s="132"/>
-      <c r="AS74" s="132"/>
-      <c r="AT74" s="132"/>
-      <c r="AU74" s="132"/>
+      <c r="AN74" s="40"/>
+      <c r="AO74" s="40"/>
+      <c r="AP74" s="40"/>
+      <c r="AQ74" s="40"/>
+      <c r="AR74" s="108"/>
+      <c r="AS74" s="108"/>
+      <c r="AT74" s="108"/>
+      <c r="AU74" s="108"/>
     </row>
     <row r="75" spans="1:47" ht="14.25" customHeight="1">
       <c r="A75" s="4"/>
@@ -6608,7 +6593,7 @@
       <c r="W75" s="4"/>
       <c r="X75" s="4"/>
       <c r="Y75" s="4"/>
-      <c r="Z75" s="90" t="s">
+      <c r="Z75" s="94" t="s">
         <v>48</v>
       </c>
       <c r="AA75" s="31"/>
@@ -6621,22 +6606,22 @@
       <c r="AH75" s="31"/>
       <c r="AI75" s="31"/>
       <c r="AJ75" s="31"/>
-      <c r="AK75" s="67"/>
+      <c r="AK75" s="58"/>
       <c r="AL75" s="4"/>
-      <c r="AM75" s="62" t="s">
+      <c r="AM75" s="54" t="s">
         <v>49</v>
       </c>
       <c r="AN75" s="31"/>
       <c r="AO75" s="31"/>
       <c r="AP75" s="31"/>
       <c r="AQ75" s="31"/>
-      <c r="AR75" s="132"/>
-      <c r="AS75" s="132"/>
-      <c r="AT75" s="132"/>
-      <c r="AU75" s="132"/>
+      <c r="AR75" s="108"/>
+      <c r="AS75" s="108"/>
+      <c r="AT75" s="108"/>
+      <c r="AU75" s="108"/>
     </row>
     <row r="76" spans="1:47" ht="1.5" customHeight="1">
-      <c r="A76" s="54" t="s">
+      <c r="A76" s="32" t="s">
         <v>50</v>
       </c>
       <c r="B76" s="31"/>
@@ -6663,7 +6648,7 @@
       <c r="W76" s="31"/>
       <c r="X76" s="31"/>
       <c r="Y76" s="4"/>
-      <c r="Z76" s="86"/>
+      <c r="Z76" s="95"/>
       <c r="AA76" s="31"/>
       <c r="AB76" s="31"/>
       <c r="AC76" s="31"/>
@@ -6674,17 +6659,17 @@
       <c r="AH76" s="31"/>
       <c r="AI76" s="31"/>
       <c r="AJ76" s="31"/>
-      <c r="AK76" s="67"/>
+      <c r="AK76" s="58"/>
       <c r="AL76" s="4"/>
-      <c r="AM76" s="32"/>
-      <c r="AN76" s="33"/>
-      <c r="AO76" s="33"/>
-      <c r="AP76" s="33"/>
-      <c r="AQ76" s="33"/>
-      <c r="AR76" s="132"/>
-      <c r="AS76" s="132"/>
-      <c r="AT76" s="132"/>
-      <c r="AU76" s="132"/>
+      <c r="AM76" s="39"/>
+      <c r="AN76" s="40"/>
+      <c r="AO76" s="40"/>
+      <c r="AP76" s="40"/>
+      <c r="AQ76" s="40"/>
+      <c r="AR76" s="108"/>
+      <c r="AS76" s="108"/>
+      <c r="AT76" s="108"/>
+      <c r="AU76" s="108"/>
     </row>
     <row r="77" spans="1:47" ht="17.25" customHeight="1">
       <c r="A77" s="31"/>
@@ -6712,7 +6697,7 @@
       <c r="W77" s="31"/>
       <c r="X77" s="31"/>
       <c r="Y77" s="4"/>
-      <c r="Z77" s="86"/>
+      <c r="Z77" s="95"/>
       <c r="AA77" s="31"/>
       <c r="AB77" s="31"/>
       <c r="AC77" s="31"/>
@@ -6723,19 +6708,19 @@
       <c r="AH77" s="31"/>
       <c r="AI77" s="31"/>
       <c r="AJ77" s="31"/>
-      <c r="AK77" s="67"/>
+      <c r="AK77" s="58"/>
       <c r="AL77" s="4"/>
-      <c r="AM77" s="62" t="s">
+      <c r="AM77" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="AN77" s="33"/>
-      <c r="AO77" s="33"/>
-      <c r="AP77" s="33"/>
-      <c r="AQ77" s="33"/>
-      <c r="AR77" s="22"/>
-      <c r="AS77" s="22"/>
-      <c r="AT77" s="132"/>
-      <c r="AU77" s="132"/>
+      <c r="AN77" s="40"/>
+      <c r="AO77" s="40"/>
+      <c r="AP77" s="40"/>
+      <c r="AQ77" s="40"/>
+      <c r="AR77" s="11"/>
+      <c r="AS77" s="11"/>
+      <c r="AT77" s="108"/>
+      <c r="AU77" s="108"/>
     </row>
     <row r="78" spans="1:47" ht="17.25" customHeight="1">
       <c r="A78" s="31"/>
@@ -6763,7 +6748,7 @@
       <c r="W78" s="31"/>
       <c r="X78" s="31"/>
       <c r="Y78" s="4"/>
-      <c r="Z78" s="86"/>
+      <c r="Z78" s="95"/>
       <c r="AA78" s="31"/>
       <c r="AB78" s="31"/>
       <c r="AC78" s="31"/>
@@ -6774,19 +6759,19 @@
       <c r="AH78" s="31"/>
       <c r="AI78" s="31"/>
       <c r="AJ78" s="31"/>
-      <c r="AK78" s="67"/>
+      <c r="AK78" s="58"/>
       <c r="AL78" s="4"/>
-      <c r="AM78" s="62" t="s">
+      <c r="AM78" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="AN78" s="33"/>
-      <c r="AO78" s="33"/>
-      <c r="AP78" s="33"/>
-      <c r="AQ78" s="33"/>
-      <c r="AR78" s="156"/>
-      <c r="AS78" s="156"/>
-      <c r="AT78" s="155"/>
-      <c r="AU78" s="155"/>
+      <c r="AN78" s="40"/>
+      <c r="AO78" s="40"/>
+      <c r="AP78" s="40"/>
+      <c r="AQ78" s="40"/>
+      <c r="AR78" s="12"/>
+      <c r="AS78" s="12"/>
+      <c r="AT78" s="35"/>
+      <c r="AU78" s="35"/>
     </row>
     <row r="79" spans="1:47" ht="9.75" customHeight="1">
       <c r="A79" s="31"/>
@@ -6814,7 +6799,7 @@
       <c r="W79" s="31"/>
       <c r="X79" s="31"/>
       <c r="Y79" s="4"/>
-      <c r="Z79" s="86"/>
+      <c r="Z79" s="95"/>
       <c r="AA79" s="31"/>
       <c r="AB79" s="31"/>
       <c r="AC79" s="31"/>
@@ -6825,49 +6810,49 @@
       <c r="AH79" s="31"/>
       <c r="AI79" s="31"/>
       <c r="AJ79" s="31"/>
-      <c r="AK79" s="67"/>
+      <c r="AK79" s="58"/>
       <c r="AL79" s="4"/>
       <c r="AM79" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="AN79" s="27"/>
-      <c r="AO79" s="27"/>
-      <c r="AP79" s="27"/>
-      <c r="AQ79" s="27"/>
-      <c r="AR79" s="155"/>
-      <c r="AS79" s="155"/>
-      <c r="AT79" s="155"/>
-      <c r="AU79" s="155"/>
+      <c r="AN79" s="37"/>
+      <c r="AO79" s="37"/>
+      <c r="AP79" s="37"/>
+      <c r="AQ79" s="37"/>
+      <c r="AR79" s="35"/>
+      <c r="AS79" s="35"/>
+      <c r="AT79" s="35"/>
+      <c r="AU79" s="35"/>
     </row>
     <row r="80" spans="1:47" ht="9.75" customHeight="1">
       <c r="A80" s="4"/>
-      <c r="B80" s="71" t="s">
+      <c r="B80" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
-      <c r="G80" s="72"/>
-      <c r="H80" s="72"/>
-      <c r="I80" s="72"/>
-      <c r="J80" s="72"/>
-      <c r="K80" s="72"/>
-      <c r="L80" s="72"/>
-      <c r="M80" s="72"/>
-      <c r="N80" s="72"/>
-      <c r="O80" s="72"/>
-      <c r="P80" s="72"/>
-      <c r="Q80" s="72"/>
-      <c r="R80" s="72"/>
-      <c r="S80" s="72"/>
-      <c r="T80" s="72"/>
-      <c r="U80" s="72"/>
-      <c r="V80" s="72"/>
-      <c r="W80" s="72"/>
-      <c r="X80" s="73"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="77"/>
+      <c r="E80" s="77"/>
+      <c r="F80" s="77"/>
+      <c r="G80" s="77"/>
+      <c r="H80" s="77"/>
+      <c r="I80" s="77"/>
+      <c r="J80" s="77"/>
+      <c r="K80" s="77"/>
+      <c r="L80" s="77"/>
+      <c r="M80" s="77"/>
+      <c r="N80" s="77"/>
+      <c r="O80" s="77"/>
+      <c r="P80" s="77"/>
+      <c r="Q80" s="77"/>
+      <c r="R80" s="77"/>
+      <c r="S80" s="77"/>
+      <c r="T80" s="77"/>
+      <c r="U80" s="77"/>
+      <c r="V80" s="77"/>
+      <c r="W80" s="77"/>
+      <c r="X80" s="78"/>
       <c r="Y80" s="4"/>
-      <c r="Z80" s="82" t="s">
+      <c r="Z80" s="88" t="s">
         <v>55</v>
       </c>
       <c r="AA80" s="31"/>
@@ -6880,21 +6865,21 @@
       <c r="AH80" s="31"/>
       <c r="AI80" s="31"/>
       <c r="AJ80" s="31"/>
-      <c r="AK80" s="67"/>
+      <c r="AK80" s="58"/>
       <c r="AL80" s="4"/>
-      <c r="AM80" s="32"/>
-      <c r="AN80" s="33"/>
-      <c r="AO80" s="33"/>
-      <c r="AP80" s="33"/>
-      <c r="AQ80" s="33"/>
-      <c r="AR80" s="155"/>
-      <c r="AS80" s="155"/>
-      <c r="AT80" s="155"/>
-      <c r="AU80" s="155"/>
+      <c r="AM80" s="39"/>
+      <c r="AN80" s="40"/>
+      <c r="AO80" s="40"/>
+      <c r="AP80" s="40"/>
+      <c r="AQ80" s="40"/>
+      <c r="AR80" s="35"/>
+      <c r="AS80" s="35"/>
+      <c r="AT80" s="35"/>
+      <c r="AU80" s="35"/>
     </row>
     <row r="81" spans="1:47" ht="9.75" customHeight="1">
       <c r="A81" s="4"/>
-      <c r="B81" s="74"/>
+      <c r="B81" s="79"/>
       <c r="C81" s="31"/>
       <c r="D81" s="31"/>
       <c r="E81" s="31"/>
@@ -6916,9 +6901,9 @@
       <c r="U81" s="31"/>
       <c r="V81" s="31"/>
       <c r="W81" s="31"/>
-      <c r="X81" s="45"/>
+      <c r="X81" s="80"/>
       <c r="Y81" s="4"/>
-      <c r="Z81" s="86"/>
+      <c r="Z81" s="95"/>
       <c r="AA81" s="31"/>
       <c r="AB81" s="31"/>
       <c r="AC81" s="31"/>
@@ -6929,23 +6914,23 @@
       <c r="AH81" s="31"/>
       <c r="AI81" s="31"/>
       <c r="AJ81" s="31"/>
-      <c r="AK81" s="67"/>
+      <c r="AK81" s="58"/>
       <c r="AL81" s="4"/>
-      <c r="AM81" s="143" t="s">
+      <c r="AM81" s="146" t="s">
         <v>56</v>
       </c>
       <c r="AN81" s="31"/>
       <c r="AO81" s="31"/>
       <c r="AP81" s="31"/>
       <c r="AQ81" s="31"/>
-      <c r="AR81" s="155"/>
-      <c r="AS81" s="155"/>
-      <c r="AT81" s="155"/>
-      <c r="AU81" s="155"/>
+      <c r="AR81" s="35"/>
+      <c r="AS81" s="35"/>
+      <c r="AT81" s="35"/>
+      <c r="AU81" s="35"/>
     </row>
     <row r="82" spans="1:47" ht="9.75" customHeight="1">
       <c r="A82" s="4"/>
-      <c r="B82" s="74"/>
+      <c r="B82" s="79"/>
       <c r="C82" s="31"/>
       <c r="D82" s="31"/>
       <c r="E82" s="31"/>
@@ -6967,9 +6952,9 @@
       <c r="U82" s="31"/>
       <c r="V82" s="31"/>
       <c r="W82" s="31"/>
-      <c r="X82" s="45"/>
+      <c r="X82" s="80"/>
       <c r="Y82" s="4"/>
-      <c r="Z82" s="90" t="s">
+      <c r="Z82" s="94" t="s">
         <v>57</v>
       </c>
       <c r="AA82" s="31"/>
@@ -6982,45 +6967,45 @@
       <c r="AH82" s="31"/>
       <c r="AI82" s="31"/>
       <c r="AJ82" s="31"/>
-      <c r="AK82" s="67"/>
+      <c r="AK82" s="58"/>
       <c r="AL82" s="4"/>
-      <c r="AM82" s="32"/>
-      <c r="AN82" s="33"/>
-      <c r="AO82" s="33"/>
-      <c r="AP82" s="33"/>
-      <c r="AQ82" s="33"/>
-      <c r="AR82" s="155"/>
-      <c r="AS82" s="155"/>
-      <c r="AT82" s="155"/>
-      <c r="AU82" s="155"/>
+      <c r="AM82" s="39"/>
+      <c r="AN82" s="40"/>
+      <c r="AO82" s="40"/>
+      <c r="AP82" s="40"/>
+      <c r="AQ82" s="40"/>
+      <c r="AR82" s="35"/>
+      <c r="AS82" s="35"/>
+      <c r="AT82" s="35"/>
+      <c r="AU82" s="35"/>
     </row>
     <row r="83" spans="1:47" ht="4.5" customHeight="1" thickBot="1">
       <c r="A83" s="4"/>
-      <c r="B83" s="75"/>
-      <c r="C83" s="76"/>
-      <c r="D83" s="76"/>
-      <c r="E83" s="76"/>
-      <c r="F83" s="76"/>
-      <c r="G83" s="76"/>
-      <c r="H83" s="76"/>
-      <c r="I83" s="76"/>
-      <c r="J83" s="76"/>
-      <c r="K83" s="76"/>
-      <c r="L83" s="76"/>
-      <c r="M83" s="76"/>
-      <c r="N83" s="76"/>
-      <c r="O83" s="76"/>
-      <c r="P83" s="76"/>
-      <c r="Q83" s="76"/>
-      <c r="R83" s="76"/>
-      <c r="S83" s="76"/>
-      <c r="T83" s="76"/>
-      <c r="U83" s="76"/>
-      <c r="V83" s="76"/>
-      <c r="W83" s="76"/>
-      <c r="X83" s="77"/>
+      <c r="B83" s="81"/>
+      <c r="C83" s="82"/>
+      <c r="D83" s="82"/>
+      <c r="E83" s="82"/>
+      <c r="F83" s="82"/>
+      <c r="G83" s="82"/>
+      <c r="H83" s="82"/>
+      <c r="I83" s="82"/>
+      <c r="J83" s="82"/>
+      <c r="K83" s="82"/>
+      <c r="L83" s="82"/>
+      <c r="M83" s="82"/>
+      <c r="N83" s="82"/>
+      <c r="O83" s="82"/>
+      <c r="P83" s="82"/>
+      <c r="Q83" s="82"/>
+      <c r="R83" s="82"/>
+      <c r="S83" s="82"/>
+      <c r="T83" s="82"/>
+      <c r="U83" s="82"/>
+      <c r="V83" s="82"/>
+      <c r="W83" s="82"/>
+      <c r="X83" s="83"/>
       <c r="Y83" s="4"/>
-      <c r="Z83" s="86"/>
+      <c r="Z83" s="95"/>
       <c r="AA83" s="31"/>
       <c r="AB83" s="31"/>
       <c r="AC83" s="31"/>
@@ -7031,19 +7016,19 @@
       <c r="AH83" s="31"/>
       <c r="AI83" s="31"/>
       <c r="AJ83" s="31"/>
-      <c r="AK83" s="67"/>
+      <c r="AK83" s="58"/>
       <c r="AL83" s="4"/>
-      <c r="AM83" s="78" t="s">
+      <c r="AM83" s="84" t="s">
         <v>58</v>
       </c>
       <c r="AN83" s="31"/>
       <c r="AO83" s="31"/>
       <c r="AP83" s="31"/>
       <c r="AQ83" s="31"/>
-      <c r="AR83" s="155"/>
-      <c r="AS83" s="155"/>
-      <c r="AT83" s="155"/>
-      <c r="AU83" s="155"/>
+      <c r="AR83" s="35"/>
+      <c r="AS83" s="35"/>
+      <c r="AT83" s="35"/>
+      <c r="AU83" s="35"/>
     </row>
     <row r="84" spans="1:47" ht="15" customHeight="1" thickBot="1">
       <c r="A84" s="4"/>
@@ -7071,7 +7056,7 @@
       <c r="W84" s="4"/>
       <c r="X84" s="4"/>
       <c r="Y84" s="4"/>
-      <c r="Z84" s="86"/>
+      <c r="Z84" s="95"/>
       <c r="AA84" s="31"/>
       <c r="AB84" s="31"/>
       <c r="AC84" s="31"/>
@@ -7082,17 +7067,17 @@
       <c r="AH84" s="31"/>
       <c r="AI84" s="31"/>
       <c r="AJ84" s="31"/>
-      <c r="AK84" s="67"/>
+      <c r="AK84" s="58"/>
       <c r="AL84" s="4"/>
-      <c r="AM84" s="59"/>
-      <c r="AN84" s="79"/>
-      <c r="AO84" s="79"/>
-      <c r="AP84" s="79"/>
-      <c r="AQ84" s="79"/>
-      <c r="AR84" s="155"/>
-      <c r="AS84" s="155"/>
-      <c r="AT84" s="155"/>
-      <c r="AU84" s="155"/>
+      <c r="AM84" s="51"/>
+      <c r="AN84" s="85"/>
+      <c r="AO84" s="85"/>
+      <c r="AP84" s="85"/>
+      <c r="AQ84" s="85"/>
+      <c r="AR84" s="35"/>
+      <c r="AS84" s="35"/>
+      <c r="AT84" s="35"/>
+      <c r="AU84" s="35"/>
     </row>
     <row r="85" spans="1:47" ht="21" customHeight="1">
       <c r="A85" s="4"/>
@@ -7120,7 +7105,7 @@
       <c r="W85" s="4"/>
       <c r="X85" s="4"/>
       <c r="Y85" s="4"/>
-      <c r="Z85" s="86"/>
+      <c r="Z85" s="95"/>
       <c r="AA85" s="31"/>
       <c r="AB85" s="31"/>
       <c r="AC85" s="31"/>
@@ -7131,7 +7116,7 @@
       <c r="AH85" s="31"/>
       <c r="AI85" s="31"/>
       <c r="AJ85" s="31"/>
-      <c r="AK85" s="67"/>
+      <c r="AK85" s="58"/>
       <c r="AL85" s="4"/>
       <c r="AM85" s="4"/>
       <c r="AN85" s="4"/>
@@ -7169,7 +7154,7 @@
       <c r="W86" s="4"/>
       <c r="X86" s="4"/>
       <c r="Y86" s="4"/>
-      <c r="Z86" s="82" t="s">
+      <c r="Z86" s="88" t="s">
         <v>59</v>
       </c>
       <c r="AA86" s="31"/>
@@ -7182,9 +7167,9 @@
       <c r="AH86" s="31"/>
       <c r="AI86" s="31"/>
       <c r="AJ86" s="31"/>
-      <c r="AK86" s="67"/>
+      <c r="AK86" s="58"/>
       <c r="AL86" s="4"/>
-      <c r="AM86" s="134" t="s">
+      <c r="AM86" s="138" t="s">
         <v>60</v>
       </c>
       <c r="AN86" s="31"/>
@@ -7222,7 +7207,7 @@
       <c r="W87" s="4"/>
       <c r="X87" s="4"/>
       <c r="Y87" s="4"/>
-      <c r="Z87" s="90" t="s">
+      <c r="Z87" s="94" t="s">
         <v>61</v>
       </c>
       <c r="AA87" s="31"/>
@@ -7235,7 +7220,7 @@
       <c r="AH87" s="31"/>
       <c r="AI87" s="31"/>
       <c r="AJ87" s="31"/>
-      <c r="AK87" s="67"/>
+      <c r="AK87" s="58"/>
       <c r="AL87" s="4"/>
       <c r="AM87" s="31"/>
       <c r="AN87" s="31"/>
@@ -7273,7 +7258,7 @@
       <c r="W88" s="4"/>
       <c r="X88" s="4"/>
       <c r="Y88" s="4"/>
-      <c r="Z88" s="86"/>
+      <c r="Z88" s="95"/>
       <c r="AA88" s="31"/>
       <c r="AB88" s="31"/>
       <c r="AC88" s="31"/>
@@ -7284,10 +7269,10 @@
       <c r="AH88" s="31"/>
       <c r="AI88" s="31"/>
       <c r="AJ88" s="31"/>
-      <c r="AK88" s="67"/>
+      <c r="AK88" s="58"/>
       <c r="AL88" s="4"/>
       <c r="AM88" s="4"/>
-      <c r="AN88" s="93"/>
+      <c r="AN88" s="107"/>
       <c r="AO88" s="31"/>
       <c r="AP88" s="31"/>
       <c r="AQ88" s="31"/>
@@ -7322,7 +7307,7 @@
       <c r="W89" s="4"/>
       <c r="X89" s="4"/>
       <c r="Y89" s="4"/>
-      <c r="Z89" s="82" t="s">
+      <c r="Z89" s="88" t="s">
         <v>62</v>
       </c>
       <c r="AA89" s="31"/>
@@ -7335,17 +7320,17 @@
       <c r="AH89" s="31"/>
       <c r="AI89" s="31"/>
       <c r="AJ89" s="31"/>
-      <c r="AK89" s="67"/>
+      <c r="AK89" s="58"/>
       <c r="AL89" s="4"/>
       <c r="AM89" s="4"/>
-      <c r="AN89" s="79"/>
-      <c r="AO89" s="79"/>
-      <c r="AP89" s="79"/>
-      <c r="AQ89" s="79"/>
-      <c r="AR89" s="79"/>
-      <c r="AS89" s="79"/>
-      <c r="AT89" s="79"/>
-      <c r="AU89" s="79"/>
+      <c r="AN89" s="85"/>
+      <c r="AO89" s="85"/>
+      <c r="AP89" s="85"/>
+      <c r="AQ89" s="85"/>
+      <c r="AR89" s="85"/>
+      <c r="AS89" s="85"/>
+      <c r="AT89" s="85"/>
+      <c r="AU89" s="85"/>
     </row>
     <row r="90" spans="1:47" ht="11.45" customHeight="1">
       <c r="A90" s="4"/>
@@ -7373,7 +7358,7 @@
       <c r="W90" s="4"/>
       <c r="X90" s="4"/>
       <c r="Y90" s="4"/>
-      <c r="Z90" s="90" t="s">
+      <c r="Z90" s="94" t="s">
         <v>63</v>
       </c>
       <c r="AA90" s="31"/>
@@ -7386,10 +7371,10 @@
       <c r="AH90" s="31"/>
       <c r="AI90" s="31"/>
       <c r="AJ90" s="31"/>
-      <c r="AK90" s="67"/>
+      <c r="AK90" s="58"/>
       <c r="AL90" s="4"/>
       <c r="AM90" s="4"/>
-      <c r="AN90" s="65" t="s">
+      <c r="AN90" s="56" t="s">
         <v>64</v>
       </c>
       <c r="AO90" s="31"/>
@@ -7426,7 +7411,7 @@
       <c r="W91" s="4"/>
       <c r="X91" s="4"/>
       <c r="Y91" s="4"/>
-      <c r="Z91" s="66" t="s">
+      <c r="Z91" s="57" t="s">
         <v>65</v>
       </c>
       <c r="AA91" s="31"/>
@@ -7439,7 +7424,7 @@
       <c r="AH91" s="31"/>
       <c r="AI91" s="31"/>
       <c r="AJ91" s="31"/>
-      <c r="AK91" s="67"/>
+      <c r="AK91" s="58"/>
       <c r="AL91" s="4"/>
       <c r="AM91" s="4"/>
       <c r="AN91" s="31"/>
@@ -7477,20 +7462,20 @@
       <c r="W92" s="4"/>
       <c r="X92" s="4"/>
       <c r="Y92" s="4"/>
-      <c r="Z92" s="68"/>
-      <c r="AA92" s="33"/>
-      <c r="AB92" s="33"/>
-      <c r="AC92" s="33"/>
-      <c r="AD92" s="33"/>
-      <c r="AE92" s="33"/>
-      <c r="AF92" s="33"/>
-      <c r="AG92" s="33"/>
-      <c r="AH92" s="33"/>
-      <c r="AI92" s="33"/>
-      <c r="AJ92" s="33"/>
-      <c r="AK92" s="69"/>
+      <c r="Z92" s="59"/>
+      <c r="AA92" s="40"/>
+      <c r="AB92" s="40"/>
+      <c r="AC92" s="40"/>
+      <c r="AD92" s="40"/>
+      <c r="AE92" s="40"/>
+      <c r="AF92" s="40"/>
+      <c r="AG92" s="40"/>
+      <c r="AH92" s="40"/>
+      <c r="AI92" s="40"/>
+      <c r="AJ92" s="40"/>
+      <c r="AK92" s="60"/>
       <c r="AL92" s="4"/>
-      <c r="AM92" s="134" t="s">
+      <c r="AM92" s="138" t="s">
         <v>66</v>
       </c>
       <c r="AN92" s="31"/>
@@ -7577,7 +7562,7 @@
       <c r="W94" s="4"/>
       <c r="X94" s="4"/>
       <c r="Y94" s="4"/>
-      <c r="Z94" s="92"/>
+      <c r="Z94" s="106"/>
       <c r="AA94" s="31"/>
       <c r="AB94" s="31"/>
       <c r="AC94" s="31"/>
@@ -7591,13 +7576,13 @@
       <c r="AK94" s="31"/>
       <c r="AL94" s="4"/>
       <c r="AM94" s="4"/>
-      <c r="AN94" s="93"/>
-      <c r="AO94" s="79"/>
-      <c r="AP94" s="79"/>
-      <c r="AQ94" s="79"/>
-      <c r="AR94" s="79"/>
-      <c r="AS94" s="79"/>
-      <c r="AT94" s="79"/>
+      <c r="AN94" s="107"/>
+      <c r="AO94" s="85"/>
+      <c r="AP94" s="85"/>
+      <c r="AQ94" s="85"/>
+      <c r="AR94" s="85"/>
+      <c r="AS94" s="85"/>
+      <c r="AT94" s="85"/>
       <c r="AU94" s="4"/>
     </row>
     <row r="95" spans="1:47" ht="19.5" customHeight="1">
@@ -7626,23 +7611,23 @@
       <c r="W95" s="4"/>
       <c r="X95" s="4"/>
       <c r="Y95" s="4"/>
-      <c r="Z95" s="55" t="s">
+      <c r="Z95" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="AA95" s="56"/>
-      <c r="AB95" s="56"/>
-      <c r="AC95" s="56"/>
-      <c r="AD95" s="56"/>
-      <c r="AE95" s="56"/>
-      <c r="AF95" s="56"/>
-      <c r="AG95" s="56"/>
-      <c r="AH95" s="56"/>
-      <c r="AI95" s="56"/>
-      <c r="AJ95" s="56"/>
-      <c r="AK95" s="56"/>
+      <c r="AA95" s="48"/>
+      <c r="AB95" s="48"/>
+      <c r="AC95" s="48"/>
+      <c r="AD95" s="48"/>
+      <c r="AE95" s="48"/>
+      <c r="AF95" s="48"/>
+      <c r="AG95" s="48"/>
+      <c r="AH95" s="48"/>
+      <c r="AI95" s="48"/>
+      <c r="AJ95" s="48"/>
+      <c r="AK95" s="48"/>
       <c r="AL95" s="4"/>
       <c r="AM95" s="4"/>
-      <c r="AN95" s="65" t="s">
+      <c r="AN95" s="56" t="s">
         <v>68</v>
       </c>
       <c r="AO95" s="31"/>
@@ -8559,18 +8544,17 @@
     <row r="999" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="381">
-    <mergeCell ref="AM57:AN57"/>
-    <mergeCell ref="AM5:AP6"/>
-    <mergeCell ref="Z63:AK63"/>
-    <mergeCell ref="AO10:AP10"/>
-    <mergeCell ref="AM25:AN25"/>
-    <mergeCell ref="AO25:AP25"/>
-    <mergeCell ref="AM74:AQ74"/>
     <mergeCell ref="AT79:AU80"/>
     <mergeCell ref="AQ21:AU21"/>
-    <mergeCell ref="G74:S74"/>
-    <mergeCell ref="AR67:AR70"/>
-    <mergeCell ref="AR79:AR80"/>
+    <mergeCell ref="AQ17:AU17"/>
+    <mergeCell ref="AM23:AN23"/>
+    <mergeCell ref="AO23:AP23"/>
+    <mergeCell ref="AO37:AP37"/>
+    <mergeCell ref="AM24:AN24"/>
+    <mergeCell ref="AO24:AP24"/>
+    <mergeCell ref="AO12:AP12"/>
+    <mergeCell ref="AM31:AN31"/>
+    <mergeCell ref="AO19:AP19"/>
     <mergeCell ref="AQ5:AU7"/>
     <mergeCell ref="AQ47:AT47"/>
     <mergeCell ref="AQ38:AU38"/>
@@ -8580,16 +8564,19 @@
     <mergeCell ref="AM43:AN43"/>
     <mergeCell ref="AM40:AN40"/>
     <mergeCell ref="AQ12:AU12"/>
-    <mergeCell ref="AR71:AR72"/>
     <mergeCell ref="AQ25:AU25"/>
     <mergeCell ref="AM28:AN28"/>
     <mergeCell ref="AQ13:AU13"/>
     <mergeCell ref="AQ14:AU14"/>
     <mergeCell ref="AM54:AN54"/>
     <mergeCell ref="AO54:AP54"/>
-    <mergeCell ref="AM81:AQ82"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="AO56:AP56"/>
+    <mergeCell ref="AQ32:AT32"/>
+    <mergeCell ref="AM27:AN27"/>
+    <mergeCell ref="AM57:AN57"/>
+    <mergeCell ref="AM5:AP6"/>
+    <mergeCell ref="AO10:AP10"/>
+    <mergeCell ref="AM25:AN25"/>
+    <mergeCell ref="AO25:AP25"/>
     <mergeCell ref="AQ15:AU15"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="A34:B34"/>
@@ -8600,10 +8587,8 @@
     <mergeCell ref="AT73:AU74"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="AO41:AP41"/>
-    <mergeCell ref="AT75:AU76"/>
     <mergeCell ref="AO34:AP34"/>
     <mergeCell ref="AQ40:AU40"/>
-    <mergeCell ref="Z75:AK79"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="A53:B53"/>
@@ -8611,9 +8596,11 @@
     <mergeCell ref="AQ56:AT56"/>
     <mergeCell ref="C55:D55"/>
     <mergeCell ref="C60:E60"/>
-    <mergeCell ref="AQ32:AT32"/>
-    <mergeCell ref="Z87:AK88"/>
-    <mergeCell ref="AO28:AP28"/>
+    <mergeCell ref="G74:S74"/>
+    <mergeCell ref="AR67:AR70"/>
+    <mergeCell ref="AR71:AR72"/>
+    <mergeCell ref="T73:V74"/>
+    <mergeCell ref="G71:S71"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="AM59:AN59"/>
     <mergeCell ref="G72:S72"/>
@@ -8634,8 +8621,11 @@
     <mergeCell ref="AM75:AQ76"/>
     <mergeCell ref="AO31:AP31"/>
     <mergeCell ref="AS79:AS80"/>
-    <mergeCell ref="AM27:AN27"/>
     <mergeCell ref="AM72:AQ72"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="AM81:AQ82"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="G73:S73"/>
     <mergeCell ref="AW17:AX23"/>
     <mergeCell ref="AQ27:AT27"/>
     <mergeCell ref="AR65:AR66"/>
@@ -8657,9 +8647,8 @@
     <mergeCell ref="AQ41:AU41"/>
     <mergeCell ref="AQ34:AU34"/>
     <mergeCell ref="AM33:AN33"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B71:F72"/>
-    <mergeCell ref="AQ46:AT46"/>
+    <mergeCell ref="AQ51:AU51"/>
+    <mergeCell ref="AM48:AN48"/>
     <mergeCell ref="AW6:AX8"/>
     <mergeCell ref="AQ18:AU18"/>
     <mergeCell ref="AN94:AT94"/>
@@ -8681,8 +8670,9 @@
     <mergeCell ref="AO44:AP44"/>
     <mergeCell ref="AQ28:AU28"/>
     <mergeCell ref="AT78:AU78"/>
-    <mergeCell ref="G73:S73"/>
-    <mergeCell ref="T73:V74"/>
+    <mergeCell ref="AM44:AN44"/>
+    <mergeCell ref="Z87:AK88"/>
+    <mergeCell ref="AO28:AP28"/>
     <mergeCell ref="A2:AU2"/>
     <mergeCell ref="AT64:AU64"/>
     <mergeCell ref="B68:F70"/>
@@ -8703,7 +8693,10 @@
     <mergeCell ref="AM11:AN11"/>
     <mergeCell ref="C52:D52"/>
     <mergeCell ref="C39:D39"/>
-    <mergeCell ref="G71:S71"/>
+    <mergeCell ref="AO18:AP18"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="AM19:AN19"/>
+    <mergeCell ref="AM46:AN46"/>
     <mergeCell ref="AW3:AX3"/>
     <mergeCell ref="AM4:AU4"/>
     <mergeCell ref="C59:D59"/>
@@ -8752,8 +8745,6 @@
     <mergeCell ref="AM7:AN7"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="AO18:AP18"/>
-    <mergeCell ref="J3:L3"/>
     <mergeCell ref="Z94:AK94"/>
     <mergeCell ref="AO43:AP43"/>
     <mergeCell ref="AN88:AU89"/>
@@ -8778,17 +8769,6 @@
     <mergeCell ref="AR63:AU63"/>
     <mergeCell ref="AO17:AP17"/>
     <mergeCell ref="AN90:AU91"/>
-    <mergeCell ref="AM19:AN19"/>
-    <mergeCell ref="AM46:AN46"/>
-    <mergeCell ref="AQ51:AU51"/>
-    <mergeCell ref="Z80:AK81"/>
-    <mergeCell ref="AM48:AN48"/>
-    <mergeCell ref="AM44:AN44"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="AO35:AP35"/>
     <mergeCell ref="AT65:AU66"/>
     <mergeCell ref="AQ57:AT57"/>
     <mergeCell ref="Z89:AK89"/>
@@ -8797,23 +8777,22 @@
     <mergeCell ref="T68:V70"/>
     <mergeCell ref="AQ59:AT59"/>
     <mergeCell ref="AS67:AS70"/>
-    <mergeCell ref="AQ17:AU17"/>
     <mergeCell ref="AM20:AN20"/>
     <mergeCell ref="AM29:AN29"/>
     <mergeCell ref="AQ37:AU37"/>
     <mergeCell ref="AO33:AP33"/>
     <mergeCell ref="AQ26:AT26"/>
     <mergeCell ref="AO47:AP47"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="B73:F74"/>
     <mergeCell ref="AM41:AN41"/>
     <mergeCell ref="AQ23:AU23"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="AM23:AN23"/>
-    <mergeCell ref="AO23:AP23"/>
-    <mergeCell ref="AO37:AP37"/>
-    <mergeCell ref="AM24:AN24"/>
-    <mergeCell ref="AO24:AP24"/>
+    <mergeCell ref="AQ46:AT46"/>
+    <mergeCell ref="AO56:AP56"/>
+    <mergeCell ref="AT75:AU76"/>
+    <mergeCell ref="Z75:AK79"/>
+    <mergeCell ref="AR79:AR80"/>
+    <mergeCell ref="Z80:AK81"/>
+    <mergeCell ref="Z63:AK63"/>
+    <mergeCell ref="AM74:AQ74"/>
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="AM73:AQ73"/>
@@ -8824,6 +8803,20 @@
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="Z70:AK73"/>
+    <mergeCell ref="AO59:AP59"/>
+    <mergeCell ref="AO46:AP46"/>
+    <mergeCell ref="AO58:AP58"/>
+    <mergeCell ref="AM67:AO68"/>
+    <mergeCell ref="A63:X63"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="AO35:AP35"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="B73:F74"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="B71:F72"/>
     <mergeCell ref="B80:X83"/>
     <mergeCell ref="AO45:AP45"/>
     <mergeCell ref="A38:B38"/>
@@ -8848,26 +8841,18 @@
     <mergeCell ref="AO22:AP22"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="AO51:AP51"/>
-    <mergeCell ref="S4:Z4"/>
-    <mergeCell ref="F4:R4"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A16:B16"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="F5:AL5"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C5:E7"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="AA3:AG3"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="Z95:AK95"/>
     <mergeCell ref="AO49:AP49"/>
     <mergeCell ref="AP63:AQ64"/>
@@ -8892,10 +8877,6 @@
     <mergeCell ref="AM10:AN10"/>
     <mergeCell ref="AQ29:AU29"/>
     <mergeCell ref="Z91:AK92"/>
-    <mergeCell ref="AO12:AP12"/>
-    <mergeCell ref="AM31:AN31"/>
-    <mergeCell ref="AO59:AP59"/>
-    <mergeCell ref="AO46:AP46"/>
     <mergeCell ref="A76:X79"/>
     <mergeCell ref="AQ54:AU54"/>
     <mergeCell ref="AO57:AP57"/>
@@ -8906,7 +8887,6 @@
     <mergeCell ref="C56:D56"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="AQ44:AU44"/>
     <mergeCell ref="AQ31:AT31"/>
@@ -8916,18 +8896,11 @@
     <mergeCell ref="AM47:AN47"/>
     <mergeCell ref="AO52:AP52"/>
     <mergeCell ref="AQ36:AU36"/>
-    <mergeCell ref="AA3:AG3"/>
     <mergeCell ref="AM71:AQ71"/>
-    <mergeCell ref="A25:B25"/>
     <mergeCell ref="AM65:AQ66"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="AO19:AP19"/>
     <mergeCell ref="AQ62:AU62"/>
     <mergeCell ref="G68:S69"/>
     <mergeCell ref="AM61:AN61"/>
-    <mergeCell ref="AO58:AP58"/>
-    <mergeCell ref="AM67:AO68"/>
-    <mergeCell ref="A63:X63"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="AM37:AN37"/>
@@ -8937,9 +8910,21 @@
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="AI4:AL4"/>
     <mergeCell ref="S3:Z3"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:D54"/>
     <mergeCell ref="A41:B41"/>
+    <mergeCell ref="S4:Z4"/>
+    <mergeCell ref="F4:R4"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <pageMargins left="0.31496062992125978" right="0.31496062992125978" top="0.15748031496062989" bottom="0.15748031496062989" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="98" orientation="landscape" r:id="rId1"/>
